--- a/salaries_with_roles/salaries_with_roles.xlsx
+++ b/salaries_with_roles/salaries_with_roles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data_Analystics-Projects\salaries_with_roles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6190E989-ED38-491F-9F61-2A5A62CD7489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603508DC-BE76-48EF-9D81-97A2002FC0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="310">
   <si>
     <t>First Name</t>
   </si>
@@ -952,12 +952,27 @@
   </si>
   <si>
     <t>Std</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Emp. Rating</t>
+  </si>
+  <si>
+    <t>Rating(1-5)</t>
+  </si>
+  <si>
+    <t>Median&gt;Avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1042,7 +1057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1057,6 +1072,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1363,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
@@ -1380,7 +1407,7 @@
     <col min="13" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,8 +1432,14 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1431,8 +1464,14 @@
       <c r="H2" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J2" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1457,8 +1496,14 @@
       <c r="H3" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J3" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1483,8 +1528,14 @@
       <c r="H4" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J4" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1509,8 +1560,14 @@
       <c r="H5" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J5" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1535,8 +1592,14 @@
       <c r="H6" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J6" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1561,8 +1624,14 @@
       <c r="H7" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J7" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1587,8 +1656,14 @@
       <c r="H8" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1613,8 +1688,14 @@
       <c r="H9" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J9" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1639,8 +1720,14 @@
       <c r="H10" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J10" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1665,8 +1752,14 @@
       <c r="H11" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J11" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1691,8 +1784,14 @@
       <c r="H12" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1717,8 +1816,14 @@
       <c r="H13" s="4" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1743,8 +1848,14 @@
       <c r="H14" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J14" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1769,8 +1880,14 @@
       <c r="H15" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1795,8 +1912,14 @@
       <c r="H16" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1821,8 +1944,14 @@
       <c r="H17" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="11">
+        <v>3</v>
+      </c>
+      <c r="J17" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1847,8 +1976,14 @@
       <c r="H18" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1873,8 +2008,14 @@
       <c r="H19" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J19" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1899,8 +2040,14 @@
       <c r="H20" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J20" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1925,8 +2072,14 @@
       <c r="H21" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J21" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1951,8 +2104,14 @@
       <c r="H22" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J22" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
@@ -1977,8 +2136,14 @@
       <c r="H23" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J23" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -2003,8 +2168,14 @@
       <c r="H24" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J24" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -2029,8 +2200,14 @@
       <c r="H25" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J25" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -2055,8 +2232,14 @@
       <c r="H26" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J26" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -2081,8 +2264,14 @@
       <c r="H27" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J27" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>33</v>
       </c>
@@ -2107,8 +2296,14 @@
       <c r="H28" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J28" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
@@ -2133,8 +2328,14 @@
       <c r="H29" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
@@ -2159,8 +2360,14 @@
       <c r="H30" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J30" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
@@ -2185,8 +2392,14 @@
       <c r="H31" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J31" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -2211,8 +2424,14 @@
       <c r="H32" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
@@ -2237,8 +2456,14 @@
       <c r="H33" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J33" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
@@ -2263,8 +2488,14 @@
       <c r="H34" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J34" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
@@ -2289,8 +2520,14 @@
       <c r="H35" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J35" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -2315,8 +2552,14 @@
       <c r="H36" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J36" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
@@ -2341,8 +2584,14 @@
       <c r="H37" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
@@ -2367,8 +2616,14 @@
       <c r="H38" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J38" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -2393,8 +2648,14 @@
       <c r="H39" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J39" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
@@ -2419,8 +2680,14 @@
       <c r="H40" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40" s="11">
+        <v>3</v>
+      </c>
+      <c r="J40" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>45</v>
       </c>
@@ -2445,8 +2712,14 @@
       <c r="H41" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="J41" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>16</v>
       </c>
@@ -2471,8 +2744,14 @@
       <c r="H42" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="J42" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
@@ -2497,8 +2776,14 @@
       <c r="H43" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J43" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
@@ -2523,8 +2808,14 @@
       <c r="H44" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J44" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>48</v>
       </c>
@@ -2549,8 +2840,14 @@
       <c r="H45" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J45" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>49</v>
       </c>
@@ -2575,8 +2872,14 @@
       <c r="H46" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J46" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>50</v>
       </c>
@@ -2601,8 +2904,14 @@
       <c r="H47" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J47" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
@@ -2627,8 +2936,14 @@
       <c r="H48" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J48" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -2653,8 +2968,14 @@
       <c r="H49" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J49" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
@@ -2679,8 +3000,14 @@
       <c r="H50" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J50" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>54</v>
       </c>
@@ -2705,8 +3032,14 @@
       <c r="H51" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="11">
+        <v>3</v>
+      </c>
+      <c r="J51" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>55</v>
       </c>
@@ -2731,8 +3064,14 @@
       <c r="H52" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J52" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
@@ -2757,8 +3096,14 @@
       <c r="H53" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J53" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>57</v>
       </c>
@@ -2783,8 +3128,14 @@
       <c r="H54" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J54" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>58</v>
       </c>
@@ -2809,8 +3160,14 @@
       <c r="H55" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J55" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>59</v>
       </c>
@@ -2835,8 +3192,14 @@
       <c r="H56" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J56" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
@@ -2861,8 +3224,14 @@
       <c r="H57" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="J57" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -2887,8 +3256,14 @@
       <c r="H58" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J58" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2913,8 +3288,14 @@
       <c r="H59" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J59" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
@@ -2939,8 +3320,14 @@
       <c r="H60" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J60" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
@@ -2965,8 +3352,14 @@
       <c r="H61" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
@@ -2991,8 +3384,14 @@
       <c r="H62" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J62" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
@@ -3017,8 +3416,14 @@
       <c r="H63" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="J63" s="8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
@@ -3043,8 +3448,14 @@
       <c r="H64" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J64" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>59</v>
       </c>
@@ -3069,8 +3480,14 @@
       <c r="H65" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="J65" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>67</v>
       </c>
@@ -3095,8 +3512,14 @@
       <c r="H66" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J66" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
@@ -3121,8 +3544,14 @@
       <c r="H67" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J67" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>69</v>
       </c>
@@ -3147,8 +3576,14 @@
       <c r="H68" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J68" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>70</v>
       </c>
@@ -3173,8 +3608,14 @@
       <c r="H69" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J69" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>71</v>
       </c>
@@ -3199,8 +3640,14 @@
       <c r="H70" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J70" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>72</v>
       </c>
@@ -3225,8 +3672,14 @@
       <c r="H71" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J71" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>73</v>
       </c>
@@ -3251,8 +3704,14 @@
       <c r="H72" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J72" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>74</v>
       </c>
@@ -3277,8 +3736,14 @@
       <c r="H73" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J73" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>75</v>
       </c>
@@ -3303,8 +3768,14 @@
       <c r="H74" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74" s="11">
+        <v>3</v>
+      </c>
+      <c r="J74" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>16</v>
       </c>
@@ -3329,8 +3800,14 @@
       <c r="H75" s="4" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J75" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>76</v>
       </c>
@@ -3355,8 +3832,14 @@
       <c r="H76" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J76" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
@@ -3381,8 +3864,14 @@
       <c r="H77" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J77" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>69</v>
       </c>
@@ -3407,8 +3896,14 @@
       <c r="H78" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J78" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
@@ -3433,8 +3928,14 @@
       <c r="H79" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J79" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
@@ -3459,8 +3960,14 @@
       <c r="H80" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="J80" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
@@ -3485,8 +3992,14 @@
       <c r="H81" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J81" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
@@ -3511,8 +4024,14 @@
       <c r="H82" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J82" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>55</v>
       </c>
@@ -3537,8 +4056,14 @@
       <c r="H83" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J83" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>77</v>
       </c>
@@ -3563,8 +4088,14 @@
       <c r="H84" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J84" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>80</v>
       </c>
@@ -3589,8 +4120,14 @@
       <c r="H85" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="J85" s="8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>81</v>
       </c>
@@ -3615,8 +4152,14 @@
       <c r="H86" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I86" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J86" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -3641,8 +4184,14 @@
       <c r="H87" s="4" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I87" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="J87" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>83</v>
       </c>
@@ -3667,8 +4216,14 @@
       <c r="H88" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I88" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J88" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>28</v>
       </c>
@@ -3693,8 +4248,14 @@
       <c r="H89" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I89" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J89" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>84</v>
       </c>
@@ -3719,8 +4280,14 @@
       <c r="H90" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I90" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J90" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>85</v>
       </c>
@@ -3745,8 +4312,14 @@
       <c r="H91" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I91" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J91" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>86</v>
       </c>
@@ -3771,8 +4344,14 @@
       <c r="H92" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I92" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J92" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>87</v>
       </c>
@@ -3797,8 +4376,14 @@
       <c r="H93" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I93" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J93" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>88</v>
       </c>
@@ -3823,8 +4408,14 @@
       <c r="H94" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I94" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="J94" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>89</v>
       </c>
@@ -3849,8 +4440,14 @@
       <c r="H95" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I95" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="J95" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>90</v>
       </c>
@@ -3875,8 +4472,14 @@
       <c r="H96" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I96" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J96" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>91</v>
       </c>
@@ -3901,8 +4504,14 @@
       <c r="H97" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I97" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="J97" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>92</v>
       </c>
@@ -3927,8 +4536,14 @@
       <c r="H98" s="4" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I98" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J98" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>93</v>
       </c>
@@ -3953,8 +4568,14 @@
       <c r="H99" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I99" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="J99" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>94</v>
       </c>
@@ -3979,8 +4600,14 @@
       <c r="H100" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I100" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J100" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>95</v>
       </c>
@@ -4005,15 +4632,43 @@
       <c r="H101" s="4" t="s">
         <v>289</v>
       </c>
+      <c r="I101" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="J101" s="8">
+        <v>4.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{82039766-BEA8-407F-836B-ED3A6E61961A}">
+            <x14:iconSet iconSet="3Stars" showValue="0">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>4</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J2:J101</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3A3C5C-E7A3-4ED0-A8D8-554506645B9D}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -4021,10 +4676,12 @@
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>300</v>
       </c>
@@ -4043,2614 +4700,3461 @@
       <c r="F1" s="7" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="str">
+      <c r="G1" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A2," ",Sheet1!B2)</f>
         <v>Maria Matthews</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A2, " (",Sheet1!H2,")")</f>
         <v>Maria (System Administrator)</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="9">
         <f>SUM(Sheet1!D2:G2)</f>
         <v>19714.559999999998</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="9">
         <f>AVERAGE(Sheet1!D2:G2)</f>
         <v>4928.6399999999994</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="9">
         <f>MEDIAN(Sheet1!D2:F2,Sheet1!G2)</f>
         <v>5229.2250000000004</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="10">
         <f>STDEV(Sheet1!D2:G2)</f>
         <v>1275.5392790763742</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="str">
+      <c r="G2" s="9">
+        <f>PRODUCT(Sheet1!D2,Sheet1!F2:G2)</f>
+        <v>113158186357.21536</v>
+      </c>
+      <c r="H2" s="9" t="str">
+        <f>IF(E2&gt;D2,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A3," ",Sheet1!B3)</f>
         <v>Jenna Wilson</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A3, " (",Sheet1!H3,")")</f>
         <v>Jenna (QA Engineer)</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <f>SUM(Sheet1!D3:G3)</f>
         <v>19350.419999999998</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <f>AVERAGE(Sheet1!D3:G3)</f>
         <v>4837.6049999999996</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="9">
         <f>MEDIAN(Sheet1!D3:F3,Sheet1!G3)</f>
         <v>4999.085</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="10">
         <f>STDEV(Sheet1!D3:G3)</f>
         <v>1126.3574497911416</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="str">
+      <c r="G3" s="9">
+        <f>PRODUCT(Sheet1!D3,Sheet1!F3:G3)</f>
+        <v>87962839949.162384</v>
+      </c>
+      <c r="H3" s="9" t="str">
+        <f t="shared" ref="H3:H66" si="0">IF(E3&gt;D3,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A4," ",Sheet1!B4)</f>
         <v>Charles Morgan</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B4" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A4, " (",Sheet1!H4,")")</f>
         <v>Charles (Mobile App Developer)</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <f>SUM(Sheet1!D4:G4)</f>
         <v>22629.119999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <f>AVERAGE(Sheet1!D4:G4)</f>
         <v>5657.28</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="9">
         <f>MEDIAN(Sheet1!D4:F4,Sheet1!G4)</f>
         <v>5960.4449999999997</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="10">
         <f>STDEV(Sheet1!D4:G4)</f>
         <v>1378.9222741692167</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="str">
+      <c r="G4" s="9">
+        <f>PRODUCT(Sheet1!D4,Sheet1!F4:G4)</f>
+        <v>157977029147.8287</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A5," ",Sheet1!B5)</f>
         <v>Richard Padilla</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A5, " (",Sheet1!H5,")")</f>
         <v>Richard (System Administrator)</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <f>SUM(Sheet1!D5:G5)</f>
         <v>22833.69</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <f>AVERAGE(Sheet1!D5:G5)</f>
         <v>5708.4224999999997</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="9">
         <f>MEDIAN(Sheet1!D5:F5,Sheet1!G5)</f>
         <v>6186.16</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="10">
         <f>STDEV(Sheet1!D5:G5)</f>
         <v>1256.5419138618797</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="str">
+      <c r="G5" s="9">
+        <f>PRODUCT(Sheet1!D5,Sheet1!F5:G5)</f>
+        <v>251538956263.08948</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A6," ",Sheet1!B6)</f>
         <v>Cindy Roberts</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A6, " (",Sheet1!H6,")")</f>
         <v>Cindy (Full Stack Developer)</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="9">
         <f>SUM(Sheet1!D6:G6)</f>
         <v>19810.580000000002</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <f>AVERAGE(Sheet1!D6:G6)</f>
         <v>4952.6450000000004</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="9">
         <f>MEDIAN(Sheet1!D6:F6,Sheet1!G6)</f>
         <v>5235.7950000000001</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="10">
         <f>STDEV(Sheet1!D6:G6)</f>
         <v>1472.3394251439872</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="str">
+      <c r="G6" s="9">
+        <f>PRODUCT(Sheet1!D6,Sheet1!F6:G6)</f>
+        <v>81951095956.771439</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A7," ",Sheet1!B7)</f>
         <v>Lauren Bailey</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A7, " (",Sheet1!H7,")")</f>
         <v>Lauren (UI/UX Designer)</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f>SUM(Sheet1!D7:G7)</f>
         <v>20536.919999999998</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f>AVERAGE(Sheet1!D7:G7)</f>
         <v>5134.2299999999996</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="9">
         <f>MEDIAN(Sheet1!D7:F7,Sheet1!G7)</f>
         <v>5292.0949999999993</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="10">
         <f>STDEV(Sheet1!D7:G7)</f>
         <v>1451.0492338304748</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="str">
+      <c r="G7" s="9">
+        <f>PRODUCT(Sheet1!D7,Sheet1!F7:G7)</f>
+        <v>107348911244.79958</v>
+      </c>
+      <c r="H7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A8," ",Sheet1!B8)</f>
         <v>Jill Thomas</v>
       </c>
-      <c r="B8" s="2" t="str">
+      <c r="B8" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A8, " (",Sheet1!H8,")")</f>
         <v>Jill (Mobile App Developer)</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="9">
         <f>SUM(Sheet1!D8:G8)</f>
         <v>22228.089999999997</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <f>AVERAGE(Sheet1!D8:G8)</f>
         <v>5557.0224999999991</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="9">
         <f>MEDIAN(Sheet1!D8:F8,Sheet1!G8)</f>
         <v>5647.27</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="10">
         <f>STDEV(Sheet1!D8:G8)</f>
         <v>1008.4312351824893</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="str">
+      <c r="G8" s="9">
+        <f>PRODUCT(Sheet1!D8,Sheet1!F8:G8)</f>
+        <v>206930333174.88055</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A9," ",Sheet1!B9)</f>
         <v>Kristin Ashley</v>
       </c>
-      <c r="B9" s="2" t="str">
+      <c r="B9" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A9, " (",Sheet1!H9,")")</f>
         <v>Kristin (QA Engineer)</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="9">
         <f>SUM(Sheet1!D9:G9)</f>
         <v>14240.029999999999</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <f>AVERAGE(Sheet1!D9:G9)</f>
         <v>3560.0074999999997</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="9">
         <f>MEDIAN(Sheet1!D9:F9,Sheet1!G9)</f>
         <v>3395.2750000000001</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="10">
         <f>STDEV(Sheet1!D9:G9)</f>
         <v>523.70867533868477</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="str">
+      <c r="G9" s="9">
+        <f>PRODUCT(Sheet1!D9,Sheet1!F9:G9)</f>
+        <v>49796409013.680664</v>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A10," ",Sheet1!B10)</f>
         <v>Amanda Howard</v>
       </c>
-      <c r="B10" s="2" t="str">
+      <c r="B10" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A10, " (",Sheet1!H10,")")</f>
         <v>Amanda (Backend Developer)</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="9">
         <f>SUM(Sheet1!D10:G10)</f>
         <v>18016.830000000002</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <f>AVERAGE(Sheet1!D10:G10)</f>
         <v>4504.2075000000004</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="9">
         <f>MEDIAN(Sheet1!D10:F10,Sheet1!G10)</f>
         <v>4344.7650000000003</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="10">
         <f>STDEV(Sheet1!D10:G10)</f>
         <v>730.13116800453304</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="str">
+      <c r="G10" s="9">
+        <f>PRODUCT(Sheet1!D10,Sheet1!F10:G10)</f>
+        <v>71890055469.734116</v>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A11," ",Sheet1!B11)</f>
         <v>Joanne Johnson</v>
       </c>
-      <c r="B11" s="2" t="str">
+      <c r="B11" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A11, " (",Sheet1!H11,")")</f>
         <v>Joanne (Product Manager)</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="9">
         <f>SUM(Sheet1!D11:G11)</f>
         <v>21615.72</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="9">
         <f>AVERAGE(Sheet1!D11:G11)</f>
         <v>5403.93</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="9">
         <f>MEDIAN(Sheet1!D11:F11,Sheet1!G11)</f>
         <v>5970.1849999999995</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="10">
         <f>STDEV(Sheet1!D11:G11)</f>
         <v>1594.0756624660767</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="str">
+      <c r="G11" s="9">
+        <f>PRODUCT(Sheet1!D11,Sheet1!F11:G11)</f>
+        <v>120367436686.89662</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A12," ",Sheet1!B12)</f>
         <v>Jackie Velasquez</v>
       </c>
-      <c r="B12" s="2" t="str">
+      <c r="B12" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A12, " (",Sheet1!H12,")")</f>
         <v>Jackie (Technical Support)</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="9">
         <f>SUM(Sheet1!D12:G12)</f>
         <v>17223.73</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="9">
         <f>AVERAGE(Sheet1!D12:G12)</f>
         <v>4305.9324999999999</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="9">
         <f>MEDIAN(Sheet1!D12:F12,Sheet1!G12)</f>
         <v>3900.2999999999997</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="10">
         <f>STDEV(Sheet1!D12:G12)</f>
         <v>1451.4359064130263</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="str">
+      <c r="G12" s="9">
+        <f>PRODUCT(Sheet1!D12,Sheet1!F12:G12)</f>
+        <v>92045222022.270508</v>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A13," ",Sheet1!B13)</f>
         <v>Alan Barton</v>
       </c>
-      <c r="B13" s="2" t="str">
+      <c r="B13" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A13, " (",Sheet1!H13,")")</f>
         <v>Alan (Cloud Engineer)</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="9">
         <f>SUM(Sheet1!D13:G13)</f>
         <v>19073.71</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="9">
         <f>AVERAGE(Sheet1!D13:G13)</f>
         <v>4768.4274999999998</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="9">
         <f>MEDIAN(Sheet1!D13:F13,Sheet1!G13)</f>
         <v>4712.0300000000007</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="10">
         <f>STDEV(Sheet1!D13:G13)</f>
         <v>561.4052111368992</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="str">
+      <c r="G13" s="9">
+        <f>PRODUCT(Sheet1!D13,Sheet1!F13:G13)</f>
+        <v>103627345702.87041</v>
+      </c>
+      <c r="H13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A14," ",Sheet1!B14)</f>
         <v>Leslie Leon</v>
       </c>
-      <c r="B14" s="2" t="str">
+      <c r="B14" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A14, " (",Sheet1!H14,")")</f>
         <v>Leslie (Data Scientist)</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="9">
         <f>SUM(Sheet1!D14:G14)</f>
         <v>20880.230000000003</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="9">
         <f>AVERAGE(Sheet1!D14:G14)</f>
         <v>5220.0575000000008</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="9">
         <f>MEDIAN(Sheet1!D14:F14,Sheet1!G14)</f>
         <v>5332.3250000000007</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="10">
         <f>STDEV(Sheet1!D14:G14)</f>
         <v>1131.6725805159615</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="str">
+      <c r="G14" s="9">
+        <f>PRODUCT(Sheet1!D14,Sheet1!F14:G14)</f>
+        <v>124110078261.20549</v>
+      </c>
+      <c r="H14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A15," ",Sheet1!B15)</f>
         <v>Ruben Chang</v>
       </c>
-      <c r="B15" s="2" t="str">
+      <c r="B15" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A15, " (",Sheet1!H15,")")</f>
         <v>Ruben (Business Analyst)</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="9">
         <f>SUM(Sheet1!D15:G15)</f>
         <v>20198.150000000001</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="9">
         <f>AVERAGE(Sheet1!D15:G15)</f>
         <v>5049.5375000000004</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="9">
         <f>MEDIAN(Sheet1!D15:F15,Sheet1!G15)</f>
         <v>5096.8850000000002</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="10">
         <f>STDEV(Sheet1!D15:G15)</f>
         <v>1600.0705218078108</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="str">
+      <c r="G15" s="9">
+        <f>PRODUCT(Sheet1!D15,Sheet1!F15:G15)</f>
+        <v>80213777587.854767</v>
+      </c>
+      <c r="H15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A16," ",Sheet1!B16)</f>
         <v>Kristine Myers</v>
       </c>
-      <c r="B16" s="2" t="str">
+      <c r="B16" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A16, " (",Sheet1!H16,")")</f>
         <v>Kristine (Product Manager)</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="9">
         <f>SUM(Sheet1!D16:G16)</f>
         <v>18639.140000000003</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="9">
         <f>AVERAGE(Sheet1!D16:G16)</f>
         <v>4659.7850000000008</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="9">
         <f>MEDIAN(Sheet1!D16:F16,Sheet1!G16)</f>
         <v>4450.8450000000003</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="10">
         <f>STDEV(Sheet1!D16:G16)</f>
         <v>1826.3813481764034</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="str">
+      <c r="G16" s="9">
+        <f>PRODUCT(Sheet1!D16,Sheet1!F16:G16)</f>
+        <v>64316747311.785149</v>
+      </c>
+      <c r="H16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A17," ",Sheet1!B17)</f>
         <v>Stanley Cannon</v>
       </c>
-      <c r="B17" s="2" t="str">
+      <c r="B17" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A17, " (",Sheet1!H17,")")</f>
         <v>Stanley (Mobile App Developer)</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="9">
         <f>SUM(Sheet1!D17:G17)</f>
         <v>19397.739999999998</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="9">
         <f>AVERAGE(Sheet1!D17:G17)</f>
         <v>4849.4349999999995</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="9">
         <f>MEDIAN(Sheet1!D17:F17,Sheet1!G17)</f>
         <v>4447.9799999999996</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="10">
         <f>STDEV(Sheet1!D17:G17)</f>
         <v>1157.5710365099294</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="str">
+      <c r="G17" s="9">
+        <f>PRODUCT(Sheet1!D17,Sheet1!F17:G17)</f>
+        <v>129420325465.51807</v>
+      </c>
+      <c r="H17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A18," ",Sheet1!B18)</f>
         <v>Derek Stanley</v>
       </c>
-      <c r="B18" s="2" t="str">
+      <c r="B18" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A18, " (",Sheet1!H18,")")</f>
         <v>Derek (Backend Developer)</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="9">
         <f>SUM(Sheet1!D18:G18)</f>
         <v>21824.71</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="9">
         <f>AVERAGE(Sheet1!D18:G18)</f>
         <v>5456.1774999999998</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="9">
         <f>MEDIAN(Sheet1!D18:F18,Sheet1!G18)</f>
         <v>5436.165</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="10">
         <f>STDEV(Sheet1!D18:G18)</f>
         <v>968.5732299065819</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="str">
+      <c r="G18" s="9">
+        <f>PRODUCT(Sheet1!D18,Sheet1!F18:G18)</f>
+        <v>183358561081.89267</v>
+      </c>
+      <c r="H18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A19," ",Sheet1!B19)</f>
         <v>Kevin Edwards</v>
       </c>
-      <c r="B19" s="2" t="str">
+      <c r="B19" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A19, " (",Sheet1!H19,")")</f>
         <v>Kevin (DevOps Engineer)</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="9">
         <f>SUM(Sheet1!D19:G19)</f>
         <v>18426.02</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="9">
         <f>AVERAGE(Sheet1!D19:G19)</f>
         <v>4606.5050000000001</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="9">
         <f>MEDIAN(Sheet1!D19:F19,Sheet1!G19)</f>
         <v>4403.5450000000001</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="10">
         <f>STDEV(Sheet1!D19:G19)</f>
         <v>713.64658940308993</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="str">
+      <c r="G19" s="9">
+        <f>PRODUCT(Sheet1!D19,Sheet1!F19:G19)</f>
+        <v>99125739732.658188</v>
+      </c>
+      <c r="H19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A20," ",Sheet1!B20)</f>
         <v>George Sanchez</v>
       </c>
-      <c r="B20" s="2" t="str">
+      <c r="B20" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A20, " (",Sheet1!H20,")")</f>
         <v>George (Frontend Developer)</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="9">
         <f>SUM(Sheet1!D20:G20)</f>
         <v>22764.21</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="9">
         <f>AVERAGE(Sheet1!D20:G20)</f>
         <v>5691.0524999999998</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="9">
         <f>MEDIAN(Sheet1!D20:F20,Sheet1!G20)</f>
         <v>6265.1</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="10">
         <f>STDEV(Sheet1!D20:G20)</f>
         <v>1344.8458723679091</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="str">
+      <c r="G20" s="9">
+        <f>PRODUCT(Sheet1!D20,Sheet1!F20:G20)</f>
+        <v>155517713008.32782</v>
+      </c>
+      <c r="H20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A21," ",Sheet1!B21)</f>
         <v>Amy Mason</v>
       </c>
-      <c r="B21" s="2" t="str">
+      <c r="B21" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A21, " (",Sheet1!H21,")")</f>
         <v>Amy (DevOps Engineer)</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="9">
         <f>SUM(Sheet1!D21:G21)</f>
         <v>24016.58</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="9">
         <f>AVERAGE(Sheet1!D21:G21)</f>
         <v>6004.1450000000004</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="9">
         <f>MEDIAN(Sheet1!D21:F21,Sheet1!G21)</f>
         <v>6666.5</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="10">
         <f>STDEV(Sheet1!D21:G21)</f>
         <v>1525.4829684507556</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="str">
+      <c r="G21" s="9">
+        <f>PRODUCT(Sheet1!D21,Sheet1!F21:G21)</f>
+        <v>165968888894.27213</v>
+      </c>
+      <c r="H21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A22," ",Sheet1!B22)</f>
         <v>Natalie Bryant</v>
       </c>
-      <c r="B22" s="2" t="str">
+      <c r="B22" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A22, " (",Sheet1!H22,")")</f>
         <v>Natalie (UI/UX Designer)</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="9">
         <f>SUM(Sheet1!D22:G22)</f>
         <v>22008.39</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="9">
         <f>AVERAGE(Sheet1!D22:G22)</f>
         <v>5502.0974999999999</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="9">
         <f>MEDIAN(Sheet1!D22:F22,Sheet1!G22)</f>
         <v>5659.01</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="10">
         <f>STDEV(Sheet1!D22:G22)</f>
         <v>1137.8845285404286</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="str">
+      <c r="G22" s="9">
+        <f>PRODUCT(Sheet1!D22,Sheet1!F22:G22)</f>
+        <v>146461600787.33304</v>
+      </c>
+      <c r="H22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A23," ",Sheet1!B23)</f>
         <v>Amy Mercer</v>
       </c>
-      <c r="B23" s="2" t="str">
+      <c r="B23" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A23, " (",Sheet1!H23,")")</f>
         <v>Amy (Scrum Master)</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="9">
         <f>SUM(Sheet1!D23:G23)</f>
         <v>20493.810000000001</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="9">
         <f>AVERAGE(Sheet1!D23:G23)</f>
         <v>5123.4525000000003</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="9">
         <f>MEDIAN(Sheet1!D23:F23,Sheet1!G23)</f>
         <v>5027.5650000000005</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="10">
         <f>STDEV(Sheet1!D23:G23)</f>
         <v>547.97091007795893</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="str">
+      <c r="G23" s="9">
+        <f>PRODUCT(Sheet1!D23,Sheet1!F23:G23)</f>
+        <v>147458259612.07111</v>
+      </c>
+      <c r="H23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A24," ",Sheet1!B24)</f>
         <v>Matthew Garza</v>
       </c>
-      <c r="B24" s="2" t="str">
+      <c r="B24" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A24, " (",Sheet1!H24,")")</f>
         <v>Matthew (Software Engineer)</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="9">
         <f>SUM(Sheet1!D24:G24)</f>
         <v>16724.97</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="9">
         <f>AVERAGE(Sheet1!D24:G24)</f>
         <v>4181.2425000000003</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="9">
         <f>MEDIAN(Sheet1!D24:F24,Sheet1!G24)</f>
         <v>4479.17</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="10">
         <f>STDEV(Sheet1!D24:G24)</f>
         <v>733.65308156625622</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="str">
+      <c r="G24" s="9">
+        <f>PRODUCT(Sheet1!D24,Sheet1!F24:G24)</f>
+        <v>93739035957.534073</v>
+      </c>
+      <c r="H24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A25," ",Sheet1!B25)</f>
         <v>Theodore Wright</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B25" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A25, " (",Sheet1!H25,")")</f>
         <v>Theodore (Frontend Developer)</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="9">
         <f>SUM(Sheet1!D25:G25)</f>
         <v>21774.05</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="9">
         <f>AVERAGE(Sheet1!D25:G25)</f>
         <v>5443.5124999999998</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="9">
         <f>MEDIAN(Sheet1!D25:F25,Sheet1!G25)</f>
         <v>5295.75</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="10">
         <f>STDEV(Sheet1!D25:G25)</f>
         <v>1384.0697617864726</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="str">
+      <c r="G25" s="9">
+        <f>PRODUCT(Sheet1!D25,Sheet1!F25:G25)</f>
+        <v>126773526660.61113</v>
+      </c>
+      <c r="H25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A26," ",Sheet1!B26)</f>
         <v>Kayla West</v>
       </c>
-      <c r="B26" s="2" t="str">
+      <c r="B26" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A26, " (",Sheet1!H26,")")</f>
         <v>Kayla (Mobile App Developer)</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="9">
         <f>SUM(Sheet1!D26:G26)</f>
         <v>14105.11</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="9">
         <f>AVERAGE(Sheet1!D26:G26)</f>
         <v>3526.2775000000001</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="9">
         <f>MEDIAN(Sheet1!D26:F26,Sheet1!G26)</f>
         <v>3577.7</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="10">
         <f>STDEV(Sheet1!D26:G26)</f>
         <v>374.17851651985598</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="str">
+      <c r="G26" s="9">
+        <f>PRODUCT(Sheet1!D26,Sheet1!F26:G26)</f>
+        <v>49787488719.748901</v>
+      </c>
+      <c r="H26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A27," ",Sheet1!B27)</f>
         <v>Jesse Carter</v>
       </c>
-      <c r="B27" s="2" t="str">
+      <c r="B27" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A27, " (",Sheet1!H27,")")</f>
         <v>Jesse (QA Engineer)</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="9">
         <f>SUM(Sheet1!D27:G27)</f>
         <v>20233.919999999998</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="9">
         <f>AVERAGE(Sheet1!D27:G27)</f>
         <v>5058.4799999999996</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="9">
         <f>MEDIAN(Sheet1!D27:F27,Sheet1!G27)</f>
         <v>5011.4549999999999</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="10">
         <f>STDEV(Sheet1!D27:G27)</f>
         <v>1304.2718354954509</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="str">
+      <c r="G27" s="9">
+        <f>PRODUCT(Sheet1!D27,Sheet1!F27:G27)</f>
+        <v>112902533972.24257</v>
+      </c>
+      <c r="H27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A28," ",Sheet1!B28)</f>
         <v>Carlos Vega</v>
       </c>
-      <c r="B28" s="2" t="str">
+      <c r="B28" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A28, " (",Sheet1!H28,")")</f>
         <v>Carlos (Technical Support)</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="9">
         <f>SUM(Sheet1!D28:G28)</f>
         <v>17441.5</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="9">
         <f>AVERAGE(Sheet1!D28:G28)</f>
         <v>4360.375</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="9">
         <f>MEDIAN(Sheet1!D28:F28,Sheet1!G28)</f>
         <v>4136.25</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="10">
         <f>STDEV(Sheet1!D28:G28)</f>
         <v>855.06618958222452</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="str">
+      <c r="G28" s="9">
+        <f>PRODUCT(Sheet1!D28,Sheet1!F28:G28)</f>
+        <v>94430736121.629593</v>
+      </c>
+      <c r="H28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A29," ",Sheet1!B29)</f>
         <v>Bridget Keith</v>
       </c>
-      <c r="B29" s="2" t="str">
+      <c r="B29" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A29, " (",Sheet1!H29,")")</f>
         <v>Bridget (UI/UX Designer)</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="9">
         <f>SUM(Sheet1!D29:G29)</f>
         <v>18843.07</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="9">
         <f>AVERAGE(Sheet1!D29:G29)</f>
         <v>4710.7674999999999</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="9">
         <f>MEDIAN(Sheet1!D29:F29,Sheet1!G29)</f>
         <v>4224.9949999999999</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="10">
         <f>STDEV(Sheet1!D29:G29)</f>
         <v>1519.7799713856623</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="str">
+      <c r="G29" s="9">
+        <f>PRODUCT(Sheet1!D29,Sheet1!F29:G29)</f>
+        <v>92860492703.391556</v>
+      </c>
+      <c r="H29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A30," ",Sheet1!B30)</f>
         <v>William Duncan</v>
       </c>
-      <c r="B30" s="2" t="str">
+      <c r="B30" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A30, " (",Sheet1!H30,")")</f>
         <v>William (Security Analyst)</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="9">
         <f>SUM(Sheet1!D30:G30)</f>
         <v>18384.02</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="9">
         <f>AVERAGE(Sheet1!D30:G30)</f>
         <v>4596.0050000000001</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="9">
         <f>MEDIAN(Sheet1!D30:F30,Sheet1!G30)</f>
         <v>4342.2350000000006</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="10">
         <f>STDEV(Sheet1!D30:G30)</f>
         <v>1538.4899608923899</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="str">
+      <c r="G30" s="9">
+        <f>PRODUCT(Sheet1!D30,Sheet1!F30:G30)</f>
+        <v>70240152244.86557</v>
+      </c>
+      <c r="H30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A31," ",Sheet1!B31)</f>
         <v>John Hernandez</v>
       </c>
-      <c r="B31" s="2" t="str">
+      <c r="B31" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A31, " (",Sheet1!H31,")")</f>
         <v>John (UI/UX Designer)</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="9">
         <f>SUM(Sheet1!D31:G31)</f>
         <v>15916.75</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="9">
         <f>AVERAGE(Sheet1!D31:G31)</f>
         <v>3979.1875</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="9">
         <f>MEDIAN(Sheet1!D31:F31,Sheet1!G31)</f>
         <v>4064.09</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="10">
         <f>STDEV(Sheet1!D31:G31)</f>
         <v>706.83200726316159</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="str">
+      <c r="G31" s="9">
+        <f>PRODUCT(Sheet1!D31,Sheet1!F31:G31)</f>
+        <v>50275890927.047287</v>
+      </c>
+      <c r="H31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A32," ",Sheet1!B32)</f>
         <v>Jesse Murray</v>
       </c>
-      <c r="B32" s="2" t="str">
+      <c r="B32" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A32, " (",Sheet1!H32,")")</f>
         <v>Jesse (Security Analyst)</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="9">
         <f>SUM(Sheet1!D32:G32)</f>
         <v>18740.980000000003</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="9">
         <f>AVERAGE(Sheet1!D32:G32)</f>
         <v>4685.2450000000008</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="9">
         <f>MEDIAN(Sheet1!D32:F32,Sheet1!G32)</f>
         <v>4510.5300000000007</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="10">
         <f>STDEV(Sheet1!D32:G32)</f>
         <v>1679.5520275259892</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="str">
+      <c r="G32" s="9">
+        <f>PRODUCT(Sheet1!D32,Sheet1!F32:G32)</f>
+        <v>111367491422.6749</v>
+      </c>
+      <c r="H32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A33," ",Sheet1!B33)</f>
         <v>Stephen Haynes</v>
       </c>
-      <c r="B33" s="2" t="str">
+      <c r="B33" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A33, " (",Sheet1!H33,")")</f>
         <v>Stephen (Technical Support)</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="9">
         <f>SUM(Sheet1!D33:G33)</f>
         <v>20347.879999999997</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="9">
         <f>AVERAGE(Sheet1!D33:G33)</f>
         <v>5086.9699999999993</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="9">
         <f>MEDIAN(Sheet1!D33:F33,Sheet1!G33)</f>
         <v>5137.9650000000001</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="10">
         <f>STDEV(Sheet1!D33:G33)</f>
         <v>2070.2973758536878</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="str">
+      <c r="G33" s="9">
+        <f>PRODUCT(Sheet1!D33,Sheet1!F33:G33)</f>
+        <v>76005189473.290848</v>
+      </c>
+      <c r="H33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A34," ",Sheet1!B34)</f>
         <v>Samuel Smith</v>
       </c>
-      <c r="B34" s="2" t="str">
+      <c r="B34" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A34, " (",Sheet1!H34,")")</f>
         <v>Samuel (System Administrator)</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="9">
         <f>SUM(Sheet1!D34:G34)</f>
         <v>18052.490000000002</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="9">
         <f>AVERAGE(Sheet1!D34:G34)</f>
         <v>4513.1225000000004</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="9">
         <f>MEDIAN(Sheet1!D34:F34,Sheet1!G34)</f>
         <v>4648.24</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="10">
         <f>STDEV(Sheet1!D34:G34)</f>
         <v>1069.434287785677</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="str">
+      <c r="G34" s="9">
+        <f>PRODUCT(Sheet1!D34,Sheet1!F34:G34)</f>
+        <v>68690336616.366364</v>
+      </c>
+      <c r="H34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A35," ",Sheet1!B35)</f>
         <v>Russell Moore</v>
       </c>
-      <c r="B35" s="2" t="str">
+      <c r="B35" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A35, " (",Sheet1!H35,")")</f>
         <v>Russell (Full Stack Developer)</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="9">
         <f>SUM(Sheet1!D35:G35)</f>
         <v>18526.12</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="9">
         <f>AVERAGE(Sheet1!D35:G35)</f>
         <v>4631.53</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="9">
         <f>MEDIAN(Sheet1!D35:F35,Sheet1!G35)</f>
         <v>4393.3999999999996</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="10">
         <f>STDEV(Sheet1!D35:G35)</f>
         <v>1087.8079752725971</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="str">
+      <c r="G35" s="9">
+        <f>PRODUCT(Sheet1!D35,Sheet1!F35:G35)</f>
+        <v>85087773454.95694</v>
+      </c>
+      <c r="H35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A36," ",Sheet1!B36)</f>
         <v>Brenda Delgado</v>
       </c>
-      <c r="B36" s="2" t="str">
+      <c r="B36" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A36, " (",Sheet1!H36,")")</f>
         <v>Brenda (Business Analyst)</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="9">
         <f>SUM(Sheet1!D36:G36)</f>
         <v>17212.75</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="9">
         <f>AVERAGE(Sheet1!D36:G36)</f>
         <v>4303.1875</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="9">
         <f>MEDIAN(Sheet1!D36:F36,Sheet1!G36)</f>
         <v>4527.6350000000002</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="10">
         <f>STDEV(Sheet1!D36:G36)</f>
         <v>861.28250074622201</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="str">
+      <c r="G36" s="9">
+        <f>PRODUCT(Sheet1!D36,Sheet1!F36:G36)</f>
+        <v>103003129353.65613</v>
+      </c>
+      <c r="H36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A37," ",Sheet1!B37)</f>
         <v>Lindsey Kline</v>
       </c>
-      <c r="B37" s="2" t="str">
+      <c r="B37" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A37, " (",Sheet1!H37,")")</f>
         <v>Lindsey (Scrum Master)</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="9">
         <f>SUM(Sheet1!D37:G37)</f>
         <v>18057.39</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="9">
         <f>AVERAGE(Sheet1!D37:G37)</f>
         <v>4514.3474999999999</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="9">
         <f>MEDIAN(Sheet1!D37:F37,Sheet1!G37)</f>
         <v>4124.8950000000004</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="10">
         <f>STDEV(Sheet1!D37:G37)</f>
         <v>1695.1464024556487</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="str">
+      <c r="G37" s="9">
+        <f>PRODUCT(Sheet1!D37,Sheet1!F37:G37)</f>
+        <v>104296013508.78088</v>
+      </c>
+      <c r="H37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A38," ",Sheet1!B38)</f>
         <v>Shelia Sanchez</v>
       </c>
-      <c r="B38" s="2" t="str">
+      <c r="B38" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A38, " (",Sheet1!H38,")")</f>
         <v>Shelia (Software Engineer)</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="9">
         <f>SUM(Sheet1!D38:G38)</f>
         <v>20384.18</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="9">
         <f>AVERAGE(Sheet1!D38:G38)</f>
         <v>5096.0450000000001</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="9">
         <f>MEDIAN(Sheet1!D38:F38,Sheet1!G38)</f>
         <v>4864.1549999999997</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="10">
         <f>STDEV(Sheet1!D38:G38)</f>
         <v>1540.3343826260568</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="str">
+      <c r="G38" s="9">
+        <f>PRODUCT(Sheet1!D38,Sheet1!F38:G38)</f>
+        <v>100175530665.01782</v>
+      </c>
+      <c r="H38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A39," ",Sheet1!B39)</f>
         <v>Holly Christensen</v>
       </c>
-      <c r="B39" s="2" t="str">
+      <c r="B39" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A39, " (",Sheet1!H39,")")</f>
         <v>Holly (Technical Support)</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="9">
         <f>SUM(Sheet1!D39:G39)</f>
         <v>21184.25</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="9">
         <f>AVERAGE(Sheet1!D39:G39)</f>
         <v>5296.0625</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="9">
         <f>MEDIAN(Sheet1!D39:F39,Sheet1!G39)</f>
         <v>5232</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="10">
         <f>STDEV(Sheet1!D39:G39)</f>
         <v>1067.8809072605738</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="str">
+      <c r="G39" s="9">
+        <f>PRODUCT(Sheet1!D39,Sheet1!F39:G39)</f>
+        <v>181642058416.75967</v>
+      </c>
+      <c r="H39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A40," ",Sheet1!B40)</f>
         <v>Jason Johnson</v>
       </c>
-      <c r="B40" s="2" t="str">
+      <c r="B40" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A40, " (",Sheet1!H40,")")</f>
         <v>Jason (Frontend Developer)</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="9">
         <f>SUM(Sheet1!D40:G40)</f>
         <v>19594.850000000002</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="9">
         <f>AVERAGE(Sheet1!D40:G40)</f>
         <v>4898.7125000000005</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="9">
         <f>MEDIAN(Sheet1!D40:F40,Sheet1!G40)</f>
         <v>4757.7700000000004</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="10">
         <f>STDEV(Sheet1!D40:G40)</f>
         <v>748.48175080736246</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="str">
+      <c r="G40" s="9">
+        <f>PRODUCT(Sheet1!D40,Sheet1!F40:G40)</f>
+        <v>95383513583.054611</v>
+      </c>
+      <c r="H40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A41," ",Sheet1!B41)</f>
         <v>Melissa Garcia</v>
       </c>
-      <c r="B41" s="2" t="str">
+      <c r="B41" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A41, " (",Sheet1!H41,")")</f>
         <v>Melissa (Frontend Developer)</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="9">
         <f>SUM(Sheet1!D41:G41)</f>
         <v>18702.18</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="9">
         <f>AVERAGE(Sheet1!D41:G41)</f>
         <v>4675.5450000000001</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="9">
         <f>MEDIAN(Sheet1!D41:F41,Sheet1!G41)</f>
         <v>4616.6750000000002</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="10">
         <f>STDEV(Sheet1!D41:G41)</f>
         <v>1006.9539666571977</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="str">
+      <c r="G41" s="9">
+        <f>PRODUCT(Sheet1!D41,Sheet1!F41:G41)</f>
+        <v>115557249581.30246</v>
+      </c>
+      <c r="H41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A42," ",Sheet1!B42)</f>
         <v>Amanda Hayes</v>
       </c>
-      <c r="B42" s="2" t="str">
+      <c r="B42" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A42, " (",Sheet1!H42,")")</f>
         <v>Amanda (Software Engineer)</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="9">
         <f>SUM(Sheet1!D42:G42)</f>
         <v>18176.54</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="9">
         <f>AVERAGE(Sheet1!D42:G42)</f>
         <v>4544.1350000000002</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="9">
         <f>MEDIAN(Sheet1!D42:F42,Sheet1!G42)</f>
         <v>4316.99</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="10">
         <f>STDEV(Sheet1!D42:G42)</f>
         <v>1045.0258708280862</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="str">
+      <c r="G42" s="9">
+        <f>PRODUCT(Sheet1!D42,Sheet1!F42:G42)</f>
+        <v>66134319202.563507</v>
+      </c>
+      <c r="H42" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A43," ",Sheet1!B43)</f>
         <v>Abigail Wright</v>
       </c>
-      <c r="B43" s="2" t="str">
+      <c r="B43" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A43, " (",Sheet1!H43,")")</f>
         <v>Abigail (Scrum Master)</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="9">
         <f>SUM(Sheet1!D43:G43)</f>
         <v>24252.629999999997</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="9">
         <f>AVERAGE(Sheet1!D43:G43)</f>
         <v>6063.1574999999993</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="9">
         <f>MEDIAN(Sheet1!D43:F43,Sheet1!G43)</f>
         <v>6148.6299999999992</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="10">
         <f>STDEV(Sheet1!D43:G43)</f>
         <v>538.28865009862488</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="str">
+      <c r="G43" s="9">
+        <f>PRODUCT(Sheet1!D43,Sheet1!F43:G43)</f>
+        <v>202739188049.12485</v>
+      </c>
+      <c r="H43" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A44," ",Sheet1!B44)</f>
         <v>Deborah Warren</v>
       </c>
-      <c r="B44" s="2" t="str">
+      <c r="B44" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A44, " (",Sheet1!H44,")")</f>
         <v>Deborah (Frontend Developer)</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="9">
         <f>SUM(Sheet1!D44:G44)</f>
         <v>21204.370000000003</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="9">
         <f>AVERAGE(Sheet1!D44:G44)</f>
         <v>5301.0925000000007</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="9">
         <f>MEDIAN(Sheet1!D44:F44,Sheet1!G44)</f>
         <v>5176.9400000000005</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="10">
         <f>STDEV(Sheet1!D44:G44)</f>
         <v>1203.3860243046106</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="str">
+      <c r="G44" s="9">
+        <f>PRODUCT(Sheet1!D44,Sheet1!F44:G44)</f>
+        <v>174873133677.57263</v>
+      </c>
+      <c r="H44" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A45," ",Sheet1!B45)</f>
         <v>Megan Mullins</v>
       </c>
-      <c r="B45" s="2" t="str">
+      <c r="B45" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A45, " (",Sheet1!H45,")")</f>
         <v>Megan (System Administrator)</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="9">
         <f>SUM(Sheet1!D45:G45)</f>
         <v>19659.090000000004</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="9">
         <f>AVERAGE(Sheet1!D45:G45)</f>
         <v>4914.7725000000009</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="9">
         <f>MEDIAN(Sheet1!D45:F45,Sheet1!G45)</f>
         <v>4765.6900000000005</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="10">
         <f>STDEV(Sheet1!D45:G45)</f>
         <v>1224.2083787867391</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="str">
+      <c r="G45" s="9">
+        <f>PRODUCT(Sheet1!D45,Sheet1!F45:G45)</f>
+        <v>106737019199.38828</v>
+      </c>
+      <c r="H45" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A46," ",Sheet1!B46)</f>
         <v>Lynn Diaz</v>
       </c>
-      <c r="B46" s="2" t="str">
+      <c r="B46" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A46, " (",Sheet1!H46,")")</f>
         <v>Lynn (Mobile App Developer)</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="9">
         <f>SUM(Sheet1!D46:G46)</f>
         <v>18686.379999999997</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="9">
         <f>AVERAGE(Sheet1!D46:G46)</f>
         <v>4671.5949999999993</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="9">
         <f>MEDIAN(Sheet1!D46:F46,Sheet1!G46)</f>
         <v>4463.1149999999998</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="10">
         <f>STDEV(Sheet1!D46:G46)</f>
         <v>1472.7776651506738</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="str">
+      <c r="G46" s="9">
+        <f>PRODUCT(Sheet1!D46,Sheet1!F46:G46)</f>
+        <v>128946644828.8494</v>
+      </c>
+      <c r="H46" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A47," ",Sheet1!B47)</f>
         <v>Suzanne Robbins</v>
       </c>
-      <c r="B47" s="2" t="str">
+      <c r="B47" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A47, " (",Sheet1!H47,")")</f>
         <v>Suzanne (Data Scientist)</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="9">
         <f>SUM(Sheet1!D47:G47)</f>
         <v>22555.739999999998</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="9">
         <f>AVERAGE(Sheet1!D47:G47)</f>
         <v>5638.9349999999995</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="9">
         <f>MEDIAN(Sheet1!D47:F47,Sheet1!G47)</f>
         <v>5605.87</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="10">
         <f>STDEV(Sheet1!D47:G47)</f>
         <v>466.24504962519467</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="str">
+      <c r="G47" s="9">
+        <f>PRODUCT(Sheet1!D47,Sheet1!F47:G47)</f>
+        <v>161034640803.93109</v>
+      </c>
+      <c r="H47" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A48," ",Sheet1!B48)</f>
         <v>Michelle Goodman</v>
       </c>
-      <c r="B48" s="2" t="str">
+      <c r="B48" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A48, " (",Sheet1!H48,")")</f>
         <v>Michelle (System Administrator)</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="9">
         <f>SUM(Sheet1!D48:G48)</f>
         <v>23021.87</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="9">
         <f>AVERAGE(Sheet1!D48:G48)</f>
         <v>5755.4674999999997</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="9">
         <f>MEDIAN(Sheet1!D48:F48,Sheet1!G48)</f>
         <v>6104.77</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="10">
         <f>STDEV(Sheet1!D48:G48)</f>
         <v>1245.4776305598587</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="str">
+      <c r="G48" s="9">
+        <f>PRODUCT(Sheet1!D48,Sheet1!F48:G48)</f>
+        <v>249717821655.48135</v>
+      </c>
+      <c r="H48" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A49," ",Sheet1!B49)</f>
         <v>Elizabeth Richards</v>
       </c>
-      <c r="B49" s="2" t="str">
+      <c r="B49" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A49, " (",Sheet1!H49,")")</f>
         <v>Elizabeth (Mobile App Developer)</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="9">
         <f>SUM(Sheet1!D49:G49)</f>
         <v>19871.43</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="9">
         <f>AVERAGE(Sheet1!D49:G49)</f>
         <v>4967.8575000000001</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="9">
         <f>MEDIAN(Sheet1!D49:F49,Sheet1!G49)</f>
         <v>4922.0349999999999</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="10">
         <f>STDEV(Sheet1!D49:G49)</f>
         <v>1805.9322798557537</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="str">
+      <c r="G49" s="9">
+        <f>PRODUCT(Sheet1!D49,Sheet1!F49:G49)</f>
+        <v>77273871180.187515</v>
+      </c>
+      <c r="H49" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A50," ",Sheet1!B50)</f>
         <v>Jeffrey Miller</v>
       </c>
-      <c r="B50" s="2" t="str">
+      <c r="B50" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A50, " (",Sheet1!H50,")")</f>
         <v>Jeffrey (QA Engineer)</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="9">
         <f>SUM(Sheet1!D50:G50)</f>
         <v>16669.78</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="9">
         <f>AVERAGE(Sheet1!D50:G50)</f>
         <v>4167.4449999999997</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="9">
         <f>MEDIAN(Sheet1!D50:F50,Sheet1!G50)</f>
         <v>4459.125</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="10">
         <f>STDEV(Sheet1!D50:G50)</f>
         <v>662.541268676909</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="str">
+      <c r="G50" s="9">
+        <f>PRODUCT(Sheet1!D50,Sheet1!F50:G50)</f>
+        <v>90952122667.10614</v>
+      </c>
+      <c r="H50" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A51," ",Sheet1!B51)</f>
         <v>Catherine Welch</v>
       </c>
-      <c r="B51" s="2" t="str">
+      <c r="B51" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A51, " (",Sheet1!H51,")")</f>
         <v>Catherine (Product Manager)</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="9">
         <f>SUM(Sheet1!D51:G51)</f>
         <v>21733.079999999998</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="9">
         <f>AVERAGE(Sheet1!D51:G51)</f>
         <v>5433.2699999999995</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="9">
         <f>MEDIAN(Sheet1!D51:F51,Sheet1!G51)</f>
         <v>5708.68</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="10">
         <f>STDEV(Sheet1!D51:G51)</f>
         <v>1404.8083472369722</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="str">
+      <c r="G51" s="9">
+        <f>PRODUCT(Sheet1!D51,Sheet1!F51:G51)</f>
+        <v>214977580537.83859</v>
+      </c>
+      <c r="H51" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A52," ",Sheet1!B52)</f>
         <v>Nicholas Nelson</v>
       </c>
-      <c r="B52" s="2" t="str">
+      <c r="B52" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A52, " (",Sheet1!H52,")")</f>
         <v>Nicholas (DevOps Engineer)</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="9">
         <f>SUM(Sheet1!D52:G52)</f>
         <v>20662.669999999998</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="9">
         <f>AVERAGE(Sheet1!D52:G52)</f>
         <v>5165.6674999999996</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="9">
         <f>MEDIAN(Sheet1!D52:F52,Sheet1!G52)</f>
         <v>4970.2999999999993</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="10">
         <f>STDEV(Sheet1!D52:G52)</f>
         <v>1270.4741508947243</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="str">
+      <c r="G52" s="9">
+        <f>PRODUCT(Sheet1!D52,Sheet1!F52:G52)</f>
+        <v>120864070328.31143</v>
+      </c>
+      <c r="H52" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A53," ",Sheet1!B53)</f>
         <v>James Diaz</v>
       </c>
-      <c r="B53" s="2" t="str">
+      <c r="B53" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A53, " (",Sheet1!H53,")")</f>
         <v>James (Data Scientist)</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="9">
         <f>SUM(Sheet1!D53:G53)</f>
         <v>22507.42</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="9">
         <f>AVERAGE(Sheet1!D53:G53)</f>
         <v>5626.8549999999996</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="9">
         <f>MEDIAN(Sheet1!D53:F53,Sheet1!G53)</f>
         <v>5606.3249999999998</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="10">
         <f>STDEV(Sheet1!D53:G53)</f>
         <v>1198.1333971501972</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="str">
+      <c r="G53" s="9">
+        <f>PRODUCT(Sheet1!D53,Sheet1!F53:G53)</f>
+        <v>214333731457.7637</v>
+      </c>
+      <c r="H53" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A54," ",Sheet1!B54)</f>
         <v>Lori Evans</v>
       </c>
-      <c r="B54" s="2" t="str">
+      <c r="B54" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A54, " (",Sheet1!H54,")")</f>
         <v>Lori (Technical Support)</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="9">
         <f>SUM(Sheet1!D54:G54)</f>
         <v>19224.239999999998</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="9">
         <f>AVERAGE(Sheet1!D54:G54)</f>
         <v>4806.0599999999995</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="9">
         <f>MEDIAN(Sheet1!D54:F54,Sheet1!G54)</f>
         <v>4594.3999999999996</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="10">
         <f>STDEV(Sheet1!D54:G54)</f>
         <v>1043.4307881535187</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="str">
+      <c r="G54" s="9">
+        <f>PRODUCT(Sheet1!D54,Sheet1!F54:G54)</f>
+        <v>79763929709.800705</v>
+      </c>
+      <c r="H54" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A55," ",Sheet1!B55)</f>
         <v>Zachary Lopez</v>
       </c>
-      <c r="B55" s="2" t="str">
+      <c r="B55" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A55, " (",Sheet1!H55,")")</f>
         <v>Zachary (System Administrator)</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="9">
         <f>SUM(Sheet1!D55:G55)</f>
         <v>23228.14</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="9">
         <f>AVERAGE(Sheet1!D55:G55)</f>
         <v>5807.0349999999999</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="9">
         <f>MEDIAN(Sheet1!D55:F55,Sheet1!G55)</f>
         <v>5764.0450000000001</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="10">
         <f>STDEV(Sheet1!D55:G55)</f>
         <v>561.05101458482966</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="str">
+      <c r="G55" s="9">
+        <f>PRODUCT(Sheet1!D55,Sheet1!F55:G55)</f>
+        <v>213121017852.15479</v>
+      </c>
+      <c r="H55" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A56," ",Sheet1!B56)</f>
         <v>Michael Gray</v>
       </c>
-      <c r="B56" s="2" t="str">
+      <c r="B56" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A56, " (",Sheet1!H56,")")</f>
         <v>Michael (Full Stack Developer)</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="9">
         <f>SUM(Sheet1!D56:G56)</f>
         <v>21206.22</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="9">
         <f>AVERAGE(Sheet1!D56:G56)</f>
         <v>5301.5550000000003</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="9">
         <f>MEDIAN(Sheet1!D56:F56,Sheet1!G56)</f>
         <v>5829.6749999999993</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="10">
         <f>STDEV(Sheet1!D56:G56)</f>
         <v>1559.00287296079</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="str">
+      <c r="G56" s="9">
+        <f>PRODUCT(Sheet1!D56,Sheet1!F56:G56)</f>
+        <v>102897099516.02682</v>
+      </c>
+      <c r="H56" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A57," ",Sheet1!B57)</f>
         <v>Charles Bradford</v>
       </c>
-      <c r="B57" s="2" t="str">
+      <c r="B57" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A57, " (",Sheet1!H57,")")</f>
         <v>Charles (Scrum Master)</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="9">
         <f>SUM(Sheet1!D57:G57)</f>
         <v>17344.05</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="9">
         <f>AVERAGE(Sheet1!D57:G57)</f>
         <v>4336.0124999999998</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="9">
         <f>MEDIAN(Sheet1!D57:F57,Sheet1!G57)</f>
         <v>4358.2250000000004</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="10">
         <f>STDEV(Sheet1!D57:G57)</f>
         <v>1317.1260867604919</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="str">
+      <c r="G57" s="9">
+        <f>PRODUCT(Sheet1!D57,Sheet1!F57:G57)</f>
+        <v>101798928932.99014</v>
+      </c>
+      <c r="H57" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A58," ",Sheet1!B58)</f>
         <v>Joshua Peters</v>
       </c>
-      <c r="B58" s="2" t="str">
+      <c r="B58" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A58, " (",Sheet1!H58,")")</f>
         <v>Joshua (Backend Developer)</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="9">
         <f>SUM(Sheet1!D58:G58)</f>
         <v>15219.650000000001</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="9">
         <f>AVERAGE(Sheet1!D58:G58)</f>
         <v>3804.9125000000004</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="9">
         <f>MEDIAN(Sheet1!D58:F58,Sheet1!G58)</f>
         <v>3883.4250000000002</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="10">
         <f>STDEV(Sheet1!D58:G58)</f>
         <v>575.72555118881451</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="str">
+      <c r="G58" s="9">
+        <f>PRODUCT(Sheet1!D58,Sheet1!F58:G58)</f>
+        <v>47962553772.182457</v>
+      </c>
+      <c r="H58" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A59," ",Sheet1!B59)</f>
         <v>Adam Mckinney</v>
       </c>
-      <c r="B59" s="2" t="str">
+      <c r="B59" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A59, " (",Sheet1!H59,")")</f>
         <v>Adam (Data Scientist)</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="9">
         <f>SUM(Sheet1!D59:G59)</f>
         <v>15557.39</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="9">
         <f>AVERAGE(Sheet1!D59:G59)</f>
         <v>3889.3474999999999</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="9">
         <f>MEDIAN(Sheet1!D59:F59,Sheet1!G59)</f>
         <v>3834.375</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="10">
         <f>STDEV(Sheet1!D59:G59)</f>
         <v>609.248544212458</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="str">
+      <c r="G59" s="9">
+        <f>PRODUCT(Sheet1!D59,Sheet1!F59:G59)</f>
+        <v>65492006729.333176</v>
+      </c>
+      <c r="H59" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A60," ",Sheet1!B60)</f>
         <v>Devin Roberts</v>
       </c>
-      <c r="B60" s="2" t="str">
+      <c r="B60" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A60, " (",Sheet1!H60,")")</f>
         <v>Devin (DevOps Engineer)</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="9">
         <f>SUM(Sheet1!D60:G60)</f>
         <v>18890.27</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="9">
         <f>AVERAGE(Sheet1!D60:G60)</f>
         <v>4722.5675000000001</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="9">
         <f>MEDIAN(Sheet1!D60:F60,Sheet1!G60)</f>
         <v>4516.88</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="10">
         <f>STDEV(Sheet1!D60:G60)</f>
         <v>1269.2449021202856</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="str">
+      <c r="G60" s="9">
+        <f>PRODUCT(Sheet1!D60,Sheet1!F60:G60)</f>
+        <v>88586808185.127838</v>
+      </c>
+      <c r="H60" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A61," ",Sheet1!B61)</f>
         <v>Brett Barry</v>
       </c>
-      <c r="B61" s="2" t="str">
+      <c r="B61" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A61, " (",Sheet1!H61,")")</f>
         <v>Brett (Data Scientist)</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="9">
         <f>SUM(Sheet1!D61:G61)</f>
         <v>18130.46</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="9">
         <f>AVERAGE(Sheet1!D61:G61)</f>
         <v>4532.6149999999998</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="9">
         <f>MEDIAN(Sheet1!D61:F61,Sheet1!G61)</f>
         <v>4571.3450000000003</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="10">
         <f>STDEV(Sheet1!D61:G61)</f>
         <v>722.447985417175</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="str">
+      <c r="G61" s="9">
+        <f>PRODUCT(Sheet1!D61,Sheet1!F61:G61)</f>
+        <v>75487772950.730072</v>
+      </c>
+      <c r="H61" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A62," ",Sheet1!B62)</f>
         <v>Wendy Jackson</v>
       </c>
-      <c r="B62" s="2" t="str">
+      <c r="B62" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A62, " (",Sheet1!H62,")")</f>
         <v>Wendy (UI/UX Designer)</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="9">
         <f>SUM(Sheet1!D62:G62)</f>
         <v>21912.55</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="9">
         <f>AVERAGE(Sheet1!D62:G62)</f>
         <v>5478.1374999999998</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="9">
         <f>MEDIAN(Sheet1!D62:F62,Sheet1!G62)</f>
         <v>5504.1949999999997</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="10">
         <f>STDEV(Sheet1!D62:G62)</f>
         <v>1322.4958020695838</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="str">
+      <c r="G62" s="9">
+        <f>PRODUCT(Sheet1!D62,Sheet1!F62:G62)</f>
+        <v>118613938050.51414</v>
+      </c>
+      <c r="H62" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A63," ",Sheet1!B63)</f>
         <v>Caitlin Farrell</v>
       </c>
-      <c r="B63" s="2" t="str">
+      <c r="B63" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A63, " (",Sheet1!H63,")")</f>
         <v>Caitlin (Data Scientist)</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="9">
         <f>SUM(Sheet1!D63:G63)</f>
         <v>20870.04</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="9">
         <f>AVERAGE(Sheet1!D63:G63)</f>
         <v>5217.51</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="9">
         <f>MEDIAN(Sheet1!D63:F63,Sheet1!G63)</f>
         <v>5380.96</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="10">
         <f>STDEV(Sheet1!D63:G63)</f>
         <v>1676.615032816617</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="str">
+      <c r="G63" s="9">
+        <f>PRODUCT(Sheet1!D63,Sheet1!F63:G63)</f>
+        <v>96595853101.523834</v>
+      </c>
+      <c r="H63" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A64," ",Sheet1!B64)</f>
         <v>Eric Blevins</v>
       </c>
-      <c r="B64" s="2" t="str">
+      <c r="B64" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A64, " (",Sheet1!H64,")")</f>
         <v>Eric (Product Manager)</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="9">
         <f>SUM(Sheet1!D64:G64)</f>
         <v>19213.14</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="9">
         <f>AVERAGE(Sheet1!D64:G64)</f>
         <v>4803.2849999999999</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="9">
         <f>MEDIAN(Sheet1!D64:F64,Sheet1!G64)</f>
         <v>4701.26</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="10">
         <f>STDEV(Sheet1!D64:G64)</f>
         <v>842.96423160574705</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="str">
+      <c r="G64" s="9">
+        <f>PRODUCT(Sheet1!D64,Sheet1!F64:G64)</f>
+        <v>86043202363.647064</v>
+      </c>
+      <c r="H64" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A65," ",Sheet1!B65)</f>
         <v>Michael Walter</v>
       </c>
-      <c r="B65" s="2" t="str">
+      <c r="B65" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A65, " (",Sheet1!H65,")")</f>
         <v>Michael (QA Engineer)</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="9">
         <f>SUM(Sheet1!D65:G65)</f>
         <v>19428.939999999999</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="9">
         <f>AVERAGE(Sheet1!D65:G65)</f>
         <v>4857.2349999999997</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="9">
         <f>MEDIAN(Sheet1!D65:F65,Sheet1!G65)</f>
         <v>4995.5249999999996</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="10">
         <f>STDEV(Sheet1!D65:G65)</f>
         <v>1168.0978610972656</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="str">
+      <c r="G65" s="9">
+        <f>PRODUCT(Sheet1!D65,Sheet1!F65:G65)</f>
+        <v>153128674617.51056</v>
+      </c>
+      <c r="H65" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A66," ",Sheet1!B66)</f>
         <v>Nancy Hughes</v>
       </c>
-      <c r="B66" s="2" t="str">
+      <c r="B66" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A66, " (",Sheet1!H66,")")</f>
         <v>Nancy (Full Stack Developer)</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="9">
         <f>SUM(Sheet1!D66:G66)</f>
         <v>20586.63</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="9">
         <f>AVERAGE(Sheet1!D66:G66)</f>
         <v>5146.6575000000003</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="9">
         <f>MEDIAN(Sheet1!D66:F66,Sheet1!G66)</f>
         <v>5252.2049999999999</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="10">
         <f>STDEV(Sheet1!D66:G66)</f>
         <v>466.03763284202722</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="str">
+      <c r="G66" s="9">
+        <f>PRODUCT(Sheet1!D66,Sheet1!F66:G66)</f>
+        <v>123987898742.00204</v>
+      </c>
+      <c r="H66" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A67," ",Sheet1!B67)</f>
         <v>Glen Wilcox</v>
       </c>
-      <c r="B67" s="2" t="str">
+      <c r="B67" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A67, " (",Sheet1!H67,")")</f>
         <v>Glen (Full Stack Developer)</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="9">
         <f>SUM(Sheet1!D67:G67)</f>
         <v>19014.72</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="9">
         <f>AVERAGE(Sheet1!D67:G67)</f>
         <v>4753.68</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="9">
         <f>MEDIAN(Sheet1!D67:F67,Sheet1!G67)</f>
         <v>4596.7700000000004</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="10">
         <f>STDEV(Sheet1!D67:G67)</f>
         <v>1463.6993273210169</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="str">
+      <c r="G67" s="9">
+        <f>PRODUCT(Sheet1!D67,Sheet1!F67:G67)</f>
+        <v>136146181659.85097</v>
+      </c>
+      <c r="H67" s="9" t="str">
+        <f t="shared" ref="H67:H101" si="1">IF(E67&gt;D67,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A68," ",Sheet1!B68)</f>
         <v>Angela Hansen</v>
       </c>
-      <c r="B68" s="2" t="str">
+      <c r="B68" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A68, " (",Sheet1!H68,")")</f>
         <v>Angela (Backend Developer)</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="9">
         <f>SUM(Sheet1!D68:G68)</f>
         <v>23047.770000000004</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="9">
         <f>AVERAGE(Sheet1!D68:G68)</f>
         <v>5761.942500000001</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="9">
         <f>MEDIAN(Sheet1!D68:F68,Sheet1!G68)</f>
         <v>6097.3649999999998</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="10">
         <f>STDEV(Sheet1!D68:G68)</f>
         <v>1363.2090341390494</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="str">
+      <c r="G68" s="9">
+        <f>PRODUCT(Sheet1!D68,Sheet1!F68:G68)</f>
+        <v>153538562781.4957</v>
+      </c>
+      <c r="H68" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A69," ",Sheet1!B69)</f>
         <v>Brian Bennett</v>
       </c>
-      <c r="B69" s="2" t="str">
+      <c r="B69" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A69, " (",Sheet1!H69,")")</f>
         <v>Brian (Product Manager)</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="9">
         <f>SUM(Sheet1!D69:G69)</f>
         <v>16931.150000000001</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="9">
         <f>AVERAGE(Sheet1!D69:G69)</f>
         <v>4232.7875000000004</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="9">
         <f>MEDIAN(Sheet1!D69:F69,Sheet1!G69)</f>
         <v>4227.47</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="10">
         <f>STDEV(Sheet1!D69:G69)</f>
         <v>505.10762373807734</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="str">
+      <c r="G69" s="9">
+        <f>PRODUCT(Sheet1!D69,Sheet1!F69:G69)</f>
+        <v>67704924764.87899</v>
+      </c>
+      <c r="H69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A70," ",Sheet1!B70)</f>
         <v>Steven Blair</v>
       </c>
-      <c r="B70" s="2" t="str">
+      <c r="B70" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A70, " (",Sheet1!H70,")")</f>
         <v>Steven (Full Stack Developer)</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="9">
         <f>SUM(Sheet1!D70:G70)</f>
         <v>17613.5</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="9">
         <f>AVERAGE(Sheet1!D70:G70)</f>
         <v>4403.375</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="9">
         <f>MEDIAN(Sheet1!D70:F70,Sheet1!G70)</f>
         <v>4440.7950000000001</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="10">
         <f>STDEV(Sheet1!D70:G70)</f>
         <v>1449.1172180906105</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="str">
+      <c r="G70" s="9">
+        <f>PRODUCT(Sheet1!D70,Sheet1!F70:G70)</f>
+        <v>104396260345.75856</v>
+      </c>
+      <c r="H70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A71," ",Sheet1!B71)</f>
         <v>Caitlyn Gutierrez</v>
       </c>
-      <c r="B71" s="2" t="str">
+      <c r="B71" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A71, " (",Sheet1!H71,")")</f>
         <v>Caitlyn (DevOps Engineer)</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="9">
         <f>SUM(Sheet1!D71:G71)</f>
         <v>18804.849999999999</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="9">
         <f>AVERAGE(Sheet1!D71:G71)</f>
         <v>4701.2124999999996</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="9">
         <f>MEDIAN(Sheet1!D71:F71,Sheet1!G71)</f>
         <v>4730.4650000000001</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="10">
         <f>STDEV(Sheet1!D71:G71)</f>
         <v>881.44978118911604</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="str">
+      <c r="G71" s="9">
+        <f>PRODUCT(Sheet1!D71,Sheet1!F71:G71)</f>
+        <v>94942775027.302032</v>
+      </c>
+      <c r="H71" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A72," ",Sheet1!B72)</f>
         <v>Jennifer Marquez</v>
       </c>
-      <c r="B72" s="2" t="str">
+      <c r="B72" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A72, " (",Sheet1!H72,")")</f>
         <v>Jennifer (Full Stack Developer)</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="9">
         <f>SUM(Sheet1!D72:G72)</f>
         <v>18896.09</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="9">
         <f>AVERAGE(Sheet1!D72:G72)</f>
         <v>4724.0225</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="9">
         <f>MEDIAN(Sheet1!D72:F72,Sheet1!G72)</f>
         <v>4809.6550000000007</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="10">
         <f>STDEV(Sheet1!D72:G72)</f>
         <v>1155.7667690722335</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="str">
+      <c r="G72" s="9">
+        <f>PRODUCT(Sheet1!D72,Sheet1!F72:G72)</f>
+        <v>133585079922.14815</v>
+      </c>
+      <c r="H72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A73," ",Sheet1!B73)</f>
         <v>Joseph Black</v>
       </c>
-      <c r="B73" s="2" t="str">
+      <c r="B73" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A73, " (",Sheet1!H73,")")</f>
         <v>Joseph (Software Engineer)</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="9">
         <f>SUM(Sheet1!D73:G73)</f>
         <v>17337.689999999999</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="9">
         <f>AVERAGE(Sheet1!D73:G73)</f>
         <v>4334.4224999999997</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="9">
         <f>MEDIAN(Sheet1!D73:F73,Sheet1!G73)</f>
         <v>4139.4799999999996</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="10">
         <f>STDEV(Sheet1!D73:G73)</f>
         <v>1167.5812113760376</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="str">
+      <c r="G73" s="9">
+        <f>PRODUCT(Sheet1!D73,Sheet1!F73:G73)</f>
+        <v>78404179577.753082</v>
+      </c>
+      <c r="H73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A74," ",Sheet1!B74)</f>
         <v>Veronica Porter</v>
       </c>
-      <c r="B74" s="2" t="str">
+      <c r="B74" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A74, " (",Sheet1!H74,")")</f>
         <v>Veronica (Business Analyst)</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="9">
         <f>SUM(Sheet1!D74:G74)</f>
         <v>17077.93</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="9">
         <f>AVERAGE(Sheet1!D74:G74)</f>
         <v>4269.4825000000001</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="9">
         <f>MEDIAN(Sheet1!D74:F74,Sheet1!G74)</f>
         <v>3602.0600000000004</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="10">
         <f>STDEV(Sheet1!D74:G74)</f>
         <v>1793.7920908209135</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="str">
+      <c r="G74" s="9">
+        <f>PRODUCT(Sheet1!D74,Sheet1!F74:G74)</f>
+        <v>85440838451.515121</v>
+      </c>
+      <c r="H74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A75," ",Sheet1!B75)</f>
         <v>Amanda Todd</v>
       </c>
-      <c r="B75" s="2" t="str">
+      <c r="B75" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A75, " (",Sheet1!H75,")")</f>
         <v>Amanda (Cloud Engineer)</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="9">
         <f>SUM(Sheet1!D75:G75)</f>
         <v>15674.35</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="9">
         <f>AVERAGE(Sheet1!D75:G75)</f>
         <v>3918.5875000000001</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="9">
         <f>MEDIAN(Sheet1!D75:F75,Sheet1!G75)</f>
         <v>4074.8950000000004</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="10">
         <f>STDEV(Sheet1!D75:G75)</f>
         <v>555.69997722842197</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="str">
+      <c r="G75" s="9">
+        <f>PRODUCT(Sheet1!D75,Sheet1!F75:G75)</f>
+        <v>57929787896.080551</v>
+      </c>
+      <c r="H75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A76," ",Sheet1!B76)</f>
         <v>Ashley Brown</v>
       </c>
-      <c r="B76" s="2" t="str">
+      <c r="B76" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A76, " (",Sheet1!H76,")")</f>
         <v>Ashley (Software Engineer)</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="9">
         <f>SUM(Sheet1!D76:G76)</f>
         <v>21780.21</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="9">
         <f>AVERAGE(Sheet1!D76:G76)</f>
         <v>5445.0524999999998</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="9">
         <f>MEDIAN(Sheet1!D76:F76,Sheet1!G76)</f>
         <v>5217.3</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="10">
         <f>STDEV(Sheet1!D76:G76)</f>
         <v>1031.1545093203399</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="str">
+      <c r="G76" s="9">
+        <f>PRODUCT(Sheet1!D76,Sheet1!F76:G76)</f>
+        <v>122123246299.63921</v>
+      </c>
+      <c r="H76" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A77," ",Sheet1!B77)</f>
         <v>Stephen Green</v>
       </c>
-      <c r="B77" s="2" t="str">
+      <c r="B77" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A77, " (",Sheet1!H77,")")</f>
         <v>Stephen (UI/UX Designer)</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="9">
         <f>SUM(Sheet1!D77:G77)</f>
         <v>22165.87</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="9">
         <f>AVERAGE(Sheet1!D77:G77)</f>
         <v>5541.4674999999997</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="9">
         <f>MEDIAN(Sheet1!D77:F77,Sheet1!G77)</f>
         <v>6060.66</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="10">
         <f>STDEV(Sheet1!D77:G77)</f>
         <v>1508.499346003063</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="str">
+      <c r="G77" s="9">
+        <f>PRODUCT(Sheet1!D77,Sheet1!F77:G77)</f>
+        <v>122340255426.26314</v>
+      </c>
+      <c r="H77" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A78," ",Sheet1!B78)</f>
         <v>Angela Gibbs</v>
       </c>
-      <c r="B78" s="2" t="str">
+      <c r="B78" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A78, " (",Sheet1!H78,")")</f>
         <v>Angela (Business Analyst)</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="9">
         <f>SUM(Sheet1!D78:G78)</f>
         <v>16554.86</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="9">
         <f>AVERAGE(Sheet1!D78:G78)</f>
         <v>4138.7150000000001</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="9">
         <f>MEDIAN(Sheet1!D78:F78,Sheet1!G78)</f>
         <v>3876.5450000000001</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="10">
         <f>STDEV(Sheet1!D78:G78)</f>
         <v>1125.3640346276086</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="str">
+      <c r="G78" s="9">
+        <f>PRODUCT(Sheet1!D78,Sheet1!F78:G78)</f>
+        <v>78383505842.041</v>
+      </c>
+      <c r="H78" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A79," ",Sheet1!B79)</f>
         <v>Timothy Hughes</v>
       </c>
-      <c r="B79" s="2" t="str">
+      <c r="B79" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A79, " (",Sheet1!H79,")")</f>
         <v>Timothy (Full Stack Developer)</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="9">
         <f>SUM(Sheet1!D79:G79)</f>
         <v>19838.38</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="9">
         <f>AVERAGE(Sheet1!D79:G79)</f>
         <v>4959.5950000000003</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="9">
         <f>MEDIAN(Sheet1!D79:F79,Sheet1!G79)</f>
         <v>4764.33</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="10">
         <f>STDEV(Sheet1!D79:G79)</f>
         <v>1127.7508440697354</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="str">
+      <c r="G79" s="9">
+        <f>PRODUCT(Sheet1!D79,Sheet1!F79:G79)</f>
+        <v>144810918400.89178</v>
+      </c>
+      <c r="H79" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A80," ",Sheet1!B80)</f>
         <v>Vanessa Griffin</v>
       </c>
-      <c r="B80" s="2" t="str">
+      <c r="B80" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A80, " (",Sheet1!H80,")")</f>
         <v>Vanessa (Data Scientist)</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="9">
         <f>SUM(Sheet1!D80:G80)</f>
         <v>18426.330000000002</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="9">
         <f>AVERAGE(Sheet1!D80:G80)</f>
         <v>4606.5825000000004</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="9">
         <f>MEDIAN(Sheet1!D80:F80,Sheet1!G80)</f>
         <v>4597.24</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="10">
         <f>STDEV(Sheet1!D80:G80)</f>
         <v>1267.6660293987775</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="str">
+      <c r="G80" s="9">
+        <f>PRODUCT(Sheet1!D80,Sheet1!F80:G80)</f>
+        <v>93292651885.618942</v>
+      </c>
+      <c r="H80" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A81," ",Sheet1!B81)</f>
         <v>Kaitlin Colon</v>
       </c>
-      <c r="B81" s="2" t="str">
+      <c r="B81" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A81, " (",Sheet1!H81,")")</f>
         <v>Kaitlin (Scrum Master)</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="9">
         <f>SUM(Sheet1!D81:G81)</f>
         <v>16668.38</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="9">
         <f>AVERAGE(Sheet1!D81:G81)</f>
         <v>4167.0950000000003</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="9">
         <f>MEDIAN(Sheet1!D81:F81,Sheet1!G81)</f>
         <v>3887.17</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="10">
         <f>STDEV(Sheet1!D81:G81)</f>
         <v>1247.4151424846491</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="str">
+      <c r="G81" s="9">
+        <f>PRODUCT(Sheet1!D81,Sheet1!F81:G81)</f>
+        <v>45405706108.971603</v>
+      </c>
+      <c r="H81" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A82," ",Sheet1!B82)</f>
         <v>Joshua Benson</v>
       </c>
-      <c r="B82" s="2" t="str">
+      <c r="B82" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A82, " (",Sheet1!H82,")")</f>
         <v>Joshua (Data Scientist)</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="9">
         <f>SUM(Sheet1!D82:G82)</f>
         <v>19293.84</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="9">
         <f>AVERAGE(Sheet1!D82:G82)</f>
         <v>4823.46</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="9">
         <f>MEDIAN(Sheet1!D82:F82,Sheet1!G82)</f>
         <v>4401.7349999999997</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="10">
         <f>STDEV(Sheet1!D82:G82)</f>
         <v>1542.8769077062902</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="str">
+      <c r="G82" s="9">
+        <f>PRODUCT(Sheet1!D82,Sheet1!F82:G82)</f>
+        <v>128302228318.60582</v>
+      </c>
+      <c r="H82" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A83," ",Sheet1!B83)</f>
         <v>Nicholas Chavez</v>
       </c>
-      <c r="B83" s="2" t="str">
+      <c r="B83" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A83, " (",Sheet1!H83,")")</f>
         <v>Nicholas (Security Analyst)</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="9">
         <f>SUM(Sheet1!D83:G83)</f>
         <v>18560.11</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="9">
         <f>AVERAGE(Sheet1!D83:G83)</f>
         <v>4640.0275000000001</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="9">
         <f>MEDIAN(Sheet1!D83:F83,Sheet1!G83)</f>
         <v>4793</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="10">
         <f>STDEV(Sheet1!D83:G83)</f>
         <v>1236.9130520877359</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="str">
+      <c r="G83" s="9">
+        <f>PRODUCT(Sheet1!D83,Sheet1!F83:G83)</f>
+        <v>90748270084.750259</v>
+      </c>
+      <c r="H83" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A84," ",Sheet1!B84)</f>
         <v>Timothy Nelson</v>
       </c>
-      <c r="B84" s="2" t="str">
+      <c r="B84" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A84, " (",Sheet1!H84,")")</f>
         <v>Timothy (Frontend Developer)</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="9">
         <f>SUM(Sheet1!D84:G84)</f>
         <v>19074.2</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="9">
         <f>AVERAGE(Sheet1!D84:G84)</f>
         <v>4768.55</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="9">
         <f>MEDIAN(Sheet1!D84:F84,Sheet1!G84)</f>
         <v>4336.2150000000001</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="10">
         <f>STDEV(Sheet1!D84:G84)</f>
         <v>1382.2439053220667</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="str">
+      <c r="G84" s="9">
+        <f>PRODUCT(Sheet1!D84,Sheet1!F84:G84)</f>
+        <v>116582513141.04779</v>
+      </c>
+      <c r="H84" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A85," ",Sheet1!B85)</f>
         <v>Scott Smith</v>
       </c>
-      <c r="B85" s="2" t="str">
+      <c r="B85" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A85, " (",Sheet1!H85,")")</f>
         <v>Scott (Frontend Developer)</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="9">
         <f>SUM(Sheet1!D85:G85)</f>
         <v>21241.65</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="9">
         <f>AVERAGE(Sheet1!D85:G85)</f>
         <v>5310.4125000000004</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="9">
         <f>MEDIAN(Sheet1!D85:F85,Sheet1!G85)</f>
         <v>5599.3600000000006</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="10">
         <f>STDEV(Sheet1!D85:G85)</f>
         <v>1031.2032643591645</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="str">
+      <c r="G85" s="9">
+        <f>PRODUCT(Sheet1!D85,Sheet1!F85:G85)</f>
+        <v>137870426873.35104</v>
+      </c>
+      <c r="H85" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A86," ",Sheet1!B86)</f>
         <v>Cathy Carr</v>
       </c>
-      <c r="B86" s="2" t="str">
+      <c r="B86" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A86, " (",Sheet1!H86,")")</f>
         <v>Cathy (DevOps Engineer)</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="9">
         <f>SUM(Sheet1!D86:G86)</f>
         <v>22267.69</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="9">
         <f>AVERAGE(Sheet1!D86:G86)</f>
         <v>5566.9224999999997</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="9">
         <f>MEDIAN(Sheet1!D86:F86,Sheet1!G86)</f>
         <v>5608.3649999999998</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="10">
         <f>STDEV(Sheet1!D86:G86)</f>
         <v>910.44551937957146</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="str">
+      <c r="G86" s="9">
+        <f>PRODUCT(Sheet1!D86,Sheet1!F86:G86)</f>
+        <v>168926898807.40781</v>
+      </c>
+      <c r="H86" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A87," ",Sheet1!B87)</f>
         <v>Katherine Williams</v>
       </c>
-      <c r="B87" s="2" t="str">
+      <c r="B87" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A87, " (",Sheet1!H87,")")</f>
         <v>Katherine (Mobile App Developer)</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="9">
         <f>SUM(Sheet1!D87:G87)</f>
         <v>21501.82</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="9">
         <f>AVERAGE(Sheet1!D87:G87)</f>
         <v>5375.4549999999999</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="9">
         <f>MEDIAN(Sheet1!D87:F87,Sheet1!G87)</f>
         <v>5780.26</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="10">
         <f>STDEV(Sheet1!D87:G87)</f>
         <v>1172.0310639085767</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="str">
+      <c r="G87" s="9">
+        <f>PRODUCT(Sheet1!D87,Sheet1!F87:G87)</f>
+        <v>210043184049.16562</v>
+      </c>
+      <c r="H87" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A88," ",Sheet1!B88)</f>
         <v>Shane Oconnor</v>
       </c>
-      <c r="B88" s="2" t="str">
+      <c r="B88" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A88, " (",Sheet1!H88,")")</f>
         <v>Shane (Security Analyst)</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88" s="9">
         <f>SUM(Sheet1!D88:G88)</f>
         <v>19744.52</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="9">
         <f>AVERAGE(Sheet1!D88:G88)</f>
         <v>4936.13</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="9">
         <f>MEDIAN(Sheet1!D88:F88,Sheet1!G88)</f>
         <v>5317.0249999999996</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="10">
         <f>STDEV(Sheet1!D88:G88)</f>
         <v>1129.455243351116</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="str">
+      <c r="G88" s="9">
+        <f>PRODUCT(Sheet1!D88,Sheet1!F88:G88)</f>
+        <v>92767991893.954193</v>
+      </c>
+      <c r="H88" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A89," ",Sheet1!B89)</f>
         <v>Natalie White</v>
       </c>
-      <c r="B89" s="2" t="str">
+      <c r="B89" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A89, " (",Sheet1!H89,")")</f>
         <v>Natalie (Backend Developer)</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="9">
         <f>SUM(Sheet1!D89:G89)</f>
         <v>22902.440000000002</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="9">
         <f>AVERAGE(Sheet1!D89:G89)</f>
         <v>5725.6100000000006</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="9">
         <f>MEDIAN(Sheet1!D89:F89,Sheet1!G89)</f>
         <v>5865.335</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="10">
         <f>STDEV(Sheet1!D89:G89)</f>
         <v>714.31725551979014</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="str">
+      <c r="G89" s="9">
+        <f>PRODUCT(Sheet1!D89,Sheet1!F89:G89)</f>
+        <v>163435881303.95099</v>
+      </c>
+      <c r="H89" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A90," ",Sheet1!B90)</f>
         <v>Hannah Schmidt</v>
       </c>
-      <c r="B90" s="2" t="str">
+      <c r="B90" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A90, " (",Sheet1!H90,")")</f>
         <v>Hannah (System Administrator)</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="9">
         <f>SUM(Sheet1!D90:G90)</f>
         <v>18634.68</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="9">
         <f>AVERAGE(Sheet1!D90:G90)</f>
         <v>4658.67</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="9">
         <f>MEDIAN(Sheet1!D90:F90,Sheet1!G90)</f>
         <v>4720.0999999999995</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="10">
         <f>STDEV(Sheet1!D90:G90)</f>
         <v>1699.9921361190648</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="str">
+      <c r="G90" s="9">
+        <f>PRODUCT(Sheet1!D90,Sheet1!F90:G90)</f>
+        <v>62897184451.772697</v>
+      </c>
+      <c r="H90" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A91," ",Sheet1!B91)</f>
         <v>Alexandra Bates</v>
       </c>
-      <c r="B91" s="2" t="str">
+      <c r="B91" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A91, " (",Sheet1!H91,")")</f>
         <v>Alexandra (DevOps Engineer)</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="9">
         <f>SUM(Sheet1!D91:G91)</f>
         <v>21365.14</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="9">
         <f>AVERAGE(Sheet1!D91:G91)</f>
         <v>5341.2849999999999</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="9">
         <f>MEDIAN(Sheet1!D91:F91,Sheet1!G91)</f>
         <v>5315.42</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="10">
         <f>STDEV(Sheet1!D91:G91)</f>
         <v>1248.1519362241143</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="str">
+      <c r="G91" s="9">
+        <f>PRODUCT(Sheet1!D91,Sheet1!F91:G91)</f>
+        <v>164025137713.203</v>
+      </c>
+      <c r="H91" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A92," ",Sheet1!B92)</f>
         <v>Justin Pham</v>
       </c>
-      <c r="B92" s="2" t="str">
+      <c r="B92" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A92, " (",Sheet1!H92,")")</f>
         <v>Justin (Business Analyst)</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="9">
         <f>SUM(Sheet1!D92:G92)</f>
         <v>19777.61</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="9">
         <f>AVERAGE(Sheet1!D92:G92)</f>
         <v>4944.4025000000001</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="9">
         <f>MEDIAN(Sheet1!D92:F92,Sheet1!G92)</f>
         <v>4975.5400000000009</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="10">
         <f>STDEV(Sheet1!D92:G92)</f>
         <v>881.11396158025946</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="str">
+      <c r="G92" s="9">
+        <f>PRODUCT(Sheet1!D92,Sheet1!F92:G92)</f>
+        <v>95118190907.376648</v>
+      </c>
+      <c r="H92" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A93," ",Sheet1!B93)</f>
         <v>Paul Peterson</v>
       </c>
-      <c r="B93" s="2" t="str">
+      <c r="B93" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A93, " (",Sheet1!H93,")")</f>
         <v>Paul (Product Manager)</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="9">
         <f>SUM(Sheet1!D93:G93)</f>
         <v>21287.41</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="9">
         <f>AVERAGE(Sheet1!D93:G93)</f>
         <v>5321.8525</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="9">
         <f>MEDIAN(Sheet1!D93:F93,Sheet1!G93)</f>
         <v>5488.3549999999996</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="10">
         <f>STDEV(Sheet1!D93:G93)</f>
         <v>726.11160516709708</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="str">
+      <c r="G93" s="9">
+        <f>PRODUCT(Sheet1!D93,Sheet1!F93:G93)</f>
+        <v>130646291244.30035</v>
+      </c>
+      <c r="H93" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A94," ",Sheet1!B94)</f>
         <v>Joel King</v>
       </c>
-      <c r="B94" s="2" t="str">
+      <c r="B94" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A94, " (",Sheet1!H94,")")</f>
         <v>Joel (Data Scientist)</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="9">
         <f>SUM(Sheet1!D94:G94)</f>
         <v>16943.949999999997</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="9">
         <f>AVERAGE(Sheet1!D94:G94)</f>
         <v>4235.9874999999993</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="9">
         <f>MEDIAN(Sheet1!D94:F94,Sheet1!G94)</f>
         <v>4050.6149999999998</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="10">
         <f>STDEV(Sheet1!D94:G94)</f>
         <v>951.94967967062269</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="str">
+      <c r="G94" s="9">
+        <f>PRODUCT(Sheet1!D94,Sheet1!F94:G94)</f>
+        <v>53912058466.226677</v>
+      </c>
+      <c r="H94" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A95," ",Sheet1!B95)</f>
         <v>Elaine Shaw</v>
       </c>
-      <c r="B95" s="2" t="str">
+      <c r="B95" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A95, " (",Sheet1!H95,")")</f>
         <v>Elaine (QA Engineer)</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="9">
         <f>SUM(Sheet1!D95:G95)</f>
         <v>23022.57</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="9">
         <f>AVERAGE(Sheet1!D95:G95)</f>
         <v>5755.6424999999999</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="9">
         <f>MEDIAN(Sheet1!D95:F95,Sheet1!G95)</f>
         <v>5897.5249999999996</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="10">
         <f>STDEV(Sheet1!D95:G95)</f>
         <v>948.32521785777556</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="str">
+      <c r="G95" s="9">
+        <f>PRODUCT(Sheet1!D95,Sheet1!F95:G95)</f>
+        <v>227770836653.85419</v>
+      </c>
+      <c r="H95" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A96," ",Sheet1!B96)</f>
         <v>Tanya Nielsen</v>
       </c>
-      <c r="B96" s="2" t="str">
+      <c r="B96" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A96, " (",Sheet1!H96,")")</f>
         <v>Tanya (System Administrator)</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="9">
         <f>SUM(Sheet1!D96:G96)</f>
         <v>19242.05</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="9">
         <f>AVERAGE(Sheet1!D96:G96)</f>
         <v>4810.5124999999998</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="9">
         <f>MEDIAN(Sheet1!D96:F96,Sheet1!G96)</f>
         <v>4876.165</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="10">
         <f>STDEV(Sheet1!D96:G96)</f>
         <v>1119.8616539964523</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="str">
+      <c r="G96" s="9">
+        <f>PRODUCT(Sheet1!D96,Sheet1!F96:G96)</f>
+        <v>80290192745.185165</v>
+      </c>
+      <c r="H96" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A97," ",Sheet1!B97)</f>
         <v>Alejandra Mueller</v>
       </c>
-      <c r="B97" s="2" t="str">
+      <c r="B97" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A97, " (",Sheet1!H97,")")</f>
         <v>Alejandra (UI/UX Designer)</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="9">
         <f>SUM(Sheet1!D97:G97)</f>
         <v>19409.71</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="9">
         <f>AVERAGE(Sheet1!D97:G97)</f>
         <v>4852.4274999999998</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="9">
         <f>MEDIAN(Sheet1!D97:F97,Sheet1!G97)</f>
         <v>4991.25</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="10">
         <f>STDEV(Sheet1!D97:G97)</f>
         <v>1222.984391352428</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="str">
+      <c r="G97" s="9">
+        <f>PRODUCT(Sheet1!D97,Sheet1!F97:G97)</f>
+        <v>102463335803.36929</v>
+      </c>
+      <c r="H97" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A98," ",Sheet1!B98)</f>
         <v>Eddie Perez</v>
       </c>
-      <c r="B98" s="2" t="str">
+      <c r="B98" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A98, " (",Sheet1!H98,")")</f>
         <v>Eddie (Technical Support)</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="9">
         <f>SUM(Sheet1!D98:G98)</f>
         <v>18746.150000000001</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="9">
         <f>AVERAGE(Sheet1!D98:G98)</f>
         <v>4686.5375000000004</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="9">
         <f>MEDIAN(Sheet1!D98:F98,Sheet1!G98)</f>
         <v>4762.4400000000005</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="10">
         <f>STDEV(Sheet1!D98:G98)</f>
         <v>1188.5130753277374</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="str">
+      <c r="G98" s="9">
+        <f>PRODUCT(Sheet1!D98,Sheet1!F98:G98)</f>
+        <v>102903114044.19565</v>
+      </c>
+      <c r="H98" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A99," ",Sheet1!B99)</f>
         <v>Jessica Nunez</v>
       </c>
-      <c r="B99" s="2" t="str">
+      <c r="B99" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A99, " (",Sheet1!H99,")")</f>
         <v>Jessica (UI/UX Designer)</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="9">
         <f>SUM(Sheet1!D99:G99)</f>
         <v>17845.009999999998</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="9">
         <f>AVERAGE(Sheet1!D99:G99)</f>
         <v>4461.2524999999996</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="9">
         <f>MEDIAN(Sheet1!D99:F99,Sheet1!G99)</f>
         <v>3923.0349999999999</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="10">
         <f>STDEV(Sheet1!D99:G99)</f>
         <v>1631.3872216281663</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="str">
+      <c r="G99" s="9">
+        <f>PRODUCT(Sheet1!D99,Sheet1!F99:G99)</f>
+        <v>78064189310.20372</v>
+      </c>
+      <c r="H99" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A100," ",Sheet1!B100)</f>
         <v>Carrie Wright</v>
       </c>
-      <c r="B100" s="2" t="str">
+      <c r="B100" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A100, " (",Sheet1!H100,")")</f>
         <v>Carrie (Full Stack Developer)</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="9">
         <f>SUM(Sheet1!D100:G100)</f>
         <v>19593.02</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="9">
         <f>AVERAGE(Sheet1!D100:G100)</f>
         <v>4898.2550000000001</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="9">
         <f>MEDIAN(Sheet1!D100:F100,Sheet1!G100)</f>
         <v>4556.71</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="10">
         <f>STDEV(Sheet1!D100:G100)</f>
         <v>1497.5227319476637</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="str">
+      <c r="G100" s="9">
+        <f>PRODUCT(Sheet1!D100,Sheet1!F100:G100)</f>
+        <v>121263863034.35628</v>
+      </c>
+      <c r="H100" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="str">
         <f>_xlfn.CONCAT(Sheet1!A101," ",Sheet1!B101)</f>
         <v>Daniel Haynes</v>
       </c>
-      <c r="B101" s="2" t="str">
+      <c r="B101" s="9" t="str">
         <f>_xlfn.CONCAT(Sheet1!A101, " (",Sheet1!H101,")")</f>
         <v>Daniel (Backend Developer)</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="9">
         <f>SUM(Sheet1!D101:G101)</f>
         <v>21449.11</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="9">
         <f>AVERAGE(Sheet1!D101:G101)</f>
         <v>5362.2775000000001</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="9">
         <f>MEDIAN(Sheet1!D101:F101,Sheet1!G101)</f>
         <v>5326.5550000000003</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="10">
         <f>STDEV(Sheet1!D101:G101)</f>
         <v>1143.3617554496905</v>
       </c>
+      <c r="G101" s="9">
+        <f>PRODUCT(Sheet1!D101,Sheet1!F101:G101)</f>
+        <v>146893185171.40561</v>
+      </c>
+      <c r="H101" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Approved</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D101">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{44831B24-8F21-4600-A16D-99B90A9E404E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F101">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G101">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B228BA3C-846D-4582-BFD8-5C0712141BC8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{4566309B-7F17-42CF-A167-48D4155CA232}">
+          <x14:cfRule type="iconSet" priority="10" id="{4566309B-7F17-42CF-A167-48D4155CA232}">
             <x14:iconSet iconSet="3Stars">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6665,6 +8169,32 @@
           </x14:cfRule>
           <xm:sqref>J5</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{44831B24-8F21-4600-A16D-99B90A9E404E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D2:D101</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B228BA3C-846D-4582-BFD8-5C0712141BC8}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G2:G101</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/salaries_with_roles/salaries_with_roles.xlsx
+++ b/salaries_with_roles/salaries_with_roles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data_Analystics-Projects\salaries_with_roles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603508DC-BE76-48EF-9D81-97A2002FC0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE59530-979C-4873-AC11-37BC4C1BCBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="313">
   <si>
     <t>First Name</t>
   </si>
@@ -964,6 +964,15 @@
   </si>
   <si>
     <t>Median&gt;Avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Joel King</t>
+  </si>
+  <si>
+    <t>VLOOKUP</t>
   </si>
 </sst>
 </file>
@@ -971,7 +980,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1080,10 +1089,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1390,24 +1399,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="2"/>
+    <col min="7" max="7" width="13.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,8 +1453,32 @@
       <c r="J1" s="7" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1470,8 +1509,40 @@
       <c r="J2" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A2," ",Sheet1!B2)</f>
+        <v>Maria Matthews</v>
+      </c>
+      <c r="L2" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A2, " (",Sheet1!H2,")")</f>
+        <v>Maria (System Administrator)</v>
+      </c>
+      <c r="M2" s="9">
+        <f>SUM(Sheet1!D2:G2)</f>
+        <v>19714.559999999998</v>
+      </c>
+      <c r="N2" s="9">
+        <f>AVERAGE(Sheet1!D2:G2)</f>
+        <v>4928.6399999999994</v>
+      </c>
+      <c r="O2" s="9">
+        <f>MEDIAN(Sheet1!D2:F2,Sheet1!G2)</f>
+        <v>5229.2250000000004</v>
+      </c>
+      <c r="P2" s="10">
+        <f>STDEV(Sheet1!D2:G2)</f>
+        <v>1275.5392790763742</v>
+      </c>
+      <c r="Q2" s="9">
+        <f>PRODUCT(Sheet1!D2,Sheet1!F2:G2)</f>
+        <v>113158186357.21536</v>
+      </c>
+      <c r="R2" s="9" t="str">
+        <f>IF(O2&gt;N2,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1502,8 +1573,40 @@
       <c r="J3" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A3," ",Sheet1!B3)</f>
+        <v>Jenna Wilson</v>
+      </c>
+      <c r="L3" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A3, " (",Sheet1!H3,")")</f>
+        <v>Jenna (QA Engineer)</v>
+      </c>
+      <c r="M3" s="9">
+        <f>SUM(Sheet1!D3:G3)</f>
+        <v>19350.419999999998</v>
+      </c>
+      <c r="N3" s="9">
+        <f>AVERAGE(Sheet1!D3:G3)</f>
+        <v>4837.6049999999996</v>
+      </c>
+      <c r="O3" s="9">
+        <f>MEDIAN(Sheet1!D3:F3,Sheet1!G3)</f>
+        <v>4999.085</v>
+      </c>
+      <c r="P3" s="10">
+        <f>STDEV(Sheet1!D3:G3)</f>
+        <v>1126.3574497911416</v>
+      </c>
+      <c r="Q3" s="9">
+        <f>PRODUCT(Sheet1!D3,Sheet1!F3:G3)</f>
+        <v>87962839949.162384</v>
+      </c>
+      <c r="R3" s="9" t="str">
+        <f>IF(O3&gt;N3,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1534,8 +1637,40 @@
       <c r="J4" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A4," ",Sheet1!B4)</f>
+        <v>Charles Morgan</v>
+      </c>
+      <c r="L4" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A4, " (",Sheet1!H4,")")</f>
+        <v>Charles (Mobile App Developer)</v>
+      </c>
+      <c r="M4" s="9">
+        <f>SUM(Sheet1!D4:G4)</f>
+        <v>22629.119999999999</v>
+      </c>
+      <c r="N4" s="9">
+        <f>AVERAGE(Sheet1!D4:G4)</f>
+        <v>5657.28</v>
+      </c>
+      <c r="O4" s="9">
+        <f>MEDIAN(Sheet1!D4:F4,Sheet1!G4)</f>
+        <v>5960.4449999999997</v>
+      </c>
+      <c r="P4" s="10">
+        <f>STDEV(Sheet1!D4:G4)</f>
+        <v>1378.9222741692167</v>
+      </c>
+      <c r="Q4" s="9">
+        <f>PRODUCT(Sheet1!D4,Sheet1!F4:G4)</f>
+        <v>157977029147.8287</v>
+      </c>
+      <c r="R4" s="9" t="str">
+        <f>IF(O4&gt;N4,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1566,8 +1701,40 @@
       <c r="J5" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A5," ",Sheet1!B5)</f>
+        <v>Richard Padilla</v>
+      </c>
+      <c r="L5" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A5, " (",Sheet1!H5,")")</f>
+        <v>Richard (System Administrator)</v>
+      </c>
+      <c r="M5" s="9">
+        <f>SUM(Sheet1!D5:G5)</f>
+        <v>22833.69</v>
+      </c>
+      <c r="N5" s="9">
+        <f>AVERAGE(Sheet1!D5:G5)</f>
+        <v>5708.4224999999997</v>
+      </c>
+      <c r="O5" s="9">
+        <f>MEDIAN(Sheet1!D5:F5,Sheet1!G5)</f>
+        <v>6186.16</v>
+      </c>
+      <c r="P5" s="10">
+        <f>STDEV(Sheet1!D5:G5)</f>
+        <v>1256.5419138618797</v>
+      </c>
+      <c r="Q5" s="9">
+        <f>PRODUCT(Sheet1!D5,Sheet1!F5:G5)</f>
+        <v>251538956263.08948</v>
+      </c>
+      <c r="R5" s="9" t="str">
+        <f>IF(O5&gt;N5,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1598,8 +1765,40 @@
       <c r="J6" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A6," ",Sheet1!B6)</f>
+        <v>Cindy Roberts</v>
+      </c>
+      <c r="L6" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A6, " (",Sheet1!H6,")")</f>
+        <v>Cindy (Full Stack Developer)</v>
+      </c>
+      <c r="M6" s="9">
+        <f>SUM(Sheet1!D6:G6)</f>
+        <v>19810.580000000002</v>
+      </c>
+      <c r="N6" s="9">
+        <f>AVERAGE(Sheet1!D6:G6)</f>
+        <v>4952.6450000000004</v>
+      </c>
+      <c r="O6" s="9">
+        <f>MEDIAN(Sheet1!D6:F6,Sheet1!G6)</f>
+        <v>5235.7950000000001</v>
+      </c>
+      <c r="P6" s="10">
+        <f>STDEV(Sheet1!D6:G6)</f>
+        <v>1472.3394251439872</v>
+      </c>
+      <c r="Q6" s="9">
+        <f>PRODUCT(Sheet1!D6,Sheet1!F6:G6)</f>
+        <v>81951095956.771439</v>
+      </c>
+      <c r="R6" s="9" t="str">
+        <f>IF(O6&gt;N6,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1630,8 +1829,40 @@
       <c r="J7" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A7," ",Sheet1!B7)</f>
+        <v>Lauren Bailey</v>
+      </c>
+      <c r="L7" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A7, " (",Sheet1!H7,")")</f>
+        <v>Lauren (UI/UX Designer)</v>
+      </c>
+      <c r="M7" s="9">
+        <f>SUM(Sheet1!D7:G7)</f>
+        <v>20536.919999999998</v>
+      </c>
+      <c r="N7" s="9">
+        <f>AVERAGE(Sheet1!D7:G7)</f>
+        <v>5134.2299999999996</v>
+      </c>
+      <c r="O7" s="9">
+        <f>MEDIAN(Sheet1!D7:F7,Sheet1!G7)</f>
+        <v>5292.0949999999993</v>
+      </c>
+      <c r="P7" s="10">
+        <f>STDEV(Sheet1!D7:G7)</f>
+        <v>1451.0492338304748</v>
+      </c>
+      <c r="Q7" s="9">
+        <f>PRODUCT(Sheet1!D7,Sheet1!F7:G7)</f>
+        <v>107348911244.79958</v>
+      </c>
+      <c r="R7" s="9" t="str">
+        <f>IF(O7&gt;N7,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1662,8 +1893,40 @@
       <c r="J8" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A8," ",Sheet1!B8)</f>
+        <v>Jill Thomas</v>
+      </c>
+      <c r="L8" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A8, " (",Sheet1!H8,")")</f>
+        <v>Jill (Mobile App Developer)</v>
+      </c>
+      <c r="M8" s="9">
+        <f>SUM(Sheet1!D8:G8)</f>
+        <v>22228.089999999997</v>
+      </c>
+      <c r="N8" s="9">
+        <f>AVERAGE(Sheet1!D8:G8)</f>
+        <v>5557.0224999999991</v>
+      </c>
+      <c r="O8" s="9">
+        <f>MEDIAN(Sheet1!D8:F8,Sheet1!G8)</f>
+        <v>5647.27</v>
+      </c>
+      <c r="P8" s="10">
+        <f>STDEV(Sheet1!D8:G8)</f>
+        <v>1008.4312351824893</v>
+      </c>
+      <c r="Q8" s="9">
+        <f>PRODUCT(Sheet1!D8,Sheet1!F8:G8)</f>
+        <v>206930333174.88055</v>
+      </c>
+      <c r="R8" s="9" t="str">
+        <f>IF(O8&gt;N8,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1694,8 +1957,40 @@
       <c r="J9" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A9," ",Sheet1!B9)</f>
+        <v>Kristin Ashley</v>
+      </c>
+      <c r="L9" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A9, " (",Sheet1!H9,")")</f>
+        <v>Kristin (QA Engineer)</v>
+      </c>
+      <c r="M9" s="9">
+        <f>SUM(Sheet1!D9:G9)</f>
+        <v>14240.029999999999</v>
+      </c>
+      <c r="N9" s="9">
+        <f>AVERAGE(Sheet1!D9:G9)</f>
+        <v>3560.0074999999997</v>
+      </c>
+      <c r="O9" s="9">
+        <f>MEDIAN(Sheet1!D9:F9,Sheet1!G9)</f>
+        <v>3395.2750000000001</v>
+      </c>
+      <c r="P9" s="10">
+        <f>STDEV(Sheet1!D9:G9)</f>
+        <v>523.70867533868477</v>
+      </c>
+      <c r="Q9" s="9">
+        <f>PRODUCT(Sheet1!D9,Sheet1!F9:G9)</f>
+        <v>49796409013.680664</v>
+      </c>
+      <c r="R9" s="9" t="str">
+        <f>IF(O9&gt;N9,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1726,8 +2021,40 @@
       <c r="J10" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A10," ",Sheet1!B10)</f>
+        <v>Amanda Howard</v>
+      </c>
+      <c r="L10" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A10, " (",Sheet1!H10,")")</f>
+        <v>Amanda (Backend Developer)</v>
+      </c>
+      <c r="M10" s="9">
+        <f>SUM(Sheet1!D10:G10)</f>
+        <v>18016.830000000002</v>
+      </c>
+      <c r="N10" s="9">
+        <f>AVERAGE(Sheet1!D10:G10)</f>
+        <v>4504.2075000000004</v>
+      </c>
+      <c r="O10" s="9">
+        <f>MEDIAN(Sheet1!D10:F10,Sheet1!G10)</f>
+        <v>4344.7650000000003</v>
+      </c>
+      <c r="P10" s="10">
+        <f>STDEV(Sheet1!D10:G10)</f>
+        <v>730.13116800453304</v>
+      </c>
+      <c r="Q10" s="9">
+        <f>PRODUCT(Sheet1!D10,Sheet1!F10:G10)</f>
+        <v>71890055469.734116</v>
+      </c>
+      <c r="R10" s="9" t="str">
+        <f>IF(O10&gt;N10,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1758,8 +2085,40 @@
       <c r="J11" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A11," ",Sheet1!B11)</f>
+        <v>Joanne Johnson</v>
+      </c>
+      <c r="L11" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A11, " (",Sheet1!H11,")")</f>
+        <v>Joanne (Product Manager)</v>
+      </c>
+      <c r="M11" s="9">
+        <f>SUM(Sheet1!D11:G11)</f>
+        <v>21615.72</v>
+      </c>
+      <c r="N11" s="9">
+        <f>AVERAGE(Sheet1!D11:G11)</f>
+        <v>5403.93</v>
+      </c>
+      <c r="O11" s="9">
+        <f>MEDIAN(Sheet1!D11:F11,Sheet1!G11)</f>
+        <v>5970.1849999999995</v>
+      </c>
+      <c r="P11" s="10">
+        <f>STDEV(Sheet1!D11:G11)</f>
+        <v>1594.0756624660767</v>
+      </c>
+      <c r="Q11" s="9">
+        <f>PRODUCT(Sheet1!D11,Sheet1!F11:G11)</f>
+        <v>120367436686.89662</v>
+      </c>
+      <c r="R11" s="9" t="str">
+        <f>IF(O11&gt;N11,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1790,8 +2149,40 @@
       <c r="J12" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A12," ",Sheet1!B12)</f>
+        <v>Jackie Velasquez</v>
+      </c>
+      <c r="L12" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A12, " (",Sheet1!H12,")")</f>
+        <v>Jackie (Technical Support)</v>
+      </c>
+      <c r="M12" s="9">
+        <f>SUM(Sheet1!D12:G12)</f>
+        <v>17223.73</v>
+      </c>
+      <c r="N12" s="9">
+        <f>AVERAGE(Sheet1!D12:G12)</f>
+        <v>4305.9324999999999</v>
+      </c>
+      <c r="O12" s="9">
+        <f>MEDIAN(Sheet1!D12:F12,Sheet1!G12)</f>
+        <v>3900.2999999999997</v>
+      </c>
+      <c r="P12" s="10">
+        <f>STDEV(Sheet1!D12:G12)</f>
+        <v>1451.4359064130263</v>
+      </c>
+      <c r="Q12" s="9">
+        <f>PRODUCT(Sheet1!D12,Sheet1!F12:G12)</f>
+        <v>92045222022.270508</v>
+      </c>
+      <c r="R12" s="9" t="str">
+        <f>IF(O12&gt;N12,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1822,8 +2213,40 @@
       <c r="J13" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A13," ",Sheet1!B13)</f>
+        <v>Alan Barton</v>
+      </c>
+      <c r="L13" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A13, " (",Sheet1!H13,")")</f>
+        <v>Alan (Cloud Engineer)</v>
+      </c>
+      <c r="M13" s="9">
+        <f>SUM(Sheet1!D13:G13)</f>
+        <v>19073.71</v>
+      </c>
+      <c r="N13" s="9">
+        <f>AVERAGE(Sheet1!D13:G13)</f>
+        <v>4768.4274999999998</v>
+      </c>
+      <c r="O13" s="9">
+        <f>MEDIAN(Sheet1!D13:F13,Sheet1!G13)</f>
+        <v>4712.0300000000007</v>
+      </c>
+      <c r="P13" s="10">
+        <f>STDEV(Sheet1!D13:G13)</f>
+        <v>561.4052111368992</v>
+      </c>
+      <c r="Q13" s="9">
+        <f>PRODUCT(Sheet1!D13,Sheet1!F13:G13)</f>
+        <v>103627345702.87041</v>
+      </c>
+      <c r="R13" s="9" t="str">
+        <f>IF(O13&gt;N13,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1854,8 +2277,40 @@
       <c r="J14" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A14," ",Sheet1!B14)</f>
+        <v>Leslie Leon</v>
+      </c>
+      <c r="L14" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A14, " (",Sheet1!H14,")")</f>
+        <v>Leslie (Data Scientist)</v>
+      </c>
+      <c r="M14" s="9">
+        <f>SUM(Sheet1!D14:G14)</f>
+        <v>20880.230000000003</v>
+      </c>
+      <c r="N14" s="9">
+        <f>AVERAGE(Sheet1!D14:G14)</f>
+        <v>5220.0575000000008</v>
+      </c>
+      <c r="O14" s="9">
+        <f>MEDIAN(Sheet1!D14:F14,Sheet1!G14)</f>
+        <v>5332.3250000000007</v>
+      </c>
+      <c r="P14" s="10">
+        <f>STDEV(Sheet1!D14:G14)</f>
+        <v>1131.6725805159615</v>
+      </c>
+      <c r="Q14" s="9">
+        <f>PRODUCT(Sheet1!D14,Sheet1!F14:G14)</f>
+        <v>124110078261.20549</v>
+      </c>
+      <c r="R14" s="9" t="str">
+        <f>IF(O14&gt;N14,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1886,8 +2341,40 @@
       <c r="J15" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A15," ",Sheet1!B15)</f>
+        <v>Ruben Chang</v>
+      </c>
+      <c r="L15" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A15, " (",Sheet1!H15,")")</f>
+        <v>Ruben (Business Analyst)</v>
+      </c>
+      <c r="M15" s="9">
+        <f>SUM(Sheet1!D15:G15)</f>
+        <v>20198.150000000001</v>
+      </c>
+      <c r="N15" s="9">
+        <f>AVERAGE(Sheet1!D15:G15)</f>
+        <v>5049.5375000000004</v>
+      </c>
+      <c r="O15" s="9">
+        <f>MEDIAN(Sheet1!D15:F15,Sheet1!G15)</f>
+        <v>5096.8850000000002</v>
+      </c>
+      <c r="P15" s="10">
+        <f>STDEV(Sheet1!D15:G15)</f>
+        <v>1600.0705218078108</v>
+      </c>
+      <c r="Q15" s="9">
+        <f>PRODUCT(Sheet1!D15,Sheet1!F15:G15)</f>
+        <v>80213777587.854767</v>
+      </c>
+      <c r="R15" s="9" t="str">
+        <f>IF(O15&gt;N15,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1918,8 +2405,40 @@
       <c r="J16" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A16," ",Sheet1!B16)</f>
+        <v>Kristine Myers</v>
+      </c>
+      <c r="L16" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A16, " (",Sheet1!H16,")")</f>
+        <v>Kristine (Product Manager)</v>
+      </c>
+      <c r="M16" s="9">
+        <f>SUM(Sheet1!D16:G16)</f>
+        <v>18639.140000000003</v>
+      </c>
+      <c r="N16" s="9">
+        <f>AVERAGE(Sheet1!D16:G16)</f>
+        <v>4659.7850000000008</v>
+      </c>
+      <c r="O16" s="9">
+        <f>MEDIAN(Sheet1!D16:F16,Sheet1!G16)</f>
+        <v>4450.8450000000003</v>
+      </c>
+      <c r="P16" s="10">
+        <f>STDEV(Sheet1!D16:G16)</f>
+        <v>1826.3813481764034</v>
+      </c>
+      <c r="Q16" s="9">
+        <f>PRODUCT(Sheet1!D16,Sheet1!F16:G16)</f>
+        <v>64316747311.785149</v>
+      </c>
+      <c r="R16" s="9" t="str">
+        <f>IF(O16&gt;N16,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1950,8 +2469,40 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A17," ",Sheet1!B17)</f>
+        <v>Stanley Cannon</v>
+      </c>
+      <c r="L17" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A17, " (",Sheet1!H17,")")</f>
+        <v>Stanley (Mobile App Developer)</v>
+      </c>
+      <c r="M17" s="9">
+        <f>SUM(Sheet1!D17:G17)</f>
+        <v>19397.739999999998</v>
+      </c>
+      <c r="N17" s="9">
+        <f>AVERAGE(Sheet1!D17:G17)</f>
+        <v>4849.4349999999995</v>
+      </c>
+      <c r="O17" s="9">
+        <f>MEDIAN(Sheet1!D17:F17,Sheet1!G17)</f>
+        <v>4447.9799999999996</v>
+      </c>
+      <c r="P17" s="10">
+        <f>STDEV(Sheet1!D17:G17)</f>
+        <v>1157.5710365099294</v>
+      </c>
+      <c r="Q17" s="9">
+        <f>PRODUCT(Sheet1!D17,Sheet1!F17:G17)</f>
+        <v>129420325465.51807</v>
+      </c>
+      <c r="R17" s="9" t="str">
+        <f>IF(O17&gt;N17,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1982,8 +2533,40 @@
       <c r="J18" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A18," ",Sheet1!B18)</f>
+        <v>Derek Stanley</v>
+      </c>
+      <c r="L18" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A18, " (",Sheet1!H18,")")</f>
+        <v>Derek (Backend Developer)</v>
+      </c>
+      <c r="M18" s="9">
+        <f>SUM(Sheet1!D18:G18)</f>
+        <v>21824.71</v>
+      </c>
+      <c r="N18" s="9">
+        <f>AVERAGE(Sheet1!D18:G18)</f>
+        <v>5456.1774999999998</v>
+      </c>
+      <c r="O18" s="9">
+        <f>MEDIAN(Sheet1!D18:F18,Sheet1!G18)</f>
+        <v>5436.165</v>
+      </c>
+      <c r="P18" s="10">
+        <f>STDEV(Sheet1!D18:G18)</f>
+        <v>968.5732299065819</v>
+      </c>
+      <c r="Q18" s="9">
+        <f>PRODUCT(Sheet1!D18,Sheet1!F18:G18)</f>
+        <v>183358561081.89267</v>
+      </c>
+      <c r="R18" s="9" t="str">
+        <f>IF(O18&gt;N18,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -2014,8 +2597,40 @@
       <c r="J19" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A19," ",Sheet1!B19)</f>
+        <v>Kevin Edwards</v>
+      </c>
+      <c r="L19" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A19, " (",Sheet1!H19,")")</f>
+        <v>Kevin (DevOps Engineer)</v>
+      </c>
+      <c r="M19" s="9">
+        <f>SUM(Sheet1!D19:G19)</f>
+        <v>18426.02</v>
+      </c>
+      <c r="N19" s="9">
+        <f>AVERAGE(Sheet1!D19:G19)</f>
+        <v>4606.5050000000001</v>
+      </c>
+      <c r="O19" s="9">
+        <f>MEDIAN(Sheet1!D19:F19,Sheet1!G19)</f>
+        <v>4403.5450000000001</v>
+      </c>
+      <c r="P19" s="10">
+        <f>STDEV(Sheet1!D19:G19)</f>
+        <v>713.64658940308993</v>
+      </c>
+      <c r="Q19" s="9">
+        <f>PRODUCT(Sheet1!D19,Sheet1!F19:G19)</f>
+        <v>99125739732.658188</v>
+      </c>
+      <c r="R19" s="9" t="str">
+        <f>IF(O19&gt;N19,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2046,8 +2661,40 @@
       <c r="J20" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A20," ",Sheet1!B20)</f>
+        <v>George Sanchez</v>
+      </c>
+      <c r="L20" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A20, " (",Sheet1!H20,")")</f>
+        <v>George (Frontend Developer)</v>
+      </c>
+      <c r="M20" s="9">
+        <f>SUM(Sheet1!D20:G20)</f>
+        <v>22764.21</v>
+      </c>
+      <c r="N20" s="9">
+        <f>AVERAGE(Sheet1!D20:G20)</f>
+        <v>5691.0524999999998</v>
+      </c>
+      <c r="O20" s="9">
+        <f>MEDIAN(Sheet1!D20:F20,Sheet1!G20)</f>
+        <v>6265.1</v>
+      </c>
+      <c r="P20" s="10">
+        <f>STDEV(Sheet1!D20:G20)</f>
+        <v>1344.8458723679091</v>
+      </c>
+      <c r="Q20" s="9">
+        <f>PRODUCT(Sheet1!D20,Sheet1!F20:G20)</f>
+        <v>155517713008.32782</v>
+      </c>
+      <c r="R20" s="9" t="str">
+        <f>IF(O20&gt;N20,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2078,8 +2725,40 @@
       <c r="J21" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A21," ",Sheet1!B21)</f>
+        <v>Amy Mason</v>
+      </c>
+      <c r="L21" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A21, " (",Sheet1!H21,")")</f>
+        <v>Amy (DevOps Engineer)</v>
+      </c>
+      <c r="M21" s="9">
+        <f>SUM(Sheet1!D21:G21)</f>
+        <v>24016.58</v>
+      </c>
+      <c r="N21" s="9">
+        <f>AVERAGE(Sheet1!D21:G21)</f>
+        <v>6004.1450000000004</v>
+      </c>
+      <c r="O21" s="9">
+        <f>MEDIAN(Sheet1!D21:F21,Sheet1!G21)</f>
+        <v>6666.5</v>
+      </c>
+      <c r="P21" s="10">
+        <f>STDEV(Sheet1!D21:G21)</f>
+        <v>1525.4829684507556</v>
+      </c>
+      <c r="Q21" s="9">
+        <f>PRODUCT(Sheet1!D21,Sheet1!F21:G21)</f>
+        <v>165968888894.27213</v>
+      </c>
+      <c r="R21" s="9" t="str">
+        <f>IF(O21&gt;N21,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2110,8 +2789,40 @@
       <c r="J22" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A22," ",Sheet1!B22)</f>
+        <v>Natalie Bryant</v>
+      </c>
+      <c r="L22" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A22, " (",Sheet1!H22,")")</f>
+        <v>Natalie (UI/UX Designer)</v>
+      </c>
+      <c r="M22" s="9">
+        <f>SUM(Sheet1!D22:G22)</f>
+        <v>22008.39</v>
+      </c>
+      <c r="N22" s="9">
+        <f>AVERAGE(Sheet1!D22:G22)</f>
+        <v>5502.0974999999999</v>
+      </c>
+      <c r="O22" s="9">
+        <f>MEDIAN(Sheet1!D22:F22,Sheet1!G22)</f>
+        <v>5659.01</v>
+      </c>
+      <c r="P22" s="10">
+        <f>STDEV(Sheet1!D22:G22)</f>
+        <v>1137.8845285404286</v>
+      </c>
+      <c r="Q22" s="9">
+        <f>PRODUCT(Sheet1!D22,Sheet1!F22:G22)</f>
+        <v>146461600787.33304</v>
+      </c>
+      <c r="R22" s="9" t="str">
+        <f>IF(O22&gt;N22,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
@@ -2142,8 +2853,40 @@
       <c r="J23" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A23," ",Sheet1!B23)</f>
+        <v>Amy Mercer</v>
+      </c>
+      <c r="L23" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A23, " (",Sheet1!H23,")")</f>
+        <v>Amy (Scrum Master)</v>
+      </c>
+      <c r="M23" s="9">
+        <f>SUM(Sheet1!D23:G23)</f>
+        <v>20493.810000000001</v>
+      </c>
+      <c r="N23" s="9">
+        <f>AVERAGE(Sheet1!D23:G23)</f>
+        <v>5123.4525000000003</v>
+      </c>
+      <c r="O23" s="9">
+        <f>MEDIAN(Sheet1!D23:F23,Sheet1!G23)</f>
+        <v>5027.5650000000005</v>
+      </c>
+      <c r="P23" s="10">
+        <f>STDEV(Sheet1!D23:G23)</f>
+        <v>547.97091007795893</v>
+      </c>
+      <c r="Q23" s="9">
+        <f>PRODUCT(Sheet1!D23,Sheet1!F23:G23)</f>
+        <v>147458259612.07111</v>
+      </c>
+      <c r="R23" s="9" t="str">
+        <f>IF(O23&gt;N23,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -2174,8 +2917,40 @@
       <c r="J24" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A24," ",Sheet1!B24)</f>
+        <v>Matthew Garza</v>
+      </c>
+      <c r="L24" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A24, " (",Sheet1!H24,")")</f>
+        <v>Matthew (Software Engineer)</v>
+      </c>
+      <c r="M24" s="9">
+        <f>SUM(Sheet1!D24:G24)</f>
+        <v>16724.97</v>
+      </c>
+      <c r="N24" s="9">
+        <f>AVERAGE(Sheet1!D24:G24)</f>
+        <v>4181.2425000000003</v>
+      </c>
+      <c r="O24" s="9">
+        <f>MEDIAN(Sheet1!D24:F24,Sheet1!G24)</f>
+        <v>4479.17</v>
+      </c>
+      <c r="P24" s="10">
+        <f>STDEV(Sheet1!D24:G24)</f>
+        <v>733.65308156625622</v>
+      </c>
+      <c r="Q24" s="9">
+        <f>PRODUCT(Sheet1!D24,Sheet1!F24:G24)</f>
+        <v>93739035957.534073</v>
+      </c>
+      <c r="R24" s="9" t="str">
+        <f>IF(O24&gt;N24,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -2206,8 +2981,40 @@
       <c r="J25" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A25," ",Sheet1!B25)</f>
+        <v>Theodore Wright</v>
+      </c>
+      <c r="L25" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A25, " (",Sheet1!H25,")")</f>
+        <v>Theodore (Frontend Developer)</v>
+      </c>
+      <c r="M25" s="9">
+        <f>SUM(Sheet1!D25:G25)</f>
+        <v>21774.05</v>
+      </c>
+      <c r="N25" s="9">
+        <f>AVERAGE(Sheet1!D25:G25)</f>
+        <v>5443.5124999999998</v>
+      </c>
+      <c r="O25" s="9">
+        <f>MEDIAN(Sheet1!D25:F25,Sheet1!G25)</f>
+        <v>5295.75</v>
+      </c>
+      <c r="P25" s="10">
+        <f>STDEV(Sheet1!D25:G25)</f>
+        <v>1384.0697617864726</v>
+      </c>
+      <c r="Q25" s="9">
+        <f>PRODUCT(Sheet1!D25,Sheet1!F25:G25)</f>
+        <v>126773526660.61113</v>
+      </c>
+      <c r="R25" s="9" t="str">
+        <f>IF(O25&gt;N25,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -2238,8 +3045,40 @@
       <c r="J26" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A26," ",Sheet1!B26)</f>
+        <v>Kayla West</v>
+      </c>
+      <c r="L26" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A26, " (",Sheet1!H26,")")</f>
+        <v>Kayla (Mobile App Developer)</v>
+      </c>
+      <c r="M26" s="9">
+        <f>SUM(Sheet1!D26:G26)</f>
+        <v>14105.11</v>
+      </c>
+      <c r="N26" s="9">
+        <f>AVERAGE(Sheet1!D26:G26)</f>
+        <v>3526.2775000000001</v>
+      </c>
+      <c r="O26" s="9">
+        <f>MEDIAN(Sheet1!D26:F26,Sheet1!G26)</f>
+        <v>3577.7</v>
+      </c>
+      <c r="P26" s="10">
+        <f>STDEV(Sheet1!D26:G26)</f>
+        <v>374.17851651985598</v>
+      </c>
+      <c r="Q26" s="9">
+        <f>PRODUCT(Sheet1!D26,Sheet1!F26:G26)</f>
+        <v>49787488719.748901</v>
+      </c>
+      <c r="R26" s="9" t="str">
+        <f>IF(O26&gt;N26,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -2270,8 +3109,40 @@
       <c r="J27" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A27," ",Sheet1!B27)</f>
+        <v>Jesse Carter</v>
+      </c>
+      <c r="L27" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A27, " (",Sheet1!H27,")")</f>
+        <v>Jesse (QA Engineer)</v>
+      </c>
+      <c r="M27" s="9">
+        <f>SUM(Sheet1!D27:G27)</f>
+        <v>20233.919999999998</v>
+      </c>
+      <c r="N27" s="9">
+        <f>AVERAGE(Sheet1!D27:G27)</f>
+        <v>5058.4799999999996</v>
+      </c>
+      <c r="O27" s="9">
+        <f>MEDIAN(Sheet1!D27:F27,Sheet1!G27)</f>
+        <v>5011.4549999999999</v>
+      </c>
+      <c r="P27" s="10">
+        <f>STDEV(Sheet1!D27:G27)</f>
+        <v>1304.2718354954509</v>
+      </c>
+      <c r="Q27" s="9">
+        <f>PRODUCT(Sheet1!D27,Sheet1!F27:G27)</f>
+        <v>112902533972.24257</v>
+      </c>
+      <c r="R27" s="9" t="str">
+        <f>IF(O27&gt;N27,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>33</v>
       </c>
@@ -2302,8 +3173,40 @@
       <c r="J28" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A28," ",Sheet1!B28)</f>
+        <v>Carlos Vega</v>
+      </c>
+      <c r="L28" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A28, " (",Sheet1!H28,")")</f>
+        <v>Carlos (Technical Support)</v>
+      </c>
+      <c r="M28" s="9">
+        <f>SUM(Sheet1!D28:G28)</f>
+        <v>17441.5</v>
+      </c>
+      <c r="N28" s="9">
+        <f>AVERAGE(Sheet1!D28:G28)</f>
+        <v>4360.375</v>
+      </c>
+      <c r="O28" s="9">
+        <f>MEDIAN(Sheet1!D28:F28,Sheet1!G28)</f>
+        <v>4136.25</v>
+      </c>
+      <c r="P28" s="10">
+        <f>STDEV(Sheet1!D28:G28)</f>
+        <v>855.06618958222452</v>
+      </c>
+      <c r="Q28" s="9">
+        <f>PRODUCT(Sheet1!D28,Sheet1!F28:G28)</f>
+        <v>94430736121.629593</v>
+      </c>
+      <c r="R28" s="9" t="str">
+        <f>IF(O28&gt;N28,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
@@ -2334,8 +3237,40 @@
       <c r="J29" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A29," ",Sheet1!B29)</f>
+        <v>Bridget Keith</v>
+      </c>
+      <c r="L29" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A29, " (",Sheet1!H29,")")</f>
+        <v>Bridget (UI/UX Designer)</v>
+      </c>
+      <c r="M29" s="9">
+        <f>SUM(Sheet1!D29:G29)</f>
+        <v>18843.07</v>
+      </c>
+      <c r="N29" s="9">
+        <f>AVERAGE(Sheet1!D29:G29)</f>
+        <v>4710.7674999999999</v>
+      </c>
+      <c r="O29" s="9">
+        <f>MEDIAN(Sheet1!D29:F29,Sheet1!G29)</f>
+        <v>4224.9949999999999</v>
+      </c>
+      <c r="P29" s="10">
+        <f>STDEV(Sheet1!D29:G29)</f>
+        <v>1519.7799713856623</v>
+      </c>
+      <c r="Q29" s="9">
+        <f>PRODUCT(Sheet1!D29,Sheet1!F29:G29)</f>
+        <v>92860492703.391556</v>
+      </c>
+      <c r="R29" s="9" t="str">
+        <f>IF(O29&gt;N29,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
@@ -2366,8 +3301,40 @@
       <c r="J30" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A30," ",Sheet1!B30)</f>
+        <v>William Duncan</v>
+      </c>
+      <c r="L30" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A30, " (",Sheet1!H30,")")</f>
+        <v>William (Security Analyst)</v>
+      </c>
+      <c r="M30" s="9">
+        <f>SUM(Sheet1!D30:G30)</f>
+        <v>18384.02</v>
+      </c>
+      <c r="N30" s="9">
+        <f>AVERAGE(Sheet1!D30:G30)</f>
+        <v>4596.0050000000001</v>
+      </c>
+      <c r="O30" s="9">
+        <f>MEDIAN(Sheet1!D30:F30,Sheet1!G30)</f>
+        <v>4342.2350000000006</v>
+      </c>
+      <c r="P30" s="10">
+        <f>STDEV(Sheet1!D30:G30)</f>
+        <v>1538.4899608923899</v>
+      </c>
+      <c r="Q30" s="9">
+        <f>PRODUCT(Sheet1!D30,Sheet1!F30:G30)</f>
+        <v>70240152244.86557</v>
+      </c>
+      <c r="R30" s="9" t="str">
+        <f>IF(O30&gt;N30,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
@@ -2398,8 +3365,40 @@
       <c r="J31" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A31," ",Sheet1!B31)</f>
+        <v>John Hernandez</v>
+      </c>
+      <c r="L31" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A31, " (",Sheet1!H31,")")</f>
+        <v>John (UI/UX Designer)</v>
+      </c>
+      <c r="M31" s="9">
+        <f>SUM(Sheet1!D31:G31)</f>
+        <v>15916.75</v>
+      </c>
+      <c r="N31" s="9">
+        <f>AVERAGE(Sheet1!D31:G31)</f>
+        <v>3979.1875</v>
+      </c>
+      <c r="O31" s="9">
+        <f>MEDIAN(Sheet1!D31:F31,Sheet1!G31)</f>
+        <v>4064.09</v>
+      </c>
+      <c r="P31" s="10">
+        <f>STDEV(Sheet1!D31:G31)</f>
+        <v>706.83200726316159</v>
+      </c>
+      <c r="Q31" s="9">
+        <f>PRODUCT(Sheet1!D31,Sheet1!F31:G31)</f>
+        <v>50275890927.047287</v>
+      </c>
+      <c r="R31" s="9" t="str">
+        <f>IF(O31&gt;N31,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -2430,8 +3429,40 @@
       <c r="J32" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A32," ",Sheet1!B32)</f>
+        <v>Jesse Murray</v>
+      </c>
+      <c r="L32" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A32, " (",Sheet1!H32,")")</f>
+        <v>Jesse (Security Analyst)</v>
+      </c>
+      <c r="M32" s="9">
+        <f>SUM(Sheet1!D32:G32)</f>
+        <v>18740.980000000003</v>
+      </c>
+      <c r="N32" s="9">
+        <f>AVERAGE(Sheet1!D32:G32)</f>
+        <v>4685.2450000000008</v>
+      </c>
+      <c r="O32" s="9">
+        <f>MEDIAN(Sheet1!D32:F32,Sheet1!G32)</f>
+        <v>4510.5300000000007</v>
+      </c>
+      <c r="P32" s="10">
+        <f>STDEV(Sheet1!D32:G32)</f>
+        <v>1679.5520275259892</v>
+      </c>
+      <c r="Q32" s="9">
+        <f>PRODUCT(Sheet1!D32,Sheet1!F32:G32)</f>
+        <v>111367491422.6749</v>
+      </c>
+      <c r="R32" s="9" t="str">
+        <f>IF(O32&gt;N32,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
@@ -2462,8 +3493,40 @@
       <c r="J33" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A33," ",Sheet1!B33)</f>
+        <v>Stephen Haynes</v>
+      </c>
+      <c r="L33" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A33, " (",Sheet1!H33,")")</f>
+        <v>Stephen (Technical Support)</v>
+      </c>
+      <c r="M33" s="9">
+        <f>SUM(Sheet1!D33:G33)</f>
+        <v>20347.879999999997</v>
+      </c>
+      <c r="N33" s="9">
+        <f>AVERAGE(Sheet1!D33:G33)</f>
+        <v>5086.9699999999993</v>
+      </c>
+      <c r="O33" s="9">
+        <f>MEDIAN(Sheet1!D33:F33,Sheet1!G33)</f>
+        <v>5137.9650000000001</v>
+      </c>
+      <c r="P33" s="10">
+        <f>STDEV(Sheet1!D33:G33)</f>
+        <v>2070.2973758536878</v>
+      </c>
+      <c r="Q33" s="9">
+        <f>PRODUCT(Sheet1!D33,Sheet1!F33:G33)</f>
+        <v>76005189473.290848</v>
+      </c>
+      <c r="R33" s="9" t="str">
+        <f>IF(O33&gt;N33,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
@@ -2494,8 +3557,40 @@
       <c r="J34" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A34," ",Sheet1!B34)</f>
+        <v>Samuel Smith</v>
+      </c>
+      <c r="L34" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A34, " (",Sheet1!H34,")")</f>
+        <v>Samuel (System Administrator)</v>
+      </c>
+      <c r="M34" s="9">
+        <f>SUM(Sheet1!D34:G34)</f>
+        <v>18052.490000000002</v>
+      </c>
+      <c r="N34" s="9">
+        <f>AVERAGE(Sheet1!D34:G34)</f>
+        <v>4513.1225000000004</v>
+      </c>
+      <c r="O34" s="9">
+        <f>MEDIAN(Sheet1!D34:F34,Sheet1!G34)</f>
+        <v>4648.24</v>
+      </c>
+      <c r="P34" s="10">
+        <f>STDEV(Sheet1!D34:G34)</f>
+        <v>1069.434287785677</v>
+      </c>
+      <c r="Q34" s="9">
+        <f>PRODUCT(Sheet1!D34,Sheet1!F34:G34)</f>
+        <v>68690336616.366364</v>
+      </c>
+      <c r="R34" s="9" t="str">
+        <f>IF(O34&gt;N34,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
@@ -2526,8 +3621,40 @@
       <c r="J35" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A35," ",Sheet1!B35)</f>
+        <v>Russell Moore</v>
+      </c>
+      <c r="L35" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A35, " (",Sheet1!H35,")")</f>
+        <v>Russell (Full Stack Developer)</v>
+      </c>
+      <c r="M35" s="9">
+        <f>SUM(Sheet1!D35:G35)</f>
+        <v>18526.12</v>
+      </c>
+      <c r="N35" s="9">
+        <f>AVERAGE(Sheet1!D35:G35)</f>
+        <v>4631.53</v>
+      </c>
+      <c r="O35" s="9">
+        <f>MEDIAN(Sheet1!D35:F35,Sheet1!G35)</f>
+        <v>4393.3999999999996</v>
+      </c>
+      <c r="P35" s="10">
+        <f>STDEV(Sheet1!D35:G35)</f>
+        <v>1087.8079752725971</v>
+      </c>
+      <c r="Q35" s="9">
+        <f>PRODUCT(Sheet1!D35,Sheet1!F35:G35)</f>
+        <v>85087773454.95694</v>
+      </c>
+      <c r="R35" s="9" t="str">
+        <f>IF(O35&gt;N35,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -2558,8 +3685,40 @@
       <c r="J36" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A36," ",Sheet1!B36)</f>
+        <v>Brenda Delgado</v>
+      </c>
+      <c r="L36" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A36, " (",Sheet1!H36,")")</f>
+        <v>Brenda (Business Analyst)</v>
+      </c>
+      <c r="M36" s="9">
+        <f>SUM(Sheet1!D36:G36)</f>
+        <v>17212.75</v>
+      </c>
+      <c r="N36" s="9">
+        <f>AVERAGE(Sheet1!D36:G36)</f>
+        <v>4303.1875</v>
+      </c>
+      <c r="O36" s="9">
+        <f>MEDIAN(Sheet1!D36:F36,Sheet1!G36)</f>
+        <v>4527.6350000000002</v>
+      </c>
+      <c r="P36" s="10">
+        <f>STDEV(Sheet1!D36:G36)</f>
+        <v>861.28250074622201</v>
+      </c>
+      <c r="Q36" s="9">
+        <f>PRODUCT(Sheet1!D36,Sheet1!F36:G36)</f>
+        <v>103003129353.65613</v>
+      </c>
+      <c r="R36" s="9" t="str">
+        <f>IF(O36&gt;N36,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
@@ -2590,8 +3749,40 @@
       <c r="J37" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A37," ",Sheet1!B37)</f>
+        <v>Lindsey Kline</v>
+      </c>
+      <c r="L37" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A37, " (",Sheet1!H37,")")</f>
+        <v>Lindsey (Scrum Master)</v>
+      </c>
+      <c r="M37" s="9">
+        <f>SUM(Sheet1!D37:G37)</f>
+        <v>18057.39</v>
+      </c>
+      <c r="N37" s="9">
+        <f>AVERAGE(Sheet1!D37:G37)</f>
+        <v>4514.3474999999999</v>
+      </c>
+      <c r="O37" s="9">
+        <f>MEDIAN(Sheet1!D37:F37,Sheet1!G37)</f>
+        <v>4124.8950000000004</v>
+      </c>
+      <c r="P37" s="10">
+        <f>STDEV(Sheet1!D37:G37)</f>
+        <v>1695.1464024556487</v>
+      </c>
+      <c r="Q37" s="9">
+        <f>PRODUCT(Sheet1!D37,Sheet1!F37:G37)</f>
+        <v>104296013508.78088</v>
+      </c>
+      <c r="R37" s="9" t="str">
+        <f>IF(O37&gt;N37,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
@@ -2622,8 +3813,40 @@
       <c r="J38" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A38," ",Sheet1!B38)</f>
+        <v>Shelia Sanchez</v>
+      </c>
+      <c r="L38" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A38, " (",Sheet1!H38,")")</f>
+        <v>Shelia (Software Engineer)</v>
+      </c>
+      <c r="M38" s="9">
+        <f>SUM(Sheet1!D38:G38)</f>
+        <v>20384.18</v>
+      </c>
+      <c r="N38" s="9">
+        <f>AVERAGE(Sheet1!D38:G38)</f>
+        <v>5096.0450000000001</v>
+      </c>
+      <c r="O38" s="9">
+        <f>MEDIAN(Sheet1!D38:F38,Sheet1!G38)</f>
+        <v>4864.1549999999997</v>
+      </c>
+      <c r="P38" s="10">
+        <f>STDEV(Sheet1!D38:G38)</f>
+        <v>1540.3343826260568</v>
+      </c>
+      <c r="Q38" s="9">
+        <f>PRODUCT(Sheet1!D38,Sheet1!F38:G38)</f>
+        <v>100175530665.01782</v>
+      </c>
+      <c r="R38" s="9" t="str">
+        <f>IF(O38&gt;N38,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
@@ -2654,8 +3877,40 @@
       <c r="J39" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A39," ",Sheet1!B39)</f>
+        <v>Holly Christensen</v>
+      </c>
+      <c r="L39" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A39, " (",Sheet1!H39,")")</f>
+        <v>Holly (Technical Support)</v>
+      </c>
+      <c r="M39" s="9">
+        <f>SUM(Sheet1!D39:G39)</f>
+        <v>21184.25</v>
+      </c>
+      <c r="N39" s="9">
+        <f>AVERAGE(Sheet1!D39:G39)</f>
+        <v>5296.0625</v>
+      </c>
+      <c r="O39" s="9">
+        <f>MEDIAN(Sheet1!D39:F39,Sheet1!G39)</f>
+        <v>5232</v>
+      </c>
+      <c r="P39" s="10">
+        <f>STDEV(Sheet1!D39:G39)</f>
+        <v>1067.8809072605738</v>
+      </c>
+      <c r="Q39" s="9">
+        <f>PRODUCT(Sheet1!D39,Sheet1!F39:G39)</f>
+        <v>181642058416.75967</v>
+      </c>
+      <c r="R39" s="9" t="str">
+        <f>IF(O39&gt;N39,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +3941,40 @@
       <c r="J40" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A40," ",Sheet1!B40)</f>
+        <v>Jason Johnson</v>
+      </c>
+      <c r="L40" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A40, " (",Sheet1!H40,")")</f>
+        <v>Jason (Frontend Developer)</v>
+      </c>
+      <c r="M40" s="9">
+        <f>SUM(Sheet1!D40:G40)</f>
+        <v>19594.850000000002</v>
+      </c>
+      <c r="N40" s="9">
+        <f>AVERAGE(Sheet1!D40:G40)</f>
+        <v>4898.7125000000005</v>
+      </c>
+      <c r="O40" s="9">
+        <f>MEDIAN(Sheet1!D40:F40,Sheet1!G40)</f>
+        <v>4757.7700000000004</v>
+      </c>
+      <c r="P40" s="10">
+        <f>STDEV(Sheet1!D40:G40)</f>
+        <v>748.48175080736246</v>
+      </c>
+      <c r="Q40" s="9">
+        <f>PRODUCT(Sheet1!D40,Sheet1!F40:G40)</f>
+        <v>95383513583.054611</v>
+      </c>
+      <c r="R40" s="9" t="str">
+        <f>IF(O40&gt;N40,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>45</v>
       </c>
@@ -2718,8 +4005,40 @@
       <c r="J41" s="8">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A41," ",Sheet1!B41)</f>
+        <v>Melissa Garcia</v>
+      </c>
+      <c r="L41" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A41, " (",Sheet1!H41,")")</f>
+        <v>Melissa (Frontend Developer)</v>
+      </c>
+      <c r="M41" s="9">
+        <f>SUM(Sheet1!D41:G41)</f>
+        <v>18702.18</v>
+      </c>
+      <c r="N41" s="9">
+        <f>AVERAGE(Sheet1!D41:G41)</f>
+        <v>4675.5450000000001</v>
+      </c>
+      <c r="O41" s="9">
+        <f>MEDIAN(Sheet1!D41:F41,Sheet1!G41)</f>
+        <v>4616.6750000000002</v>
+      </c>
+      <c r="P41" s="10">
+        <f>STDEV(Sheet1!D41:G41)</f>
+        <v>1006.9539666571977</v>
+      </c>
+      <c r="Q41" s="9">
+        <f>PRODUCT(Sheet1!D41,Sheet1!F41:G41)</f>
+        <v>115557249581.30246</v>
+      </c>
+      <c r="R41" s="9" t="str">
+        <f>IF(O41&gt;N41,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>16</v>
       </c>
@@ -2750,8 +4069,40 @@
       <c r="J42" s="8">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A42," ",Sheet1!B42)</f>
+        <v>Amanda Hayes</v>
+      </c>
+      <c r="L42" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A42, " (",Sheet1!H42,")")</f>
+        <v>Amanda (Software Engineer)</v>
+      </c>
+      <c r="M42" s="9">
+        <f>SUM(Sheet1!D42:G42)</f>
+        <v>18176.54</v>
+      </c>
+      <c r="N42" s="9">
+        <f>AVERAGE(Sheet1!D42:G42)</f>
+        <v>4544.1350000000002</v>
+      </c>
+      <c r="O42" s="9">
+        <f>MEDIAN(Sheet1!D42:F42,Sheet1!G42)</f>
+        <v>4316.99</v>
+      </c>
+      <c r="P42" s="10">
+        <f>STDEV(Sheet1!D42:G42)</f>
+        <v>1045.0258708280862</v>
+      </c>
+      <c r="Q42" s="9">
+        <f>PRODUCT(Sheet1!D42,Sheet1!F42:G42)</f>
+        <v>66134319202.563507</v>
+      </c>
+      <c r="R42" s="9" t="str">
+        <f>IF(O42&gt;N42,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
@@ -2782,8 +4133,40 @@
       <c r="J43" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A43," ",Sheet1!B43)</f>
+        <v>Abigail Wright</v>
+      </c>
+      <c r="L43" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A43, " (",Sheet1!H43,")")</f>
+        <v>Abigail (Scrum Master)</v>
+      </c>
+      <c r="M43" s="9">
+        <f>SUM(Sheet1!D43:G43)</f>
+        <v>24252.629999999997</v>
+      </c>
+      <c r="N43" s="9">
+        <f>AVERAGE(Sheet1!D43:G43)</f>
+        <v>6063.1574999999993</v>
+      </c>
+      <c r="O43" s="9">
+        <f>MEDIAN(Sheet1!D43:F43,Sheet1!G43)</f>
+        <v>6148.6299999999992</v>
+      </c>
+      <c r="P43" s="10">
+        <f>STDEV(Sheet1!D43:G43)</f>
+        <v>538.28865009862488</v>
+      </c>
+      <c r="Q43" s="9">
+        <f>PRODUCT(Sheet1!D43,Sheet1!F43:G43)</f>
+        <v>202739188049.12485</v>
+      </c>
+      <c r="R43" s="9" t="str">
+        <f>IF(O43&gt;N43,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
@@ -2814,8 +4197,40 @@
       <c r="J44" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A44," ",Sheet1!B44)</f>
+        <v>Deborah Warren</v>
+      </c>
+      <c r="L44" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A44, " (",Sheet1!H44,")")</f>
+        <v>Deborah (Frontend Developer)</v>
+      </c>
+      <c r="M44" s="9">
+        <f>SUM(Sheet1!D44:G44)</f>
+        <v>21204.370000000003</v>
+      </c>
+      <c r="N44" s="9">
+        <f>AVERAGE(Sheet1!D44:G44)</f>
+        <v>5301.0925000000007</v>
+      </c>
+      <c r="O44" s="9">
+        <f>MEDIAN(Sheet1!D44:F44,Sheet1!G44)</f>
+        <v>5176.9400000000005</v>
+      </c>
+      <c r="P44" s="10">
+        <f>STDEV(Sheet1!D44:G44)</f>
+        <v>1203.3860243046106</v>
+      </c>
+      <c r="Q44" s="9">
+        <f>PRODUCT(Sheet1!D44,Sheet1!F44:G44)</f>
+        <v>174873133677.57263</v>
+      </c>
+      <c r="R44" s="9" t="str">
+        <f>IF(O44&gt;N44,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>48</v>
       </c>
@@ -2846,8 +4261,40 @@
       <c r="J45" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A45," ",Sheet1!B45)</f>
+        <v>Megan Mullins</v>
+      </c>
+      <c r="L45" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A45, " (",Sheet1!H45,")")</f>
+        <v>Megan (System Administrator)</v>
+      </c>
+      <c r="M45" s="9">
+        <f>SUM(Sheet1!D45:G45)</f>
+        <v>19659.090000000004</v>
+      </c>
+      <c r="N45" s="9">
+        <f>AVERAGE(Sheet1!D45:G45)</f>
+        <v>4914.7725000000009</v>
+      </c>
+      <c r="O45" s="9">
+        <f>MEDIAN(Sheet1!D45:F45,Sheet1!G45)</f>
+        <v>4765.6900000000005</v>
+      </c>
+      <c r="P45" s="10">
+        <f>STDEV(Sheet1!D45:G45)</f>
+        <v>1224.2083787867391</v>
+      </c>
+      <c r="Q45" s="9">
+        <f>PRODUCT(Sheet1!D45,Sheet1!F45:G45)</f>
+        <v>106737019199.38828</v>
+      </c>
+      <c r="R45" s="9" t="str">
+        <f>IF(O45&gt;N45,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>49</v>
       </c>
@@ -2878,8 +4325,40 @@
       <c r="J46" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A46," ",Sheet1!B46)</f>
+        <v>Lynn Diaz</v>
+      </c>
+      <c r="L46" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A46, " (",Sheet1!H46,")")</f>
+        <v>Lynn (Mobile App Developer)</v>
+      </c>
+      <c r="M46" s="9">
+        <f>SUM(Sheet1!D46:G46)</f>
+        <v>18686.379999999997</v>
+      </c>
+      <c r="N46" s="9">
+        <f>AVERAGE(Sheet1!D46:G46)</f>
+        <v>4671.5949999999993</v>
+      </c>
+      <c r="O46" s="9">
+        <f>MEDIAN(Sheet1!D46:F46,Sheet1!G46)</f>
+        <v>4463.1149999999998</v>
+      </c>
+      <c r="P46" s="10">
+        <f>STDEV(Sheet1!D46:G46)</f>
+        <v>1472.7776651506738</v>
+      </c>
+      <c r="Q46" s="9">
+        <f>PRODUCT(Sheet1!D46,Sheet1!F46:G46)</f>
+        <v>128946644828.8494</v>
+      </c>
+      <c r="R46" s="9" t="str">
+        <f>IF(O46&gt;N46,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>50</v>
       </c>
@@ -2910,8 +4389,40 @@
       <c r="J47" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A47," ",Sheet1!B47)</f>
+        <v>Suzanne Robbins</v>
+      </c>
+      <c r="L47" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A47, " (",Sheet1!H47,")")</f>
+        <v>Suzanne (Data Scientist)</v>
+      </c>
+      <c r="M47" s="9">
+        <f>SUM(Sheet1!D47:G47)</f>
+        <v>22555.739999999998</v>
+      </c>
+      <c r="N47" s="9">
+        <f>AVERAGE(Sheet1!D47:G47)</f>
+        <v>5638.9349999999995</v>
+      </c>
+      <c r="O47" s="9">
+        <f>MEDIAN(Sheet1!D47:F47,Sheet1!G47)</f>
+        <v>5605.87</v>
+      </c>
+      <c r="P47" s="10">
+        <f>STDEV(Sheet1!D47:G47)</f>
+        <v>466.24504962519467</v>
+      </c>
+      <c r="Q47" s="9">
+        <f>PRODUCT(Sheet1!D47,Sheet1!F47:G47)</f>
+        <v>161034640803.93109</v>
+      </c>
+      <c r="R47" s="9" t="str">
+        <f>IF(O47&gt;N47,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
@@ -2942,8 +4453,40 @@
       <c r="J48" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A48," ",Sheet1!B48)</f>
+        <v>Michelle Goodman</v>
+      </c>
+      <c r="L48" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A48, " (",Sheet1!H48,")")</f>
+        <v>Michelle (System Administrator)</v>
+      </c>
+      <c r="M48" s="9">
+        <f>SUM(Sheet1!D48:G48)</f>
+        <v>23021.87</v>
+      </c>
+      <c r="N48" s="9">
+        <f>AVERAGE(Sheet1!D48:G48)</f>
+        <v>5755.4674999999997</v>
+      </c>
+      <c r="O48" s="9">
+        <f>MEDIAN(Sheet1!D48:F48,Sheet1!G48)</f>
+        <v>6104.77</v>
+      </c>
+      <c r="P48" s="10">
+        <f>STDEV(Sheet1!D48:G48)</f>
+        <v>1245.4776305598587</v>
+      </c>
+      <c r="Q48" s="9">
+        <f>PRODUCT(Sheet1!D48,Sheet1!F48:G48)</f>
+        <v>249717821655.48135</v>
+      </c>
+      <c r="R48" s="9" t="str">
+        <f>IF(O48&gt;N48,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -2974,8 +4517,40 @@
       <c r="J49" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A49," ",Sheet1!B49)</f>
+        <v>Elizabeth Richards</v>
+      </c>
+      <c r="L49" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A49, " (",Sheet1!H49,")")</f>
+        <v>Elizabeth (Mobile App Developer)</v>
+      </c>
+      <c r="M49" s="9">
+        <f>SUM(Sheet1!D49:G49)</f>
+        <v>19871.43</v>
+      </c>
+      <c r="N49" s="9">
+        <f>AVERAGE(Sheet1!D49:G49)</f>
+        <v>4967.8575000000001</v>
+      </c>
+      <c r="O49" s="9">
+        <f>MEDIAN(Sheet1!D49:F49,Sheet1!G49)</f>
+        <v>4922.0349999999999</v>
+      </c>
+      <c r="P49" s="10">
+        <f>STDEV(Sheet1!D49:G49)</f>
+        <v>1805.9322798557537</v>
+      </c>
+      <c r="Q49" s="9">
+        <f>PRODUCT(Sheet1!D49,Sheet1!F49:G49)</f>
+        <v>77273871180.187515</v>
+      </c>
+      <c r="R49" s="9" t="str">
+        <f>IF(O49&gt;N49,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
@@ -3006,8 +4581,40 @@
       <c r="J50" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A50," ",Sheet1!B50)</f>
+        <v>Jeffrey Miller</v>
+      </c>
+      <c r="L50" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A50, " (",Sheet1!H50,")")</f>
+        <v>Jeffrey (QA Engineer)</v>
+      </c>
+      <c r="M50" s="9">
+        <f>SUM(Sheet1!D50:G50)</f>
+        <v>16669.78</v>
+      </c>
+      <c r="N50" s="9">
+        <f>AVERAGE(Sheet1!D50:G50)</f>
+        <v>4167.4449999999997</v>
+      </c>
+      <c r="O50" s="9">
+        <f>MEDIAN(Sheet1!D50:F50,Sheet1!G50)</f>
+        <v>4459.125</v>
+      </c>
+      <c r="P50" s="10">
+        <f>STDEV(Sheet1!D50:G50)</f>
+        <v>662.541268676909</v>
+      </c>
+      <c r="Q50" s="9">
+        <f>PRODUCT(Sheet1!D50,Sheet1!F50:G50)</f>
+        <v>90952122667.10614</v>
+      </c>
+      <c r="R50" s="9" t="str">
+        <f>IF(O50&gt;N50,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>54</v>
       </c>
@@ -3038,8 +4645,40 @@
       <c r="J51" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A51," ",Sheet1!B51)</f>
+        <v>Catherine Welch</v>
+      </c>
+      <c r="L51" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A51, " (",Sheet1!H51,")")</f>
+        <v>Catherine (Product Manager)</v>
+      </c>
+      <c r="M51" s="9">
+        <f>SUM(Sheet1!D51:G51)</f>
+        <v>21733.079999999998</v>
+      </c>
+      <c r="N51" s="9">
+        <f>AVERAGE(Sheet1!D51:G51)</f>
+        <v>5433.2699999999995</v>
+      </c>
+      <c r="O51" s="9">
+        <f>MEDIAN(Sheet1!D51:F51,Sheet1!G51)</f>
+        <v>5708.68</v>
+      </c>
+      <c r="P51" s="10">
+        <f>STDEV(Sheet1!D51:G51)</f>
+        <v>1404.8083472369722</v>
+      </c>
+      <c r="Q51" s="9">
+        <f>PRODUCT(Sheet1!D51,Sheet1!F51:G51)</f>
+        <v>214977580537.83859</v>
+      </c>
+      <c r="R51" s="9" t="str">
+        <f>IF(O51&gt;N51,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>55</v>
       </c>
@@ -3070,8 +4709,40 @@
       <c r="J52" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A52," ",Sheet1!B52)</f>
+        <v>Nicholas Nelson</v>
+      </c>
+      <c r="L52" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A52, " (",Sheet1!H52,")")</f>
+        <v>Nicholas (DevOps Engineer)</v>
+      </c>
+      <c r="M52" s="9">
+        <f>SUM(Sheet1!D52:G52)</f>
+        <v>20662.669999999998</v>
+      </c>
+      <c r="N52" s="9">
+        <f>AVERAGE(Sheet1!D52:G52)</f>
+        <v>5165.6674999999996</v>
+      </c>
+      <c r="O52" s="9">
+        <f>MEDIAN(Sheet1!D52:F52,Sheet1!G52)</f>
+        <v>4970.2999999999993</v>
+      </c>
+      <c r="P52" s="10">
+        <f>STDEV(Sheet1!D52:G52)</f>
+        <v>1270.4741508947243</v>
+      </c>
+      <c r="Q52" s="9">
+        <f>PRODUCT(Sheet1!D52,Sheet1!F52:G52)</f>
+        <v>120864070328.31143</v>
+      </c>
+      <c r="R52" s="9" t="str">
+        <f>IF(O52&gt;N52,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
@@ -3102,8 +4773,40 @@
       <c r="J53" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A53," ",Sheet1!B53)</f>
+        <v>James Diaz</v>
+      </c>
+      <c r="L53" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A53, " (",Sheet1!H53,")")</f>
+        <v>James (Data Scientist)</v>
+      </c>
+      <c r="M53" s="9">
+        <f>SUM(Sheet1!D53:G53)</f>
+        <v>22507.42</v>
+      </c>
+      <c r="N53" s="9">
+        <f>AVERAGE(Sheet1!D53:G53)</f>
+        <v>5626.8549999999996</v>
+      </c>
+      <c r="O53" s="9">
+        <f>MEDIAN(Sheet1!D53:F53,Sheet1!G53)</f>
+        <v>5606.3249999999998</v>
+      </c>
+      <c r="P53" s="10">
+        <f>STDEV(Sheet1!D53:G53)</f>
+        <v>1198.1333971501972</v>
+      </c>
+      <c r="Q53" s="9">
+        <f>PRODUCT(Sheet1!D53,Sheet1!F53:G53)</f>
+        <v>214333731457.7637</v>
+      </c>
+      <c r="R53" s="9" t="str">
+        <f>IF(O53&gt;N53,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>57</v>
       </c>
@@ -3134,8 +4837,40 @@
       <c r="J54" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A54," ",Sheet1!B54)</f>
+        <v>Lori Evans</v>
+      </c>
+      <c r="L54" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A54, " (",Sheet1!H54,")")</f>
+        <v>Lori (Technical Support)</v>
+      </c>
+      <c r="M54" s="9">
+        <f>SUM(Sheet1!D54:G54)</f>
+        <v>19224.239999999998</v>
+      </c>
+      <c r="N54" s="9">
+        <f>AVERAGE(Sheet1!D54:G54)</f>
+        <v>4806.0599999999995</v>
+      </c>
+      <c r="O54" s="9">
+        <f>MEDIAN(Sheet1!D54:F54,Sheet1!G54)</f>
+        <v>4594.3999999999996</v>
+      </c>
+      <c r="P54" s="10">
+        <f>STDEV(Sheet1!D54:G54)</f>
+        <v>1043.4307881535187</v>
+      </c>
+      <c r="Q54" s="9">
+        <f>PRODUCT(Sheet1!D54,Sheet1!F54:G54)</f>
+        <v>79763929709.800705</v>
+      </c>
+      <c r="R54" s="9" t="str">
+        <f>IF(O54&gt;N54,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>58</v>
       </c>
@@ -3166,8 +4901,40 @@
       <c r="J55" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A55," ",Sheet1!B55)</f>
+        <v>Zachary Lopez</v>
+      </c>
+      <c r="L55" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A55, " (",Sheet1!H55,")")</f>
+        <v>Zachary (System Administrator)</v>
+      </c>
+      <c r="M55" s="9">
+        <f>SUM(Sheet1!D55:G55)</f>
+        <v>23228.14</v>
+      </c>
+      <c r="N55" s="9">
+        <f>AVERAGE(Sheet1!D55:G55)</f>
+        <v>5807.0349999999999</v>
+      </c>
+      <c r="O55" s="9">
+        <f>MEDIAN(Sheet1!D55:F55,Sheet1!G55)</f>
+        <v>5764.0450000000001</v>
+      </c>
+      <c r="P55" s="10">
+        <f>STDEV(Sheet1!D55:G55)</f>
+        <v>561.05101458482966</v>
+      </c>
+      <c r="Q55" s="9">
+        <f>PRODUCT(Sheet1!D55,Sheet1!F55:G55)</f>
+        <v>213121017852.15479</v>
+      </c>
+      <c r="R55" s="9" t="str">
+        <f>IF(O55&gt;N55,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>59</v>
       </c>
@@ -3198,8 +4965,40 @@
       <c r="J56" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A56," ",Sheet1!B56)</f>
+        <v>Michael Gray</v>
+      </c>
+      <c r="L56" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A56, " (",Sheet1!H56,")")</f>
+        <v>Michael (Full Stack Developer)</v>
+      </c>
+      <c r="M56" s="9">
+        <f>SUM(Sheet1!D56:G56)</f>
+        <v>21206.22</v>
+      </c>
+      <c r="N56" s="9">
+        <f>AVERAGE(Sheet1!D56:G56)</f>
+        <v>5301.5550000000003</v>
+      </c>
+      <c r="O56" s="9">
+        <f>MEDIAN(Sheet1!D56:F56,Sheet1!G56)</f>
+        <v>5829.6749999999993</v>
+      </c>
+      <c r="P56" s="10">
+        <f>STDEV(Sheet1!D56:G56)</f>
+        <v>1559.00287296079</v>
+      </c>
+      <c r="Q56" s="9">
+        <f>PRODUCT(Sheet1!D56,Sheet1!F56:G56)</f>
+        <v>102897099516.02682</v>
+      </c>
+      <c r="R56" s="9" t="str">
+        <f>IF(O56&gt;N56,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
@@ -3230,8 +5029,40 @@
       <c r="J57" s="8">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A57," ",Sheet1!B57)</f>
+        <v>Charles Bradford</v>
+      </c>
+      <c r="L57" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A57, " (",Sheet1!H57,")")</f>
+        <v>Charles (Scrum Master)</v>
+      </c>
+      <c r="M57" s="9">
+        <f>SUM(Sheet1!D57:G57)</f>
+        <v>17344.05</v>
+      </c>
+      <c r="N57" s="9">
+        <f>AVERAGE(Sheet1!D57:G57)</f>
+        <v>4336.0124999999998</v>
+      </c>
+      <c r="O57" s="9">
+        <f>MEDIAN(Sheet1!D57:F57,Sheet1!G57)</f>
+        <v>4358.2250000000004</v>
+      </c>
+      <c r="P57" s="10">
+        <f>STDEV(Sheet1!D57:G57)</f>
+        <v>1317.1260867604919</v>
+      </c>
+      <c r="Q57" s="9">
+        <f>PRODUCT(Sheet1!D57,Sheet1!F57:G57)</f>
+        <v>101798928932.99014</v>
+      </c>
+      <c r="R57" s="9" t="str">
+        <f>IF(O57&gt;N57,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -3262,8 +5093,40 @@
       <c r="J58" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A58," ",Sheet1!B58)</f>
+        <v>Joshua Peters</v>
+      </c>
+      <c r="L58" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A58, " (",Sheet1!H58,")")</f>
+        <v>Joshua (Backend Developer)</v>
+      </c>
+      <c r="M58" s="9">
+        <f>SUM(Sheet1!D58:G58)</f>
+        <v>15219.650000000001</v>
+      </c>
+      <c r="N58" s="9">
+        <f>AVERAGE(Sheet1!D58:G58)</f>
+        <v>3804.9125000000004</v>
+      </c>
+      <c r="O58" s="9">
+        <f>MEDIAN(Sheet1!D58:F58,Sheet1!G58)</f>
+        <v>3883.4250000000002</v>
+      </c>
+      <c r="P58" s="10">
+        <f>STDEV(Sheet1!D58:G58)</f>
+        <v>575.72555118881451</v>
+      </c>
+      <c r="Q58" s="9">
+        <f>PRODUCT(Sheet1!D58,Sheet1!F58:G58)</f>
+        <v>47962553772.182457</v>
+      </c>
+      <c r="R58" s="9" t="str">
+        <f>IF(O58&gt;N58,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -3294,8 +5157,40 @@
       <c r="J59" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A59," ",Sheet1!B59)</f>
+        <v>Adam Mckinney</v>
+      </c>
+      <c r="L59" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A59, " (",Sheet1!H59,")")</f>
+        <v>Adam (Data Scientist)</v>
+      </c>
+      <c r="M59" s="9">
+        <f>SUM(Sheet1!D59:G59)</f>
+        <v>15557.39</v>
+      </c>
+      <c r="N59" s="9">
+        <f>AVERAGE(Sheet1!D59:G59)</f>
+        <v>3889.3474999999999</v>
+      </c>
+      <c r="O59" s="9">
+        <f>MEDIAN(Sheet1!D59:F59,Sheet1!G59)</f>
+        <v>3834.375</v>
+      </c>
+      <c r="P59" s="10">
+        <f>STDEV(Sheet1!D59:G59)</f>
+        <v>609.248544212458</v>
+      </c>
+      <c r="Q59" s="9">
+        <f>PRODUCT(Sheet1!D59,Sheet1!F59:G59)</f>
+        <v>65492006729.333176</v>
+      </c>
+      <c r="R59" s="9" t="str">
+        <f>IF(O59&gt;N59,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
@@ -3326,8 +5221,40 @@
       <c r="J60" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A60," ",Sheet1!B60)</f>
+        <v>Devin Roberts</v>
+      </c>
+      <c r="L60" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A60, " (",Sheet1!H60,")")</f>
+        <v>Devin (DevOps Engineer)</v>
+      </c>
+      <c r="M60" s="9">
+        <f>SUM(Sheet1!D60:G60)</f>
+        <v>18890.27</v>
+      </c>
+      <c r="N60" s="9">
+        <f>AVERAGE(Sheet1!D60:G60)</f>
+        <v>4722.5675000000001</v>
+      </c>
+      <c r="O60" s="9">
+        <f>MEDIAN(Sheet1!D60:F60,Sheet1!G60)</f>
+        <v>4516.88</v>
+      </c>
+      <c r="P60" s="10">
+        <f>STDEV(Sheet1!D60:G60)</f>
+        <v>1269.2449021202856</v>
+      </c>
+      <c r="Q60" s="9">
+        <f>PRODUCT(Sheet1!D60,Sheet1!F60:G60)</f>
+        <v>88586808185.127838</v>
+      </c>
+      <c r="R60" s="9" t="str">
+        <f>IF(O60&gt;N60,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
@@ -3358,8 +5285,40 @@
       <c r="J61" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A61," ",Sheet1!B61)</f>
+        <v>Brett Barry</v>
+      </c>
+      <c r="L61" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A61, " (",Sheet1!H61,")")</f>
+        <v>Brett (Data Scientist)</v>
+      </c>
+      <c r="M61" s="9">
+        <f>SUM(Sheet1!D61:G61)</f>
+        <v>18130.46</v>
+      </c>
+      <c r="N61" s="9">
+        <f>AVERAGE(Sheet1!D61:G61)</f>
+        <v>4532.6149999999998</v>
+      </c>
+      <c r="O61" s="9">
+        <f>MEDIAN(Sheet1!D61:F61,Sheet1!G61)</f>
+        <v>4571.3450000000003</v>
+      </c>
+      <c r="P61" s="10">
+        <f>STDEV(Sheet1!D61:G61)</f>
+        <v>722.447985417175</v>
+      </c>
+      <c r="Q61" s="9">
+        <f>PRODUCT(Sheet1!D61,Sheet1!F61:G61)</f>
+        <v>75487772950.730072</v>
+      </c>
+      <c r="R61" s="9" t="str">
+        <f>IF(O61&gt;N61,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
@@ -3390,8 +5349,40 @@
       <c r="J62" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A62," ",Sheet1!B62)</f>
+        <v>Wendy Jackson</v>
+      </c>
+      <c r="L62" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A62, " (",Sheet1!H62,")")</f>
+        <v>Wendy (UI/UX Designer)</v>
+      </c>
+      <c r="M62" s="9">
+        <f>SUM(Sheet1!D62:G62)</f>
+        <v>21912.55</v>
+      </c>
+      <c r="N62" s="9">
+        <f>AVERAGE(Sheet1!D62:G62)</f>
+        <v>5478.1374999999998</v>
+      </c>
+      <c r="O62" s="9">
+        <f>MEDIAN(Sheet1!D62:F62,Sheet1!G62)</f>
+        <v>5504.1949999999997</v>
+      </c>
+      <c r="P62" s="10">
+        <f>STDEV(Sheet1!D62:G62)</f>
+        <v>1322.4958020695838</v>
+      </c>
+      <c r="Q62" s="9">
+        <f>PRODUCT(Sheet1!D62,Sheet1!F62:G62)</f>
+        <v>118613938050.51414</v>
+      </c>
+      <c r="R62" s="9" t="str">
+        <f>IF(O62&gt;N62,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
@@ -3422,8 +5413,40 @@
       <c r="J63" s="8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A63," ",Sheet1!B63)</f>
+        <v>Caitlin Farrell</v>
+      </c>
+      <c r="L63" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A63, " (",Sheet1!H63,")")</f>
+        <v>Caitlin (Data Scientist)</v>
+      </c>
+      <c r="M63" s="9">
+        <f>SUM(Sheet1!D63:G63)</f>
+        <v>20870.04</v>
+      </c>
+      <c r="N63" s="9">
+        <f>AVERAGE(Sheet1!D63:G63)</f>
+        <v>5217.51</v>
+      </c>
+      <c r="O63" s="9">
+        <f>MEDIAN(Sheet1!D63:F63,Sheet1!G63)</f>
+        <v>5380.96</v>
+      </c>
+      <c r="P63" s="10">
+        <f>STDEV(Sheet1!D63:G63)</f>
+        <v>1676.615032816617</v>
+      </c>
+      <c r="Q63" s="9">
+        <f>PRODUCT(Sheet1!D63,Sheet1!F63:G63)</f>
+        <v>96595853101.523834</v>
+      </c>
+      <c r="R63" s="9" t="str">
+        <f>IF(O63&gt;N63,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
@@ -3454,8 +5477,40 @@
       <c r="J64" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A64," ",Sheet1!B64)</f>
+        <v>Eric Blevins</v>
+      </c>
+      <c r="L64" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A64, " (",Sheet1!H64,")")</f>
+        <v>Eric (Product Manager)</v>
+      </c>
+      <c r="M64" s="9">
+        <f>SUM(Sheet1!D64:G64)</f>
+        <v>19213.14</v>
+      </c>
+      <c r="N64" s="9">
+        <f>AVERAGE(Sheet1!D64:G64)</f>
+        <v>4803.2849999999999</v>
+      </c>
+      <c r="O64" s="9">
+        <f>MEDIAN(Sheet1!D64:F64,Sheet1!G64)</f>
+        <v>4701.26</v>
+      </c>
+      <c r="P64" s="10">
+        <f>STDEV(Sheet1!D64:G64)</f>
+        <v>842.96423160574705</v>
+      </c>
+      <c r="Q64" s="9">
+        <f>PRODUCT(Sheet1!D64,Sheet1!F64:G64)</f>
+        <v>86043202363.647064</v>
+      </c>
+      <c r="R64" s="9" t="str">
+        <f>IF(O64&gt;N64,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>59</v>
       </c>
@@ -3486,8 +5541,40 @@
       <c r="J65" s="8">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A65," ",Sheet1!B65)</f>
+        <v>Michael Walter</v>
+      </c>
+      <c r="L65" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A65, " (",Sheet1!H65,")")</f>
+        <v>Michael (QA Engineer)</v>
+      </c>
+      <c r="M65" s="9">
+        <f>SUM(Sheet1!D65:G65)</f>
+        <v>19428.939999999999</v>
+      </c>
+      <c r="N65" s="9">
+        <f>AVERAGE(Sheet1!D65:G65)</f>
+        <v>4857.2349999999997</v>
+      </c>
+      <c r="O65" s="9">
+        <f>MEDIAN(Sheet1!D65:F65,Sheet1!G65)</f>
+        <v>4995.5249999999996</v>
+      </c>
+      <c r="P65" s="10">
+        <f>STDEV(Sheet1!D65:G65)</f>
+        <v>1168.0978610972656</v>
+      </c>
+      <c r="Q65" s="9">
+        <f>PRODUCT(Sheet1!D65,Sheet1!F65:G65)</f>
+        <v>153128674617.51056</v>
+      </c>
+      <c r="R65" s="9" t="str">
+        <f>IF(O65&gt;N65,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>67</v>
       </c>
@@ -3518,8 +5605,40 @@
       <c r="J66" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A66," ",Sheet1!B66)</f>
+        <v>Nancy Hughes</v>
+      </c>
+      <c r="L66" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A66, " (",Sheet1!H66,")")</f>
+        <v>Nancy (Full Stack Developer)</v>
+      </c>
+      <c r="M66" s="9">
+        <f>SUM(Sheet1!D66:G66)</f>
+        <v>20586.63</v>
+      </c>
+      <c r="N66" s="9">
+        <f>AVERAGE(Sheet1!D66:G66)</f>
+        <v>5146.6575000000003</v>
+      </c>
+      <c r="O66" s="9">
+        <f>MEDIAN(Sheet1!D66:F66,Sheet1!G66)</f>
+        <v>5252.2049999999999</v>
+      </c>
+      <c r="P66" s="10">
+        <f>STDEV(Sheet1!D66:G66)</f>
+        <v>466.03763284202722</v>
+      </c>
+      <c r="Q66" s="9">
+        <f>PRODUCT(Sheet1!D66,Sheet1!F66:G66)</f>
+        <v>123987898742.00204</v>
+      </c>
+      <c r="R66" s="9" t="str">
+        <f>IF(O66&gt;N66,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
@@ -3550,8 +5669,40 @@
       <c r="J67" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A67," ",Sheet1!B67)</f>
+        <v>Glen Wilcox</v>
+      </c>
+      <c r="L67" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A67, " (",Sheet1!H67,")")</f>
+        <v>Glen (Full Stack Developer)</v>
+      </c>
+      <c r="M67" s="9">
+        <f>SUM(Sheet1!D67:G67)</f>
+        <v>19014.72</v>
+      </c>
+      <c r="N67" s="9">
+        <f>AVERAGE(Sheet1!D67:G67)</f>
+        <v>4753.68</v>
+      </c>
+      <c r="O67" s="9">
+        <f>MEDIAN(Sheet1!D67:F67,Sheet1!G67)</f>
+        <v>4596.7700000000004</v>
+      </c>
+      <c r="P67" s="10">
+        <f>STDEV(Sheet1!D67:G67)</f>
+        <v>1463.6993273210169</v>
+      </c>
+      <c r="Q67" s="9">
+        <f>PRODUCT(Sheet1!D67,Sheet1!F67:G67)</f>
+        <v>136146181659.85097</v>
+      </c>
+      <c r="R67" s="9" t="str">
+        <f>IF(O67&gt;N67,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>69</v>
       </c>
@@ -3582,8 +5733,40 @@
       <c r="J68" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A68," ",Sheet1!B68)</f>
+        <v>Angela Hansen</v>
+      </c>
+      <c r="L68" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A68, " (",Sheet1!H68,")")</f>
+        <v>Angela (Backend Developer)</v>
+      </c>
+      <c r="M68" s="9">
+        <f>SUM(Sheet1!D68:G68)</f>
+        <v>23047.770000000004</v>
+      </c>
+      <c r="N68" s="9">
+        <f>AVERAGE(Sheet1!D68:G68)</f>
+        <v>5761.942500000001</v>
+      </c>
+      <c r="O68" s="9">
+        <f>MEDIAN(Sheet1!D68:F68,Sheet1!G68)</f>
+        <v>6097.3649999999998</v>
+      </c>
+      <c r="P68" s="10">
+        <f>STDEV(Sheet1!D68:G68)</f>
+        <v>1363.2090341390494</v>
+      </c>
+      <c r="Q68" s="9">
+        <f>PRODUCT(Sheet1!D68,Sheet1!F68:G68)</f>
+        <v>153538562781.4957</v>
+      </c>
+      <c r="R68" s="9" t="str">
+        <f>IF(O68&gt;N68,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>70</v>
       </c>
@@ -3614,8 +5797,40 @@
       <c r="J69" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A69," ",Sheet1!B69)</f>
+        <v>Brian Bennett</v>
+      </c>
+      <c r="L69" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A69, " (",Sheet1!H69,")")</f>
+        <v>Brian (Product Manager)</v>
+      </c>
+      <c r="M69" s="9">
+        <f>SUM(Sheet1!D69:G69)</f>
+        <v>16931.150000000001</v>
+      </c>
+      <c r="N69" s="9">
+        <f>AVERAGE(Sheet1!D69:G69)</f>
+        <v>4232.7875000000004</v>
+      </c>
+      <c r="O69" s="9">
+        <f>MEDIAN(Sheet1!D69:F69,Sheet1!G69)</f>
+        <v>4227.47</v>
+      </c>
+      <c r="P69" s="10">
+        <f>STDEV(Sheet1!D69:G69)</f>
+        <v>505.10762373807734</v>
+      </c>
+      <c r="Q69" s="9">
+        <f>PRODUCT(Sheet1!D69,Sheet1!F69:G69)</f>
+        <v>67704924764.87899</v>
+      </c>
+      <c r="R69" s="9" t="str">
+        <f>IF(O69&gt;N69,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>71</v>
       </c>
@@ -3646,8 +5861,40 @@
       <c r="J70" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A70," ",Sheet1!B70)</f>
+        <v>Steven Blair</v>
+      </c>
+      <c r="L70" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A70, " (",Sheet1!H70,")")</f>
+        <v>Steven (Full Stack Developer)</v>
+      </c>
+      <c r="M70" s="9">
+        <f>SUM(Sheet1!D70:G70)</f>
+        <v>17613.5</v>
+      </c>
+      <c r="N70" s="9">
+        <f>AVERAGE(Sheet1!D70:G70)</f>
+        <v>4403.375</v>
+      </c>
+      <c r="O70" s="9">
+        <f>MEDIAN(Sheet1!D70:F70,Sheet1!G70)</f>
+        <v>4440.7950000000001</v>
+      </c>
+      <c r="P70" s="10">
+        <f>STDEV(Sheet1!D70:G70)</f>
+        <v>1449.1172180906105</v>
+      </c>
+      <c r="Q70" s="9">
+        <f>PRODUCT(Sheet1!D70,Sheet1!F70:G70)</f>
+        <v>104396260345.75856</v>
+      </c>
+      <c r="R70" s="9" t="str">
+        <f>IF(O70&gt;N70,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>72</v>
       </c>
@@ -3678,8 +5925,40 @@
       <c r="J71" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A71," ",Sheet1!B71)</f>
+        <v>Caitlyn Gutierrez</v>
+      </c>
+      <c r="L71" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A71, " (",Sheet1!H71,")")</f>
+        <v>Caitlyn (DevOps Engineer)</v>
+      </c>
+      <c r="M71" s="9">
+        <f>SUM(Sheet1!D71:G71)</f>
+        <v>18804.849999999999</v>
+      </c>
+      <c r="N71" s="9">
+        <f>AVERAGE(Sheet1!D71:G71)</f>
+        <v>4701.2124999999996</v>
+      </c>
+      <c r="O71" s="9">
+        <f>MEDIAN(Sheet1!D71:F71,Sheet1!G71)</f>
+        <v>4730.4650000000001</v>
+      </c>
+      <c r="P71" s="10">
+        <f>STDEV(Sheet1!D71:G71)</f>
+        <v>881.44978118911604</v>
+      </c>
+      <c r="Q71" s="9">
+        <f>PRODUCT(Sheet1!D71,Sheet1!F71:G71)</f>
+        <v>94942775027.302032</v>
+      </c>
+      <c r="R71" s="9" t="str">
+        <f>IF(O71&gt;N71,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +5989,40 @@
       <c r="J72" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A72," ",Sheet1!B72)</f>
+        <v>Jennifer Marquez</v>
+      </c>
+      <c r="L72" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A72, " (",Sheet1!H72,")")</f>
+        <v>Jennifer (Full Stack Developer)</v>
+      </c>
+      <c r="M72" s="9">
+        <f>SUM(Sheet1!D72:G72)</f>
+        <v>18896.09</v>
+      </c>
+      <c r="N72" s="9">
+        <f>AVERAGE(Sheet1!D72:G72)</f>
+        <v>4724.0225</v>
+      </c>
+      <c r="O72" s="9">
+        <f>MEDIAN(Sheet1!D72:F72,Sheet1!G72)</f>
+        <v>4809.6550000000007</v>
+      </c>
+      <c r="P72" s="10">
+        <f>STDEV(Sheet1!D72:G72)</f>
+        <v>1155.7667690722335</v>
+      </c>
+      <c r="Q72" s="9">
+        <f>PRODUCT(Sheet1!D72,Sheet1!F72:G72)</f>
+        <v>133585079922.14815</v>
+      </c>
+      <c r="R72" s="9" t="str">
+        <f>IF(O72&gt;N72,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>74</v>
       </c>
@@ -3742,8 +6053,40 @@
       <c r="J73" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A73," ",Sheet1!B73)</f>
+        <v>Joseph Black</v>
+      </c>
+      <c r="L73" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A73, " (",Sheet1!H73,")")</f>
+        <v>Joseph (Software Engineer)</v>
+      </c>
+      <c r="M73" s="9">
+        <f>SUM(Sheet1!D73:G73)</f>
+        <v>17337.689999999999</v>
+      </c>
+      <c r="N73" s="9">
+        <f>AVERAGE(Sheet1!D73:G73)</f>
+        <v>4334.4224999999997</v>
+      </c>
+      <c r="O73" s="9">
+        <f>MEDIAN(Sheet1!D73:F73,Sheet1!G73)</f>
+        <v>4139.4799999999996</v>
+      </c>
+      <c r="P73" s="10">
+        <f>STDEV(Sheet1!D73:G73)</f>
+        <v>1167.5812113760376</v>
+      </c>
+      <c r="Q73" s="9">
+        <f>PRODUCT(Sheet1!D73,Sheet1!F73:G73)</f>
+        <v>78404179577.753082</v>
+      </c>
+      <c r="R73" s="9" t="str">
+        <f>IF(O73&gt;N73,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>75</v>
       </c>
@@ -3774,8 +6117,40 @@
       <c r="J74" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A74," ",Sheet1!B74)</f>
+        <v>Veronica Porter</v>
+      </c>
+      <c r="L74" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A74, " (",Sheet1!H74,")")</f>
+        <v>Veronica (Business Analyst)</v>
+      </c>
+      <c r="M74" s="9">
+        <f>SUM(Sheet1!D74:G74)</f>
+        <v>17077.93</v>
+      </c>
+      <c r="N74" s="9">
+        <f>AVERAGE(Sheet1!D74:G74)</f>
+        <v>4269.4825000000001</v>
+      </c>
+      <c r="O74" s="9">
+        <f>MEDIAN(Sheet1!D74:F74,Sheet1!G74)</f>
+        <v>3602.0600000000004</v>
+      </c>
+      <c r="P74" s="10">
+        <f>STDEV(Sheet1!D74:G74)</f>
+        <v>1793.7920908209135</v>
+      </c>
+      <c r="Q74" s="9">
+        <f>PRODUCT(Sheet1!D74,Sheet1!F74:G74)</f>
+        <v>85440838451.515121</v>
+      </c>
+      <c r="R74" s="9" t="str">
+        <f>IF(O74&gt;N74,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>16</v>
       </c>
@@ -3806,8 +6181,40 @@
       <c r="J75" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A75," ",Sheet1!B75)</f>
+        <v>Amanda Todd</v>
+      </c>
+      <c r="L75" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A75, " (",Sheet1!H75,")")</f>
+        <v>Amanda (Cloud Engineer)</v>
+      </c>
+      <c r="M75" s="9">
+        <f>SUM(Sheet1!D75:G75)</f>
+        <v>15674.35</v>
+      </c>
+      <c r="N75" s="9">
+        <f>AVERAGE(Sheet1!D75:G75)</f>
+        <v>3918.5875000000001</v>
+      </c>
+      <c r="O75" s="9">
+        <f>MEDIAN(Sheet1!D75:F75,Sheet1!G75)</f>
+        <v>4074.8950000000004</v>
+      </c>
+      <c r="P75" s="10">
+        <f>STDEV(Sheet1!D75:G75)</f>
+        <v>555.69997722842197</v>
+      </c>
+      <c r="Q75" s="9">
+        <f>PRODUCT(Sheet1!D75,Sheet1!F75:G75)</f>
+        <v>57929787896.080551</v>
+      </c>
+      <c r="R75" s="9" t="str">
+        <f>IF(O75&gt;N75,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>76</v>
       </c>
@@ -3838,8 +6245,40 @@
       <c r="J76" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A76," ",Sheet1!B76)</f>
+        <v>Ashley Brown</v>
+      </c>
+      <c r="L76" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A76, " (",Sheet1!H76,")")</f>
+        <v>Ashley (Software Engineer)</v>
+      </c>
+      <c r="M76" s="9">
+        <f>SUM(Sheet1!D76:G76)</f>
+        <v>21780.21</v>
+      </c>
+      <c r="N76" s="9">
+        <f>AVERAGE(Sheet1!D76:G76)</f>
+        <v>5445.0524999999998</v>
+      </c>
+      <c r="O76" s="9">
+        <f>MEDIAN(Sheet1!D76:F76,Sheet1!G76)</f>
+        <v>5217.3</v>
+      </c>
+      <c r="P76" s="10">
+        <f>STDEV(Sheet1!D76:G76)</f>
+        <v>1031.1545093203399</v>
+      </c>
+      <c r="Q76" s="9">
+        <f>PRODUCT(Sheet1!D76,Sheet1!F76:G76)</f>
+        <v>122123246299.63921</v>
+      </c>
+      <c r="R76" s="9" t="str">
+        <f>IF(O76&gt;N76,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
@@ -3870,8 +6309,40 @@
       <c r="J77" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A77," ",Sheet1!B77)</f>
+        <v>Stephen Green</v>
+      </c>
+      <c r="L77" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A77, " (",Sheet1!H77,")")</f>
+        <v>Stephen (UI/UX Designer)</v>
+      </c>
+      <c r="M77" s="9">
+        <f>SUM(Sheet1!D77:G77)</f>
+        <v>22165.87</v>
+      </c>
+      <c r="N77" s="9">
+        <f>AVERAGE(Sheet1!D77:G77)</f>
+        <v>5541.4674999999997</v>
+      </c>
+      <c r="O77" s="9">
+        <f>MEDIAN(Sheet1!D77:F77,Sheet1!G77)</f>
+        <v>6060.66</v>
+      </c>
+      <c r="P77" s="10">
+        <f>STDEV(Sheet1!D77:G77)</f>
+        <v>1508.499346003063</v>
+      </c>
+      <c r="Q77" s="9">
+        <f>PRODUCT(Sheet1!D77,Sheet1!F77:G77)</f>
+        <v>122340255426.26314</v>
+      </c>
+      <c r="R77" s="9" t="str">
+        <f>IF(O77&gt;N77,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>69</v>
       </c>
@@ -3902,8 +6373,40 @@
       <c r="J78" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A78," ",Sheet1!B78)</f>
+        <v>Angela Gibbs</v>
+      </c>
+      <c r="L78" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A78, " (",Sheet1!H78,")")</f>
+        <v>Angela (Business Analyst)</v>
+      </c>
+      <c r="M78" s="9">
+        <f>SUM(Sheet1!D78:G78)</f>
+        <v>16554.86</v>
+      </c>
+      <c r="N78" s="9">
+        <f>AVERAGE(Sheet1!D78:G78)</f>
+        <v>4138.7150000000001</v>
+      </c>
+      <c r="O78" s="9">
+        <f>MEDIAN(Sheet1!D78:F78,Sheet1!G78)</f>
+        <v>3876.5450000000001</v>
+      </c>
+      <c r="P78" s="10">
+        <f>STDEV(Sheet1!D78:G78)</f>
+        <v>1125.3640346276086</v>
+      </c>
+      <c r="Q78" s="9">
+        <f>PRODUCT(Sheet1!D78,Sheet1!F78:G78)</f>
+        <v>78383505842.041</v>
+      </c>
+      <c r="R78" s="9" t="str">
+        <f>IF(O78&gt;N78,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
@@ -3934,8 +6437,40 @@
       <c r="J79" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K79" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A79," ",Sheet1!B79)</f>
+        <v>Timothy Hughes</v>
+      </c>
+      <c r="L79" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A79, " (",Sheet1!H79,")")</f>
+        <v>Timothy (Full Stack Developer)</v>
+      </c>
+      <c r="M79" s="9">
+        <f>SUM(Sheet1!D79:G79)</f>
+        <v>19838.38</v>
+      </c>
+      <c r="N79" s="9">
+        <f>AVERAGE(Sheet1!D79:G79)</f>
+        <v>4959.5950000000003</v>
+      </c>
+      <c r="O79" s="9">
+        <f>MEDIAN(Sheet1!D79:F79,Sheet1!G79)</f>
+        <v>4764.33</v>
+      </c>
+      <c r="P79" s="10">
+        <f>STDEV(Sheet1!D79:G79)</f>
+        <v>1127.7508440697354</v>
+      </c>
+      <c r="Q79" s="9">
+        <f>PRODUCT(Sheet1!D79,Sheet1!F79:G79)</f>
+        <v>144810918400.89178</v>
+      </c>
+      <c r="R79" s="9" t="str">
+        <f>IF(O79&gt;N79,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
@@ -3966,8 +6501,40 @@
       <c r="J80" s="8">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A80," ",Sheet1!B80)</f>
+        <v>Vanessa Griffin</v>
+      </c>
+      <c r="L80" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A80, " (",Sheet1!H80,")")</f>
+        <v>Vanessa (Data Scientist)</v>
+      </c>
+      <c r="M80" s="9">
+        <f>SUM(Sheet1!D80:G80)</f>
+        <v>18426.330000000002</v>
+      </c>
+      <c r="N80" s="9">
+        <f>AVERAGE(Sheet1!D80:G80)</f>
+        <v>4606.5825000000004</v>
+      </c>
+      <c r="O80" s="9">
+        <f>MEDIAN(Sheet1!D80:F80,Sheet1!G80)</f>
+        <v>4597.24</v>
+      </c>
+      <c r="P80" s="10">
+        <f>STDEV(Sheet1!D80:G80)</f>
+        <v>1267.6660293987775</v>
+      </c>
+      <c r="Q80" s="9">
+        <f>PRODUCT(Sheet1!D80,Sheet1!F80:G80)</f>
+        <v>93292651885.618942</v>
+      </c>
+      <c r="R80" s="9" t="str">
+        <f>IF(O80&gt;N80,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
@@ -3998,8 +6565,40 @@
       <c r="J81" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K81" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A81," ",Sheet1!B81)</f>
+        <v>Kaitlin Colon</v>
+      </c>
+      <c r="L81" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A81, " (",Sheet1!H81,")")</f>
+        <v>Kaitlin (Scrum Master)</v>
+      </c>
+      <c r="M81" s="9">
+        <f>SUM(Sheet1!D81:G81)</f>
+        <v>16668.38</v>
+      </c>
+      <c r="N81" s="9">
+        <f>AVERAGE(Sheet1!D81:G81)</f>
+        <v>4167.0950000000003</v>
+      </c>
+      <c r="O81" s="9">
+        <f>MEDIAN(Sheet1!D81:F81,Sheet1!G81)</f>
+        <v>3887.17</v>
+      </c>
+      <c r="P81" s="10">
+        <f>STDEV(Sheet1!D81:G81)</f>
+        <v>1247.4151424846491</v>
+      </c>
+      <c r="Q81" s="9">
+        <f>PRODUCT(Sheet1!D81,Sheet1!F81:G81)</f>
+        <v>45405706108.971603</v>
+      </c>
+      <c r="R81" s="9" t="str">
+        <f>IF(O81&gt;N81,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
@@ -4030,8 +6629,40 @@
       <c r="J82" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K82" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A82," ",Sheet1!B82)</f>
+        <v>Joshua Benson</v>
+      </c>
+      <c r="L82" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A82, " (",Sheet1!H82,")")</f>
+        <v>Joshua (Data Scientist)</v>
+      </c>
+      <c r="M82" s="9">
+        <f>SUM(Sheet1!D82:G82)</f>
+        <v>19293.84</v>
+      </c>
+      <c r="N82" s="9">
+        <f>AVERAGE(Sheet1!D82:G82)</f>
+        <v>4823.46</v>
+      </c>
+      <c r="O82" s="9">
+        <f>MEDIAN(Sheet1!D82:F82,Sheet1!G82)</f>
+        <v>4401.7349999999997</v>
+      </c>
+      <c r="P82" s="10">
+        <f>STDEV(Sheet1!D82:G82)</f>
+        <v>1542.8769077062902</v>
+      </c>
+      <c r="Q82" s="9">
+        <f>PRODUCT(Sheet1!D82,Sheet1!F82:G82)</f>
+        <v>128302228318.60582</v>
+      </c>
+      <c r="R82" s="9" t="str">
+        <f>IF(O82&gt;N82,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>55</v>
       </c>
@@ -4062,8 +6693,40 @@
       <c r="J83" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K83" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A83," ",Sheet1!B83)</f>
+        <v>Nicholas Chavez</v>
+      </c>
+      <c r="L83" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A83, " (",Sheet1!H83,")")</f>
+        <v>Nicholas (Security Analyst)</v>
+      </c>
+      <c r="M83" s="9">
+        <f>SUM(Sheet1!D83:G83)</f>
+        <v>18560.11</v>
+      </c>
+      <c r="N83" s="9">
+        <f>AVERAGE(Sheet1!D83:G83)</f>
+        <v>4640.0275000000001</v>
+      </c>
+      <c r="O83" s="9">
+        <f>MEDIAN(Sheet1!D83:F83,Sheet1!G83)</f>
+        <v>4793</v>
+      </c>
+      <c r="P83" s="10">
+        <f>STDEV(Sheet1!D83:G83)</f>
+        <v>1236.9130520877359</v>
+      </c>
+      <c r="Q83" s="9">
+        <f>PRODUCT(Sheet1!D83,Sheet1!F83:G83)</f>
+        <v>90748270084.750259</v>
+      </c>
+      <c r="R83" s="9" t="str">
+        <f>IF(O83&gt;N83,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>77</v>
       </c>
@@ -4094,8 +6757,40 @@
       <c r="J84" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K84" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A84," ",Sheet1!B84)</f>
+        <v>Timothy Nelson</v>
+      </c>
+      <c r="L84" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A84, " (",Sheet1!H84,")")</f>
+        <v>Timothy (Frontend Developer)</v>
+      </c>
+      <c r="M84" s="9">
+        <f>SUM(Sheet1!D84:G84)</f>
+        <v>19074.2</v>
+      </c>
+      <c r="N84" s="9">
+        <f>AVERAGE(Sheet1!D84:G84)</f>
+        <v>4768.55</v>
+      </c>
+      <c r="O84" s="9">
+        <f>MEDIAN(Sheet1!D84:F84,Sheet1!G84)</f>
+        <v>4336.2150000000001</v>
+      </c>
+      <c r="P84" s="10">
+        <f>STDEV(Sheet1!D84:G84)</f>
+        <v>1382.2439053220667</v>
+      </c>
+      <c r="Q84" s="9">
+        <f>PRODUCT(Sheet1!D84,Sheet1!F84:G84)</f>
+        <v>116582513141.04779</v>
+      </c>
+      <c r="R84" s="9" t="str">
+        <f>IF(O84&gt;N84,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>80</v>
       </c>
@@ -4126,8 +6821,40 @@
       <c r="J85" s="8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K85" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A85," ",Sheet1!B85)</f>
+        <v>Scott Smith</v>
+      </c>
+      <c r="L85" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A85, " (",Sheet1!H85,")")</f>
+        <v>Scott (Frontend Developer)</v>
+      </c>
+      <c r="M85" s="9">
+        <f>SUM(Sheet1!D85:G85)</f>
+        <v>21241.65</v>
+      </c>
+      <c r="N85" s="9">
+        <f>AVERAGE(Sheet1!D85:G85)</f>
+        <v>5310.4125000000004</v>
+      </c>
+      <c r="O85" s="9">
+        <f>MEDIAN(Sheet1!D85:F85,Sheet1!G85)</f>
+        <v>5599.3600000000006</v>
+      </c>
+      <c r="P85" s="10">
+        <f>STDEV(Sheet1!D85:G85)</f>
+        <v>1031.2032643591645</v>
+      </c>
+      <c r="Q85" s="9">
+        <f>PRODUCT(Sheet1!D85,Sheet1!F85:G85)</f>
+        <v>137870426873.35104</v>
+      </c>
+      <c r="R85" s="9" t="str">
+        <f>IF(O85&gt;N85,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>81</v>
       </c>
@@ -4158,8 +6885,40 @@
       <c r="J86" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K86" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A86," ",Sheet1!B86)</f>
+        <v>Cathy Carr</v>
+      </c>
+      <c r="L86" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A86, " (",Sheet1!H86,")")</f>
+        <v>Cathy (DevOps Engineer)</v>
+      </c>
+      <c r="M86" s="9">
+        <f>SUM(Sheet1!D86:G86)</f>
+        <v>22267.69</v>
+      </c>
+      <c r="N86" s="9">
+        <f>AVERAGE(Sheet1!D86:G86)</f>
+        <v>5566.9224999999997</v>
+      </c>
+      <c r="O86" s="9">
+        <f>MEDIAN(Sheet1!D86:F86,Sheet1!G86)</f>
+        <v>5608.3649999999998</v>
+      </c>
+      <c r="P86" s="10">
+        <f>STDEV(Sheet1!D86:G86)</f>
+        <v>910.44551937957146</v>
+      </c>
+      <c r="Q86" s="9">
+        <f>PRODUCT(Sheet1!D86,Sheet1!F86:G86)</f>
+        <v>168926898807.40781</v>
+      </c>
+      <c r="R86" s="9" t="str">
+        <f>IF(O86&gt;N86,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -4190,8 +6949,40 @@
       <c r="J87" s="8">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K87" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A87," ",Sheet1!B87)</f>
+        <v>Katherine Williams</v>
+      </c>
+      <c r="L87" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A87, " (",Sheet1!H87,")")</f>
+        <v>Katherine (Mobile App Developer)</v>
+      </c>
+      <c r="M87" s="9">
+        <f>SUM(Sheet1!D87:G87)</f>
+        <v>21501.82</v>
+      </c>
+      <c r="N87" s="9">
+        <f>AVERAGE(Sheet1!D87:G87)</f>
+        <v>5375.4549999999999</v>
+      </c>
+      <c r="O87" s="9">
+        <f>MEDIAN(Sheet1!D87:F87,Sheet1!G87)</f>
+        <v>5780.26</v>
+      </c>
+      <c r="P87" s="10">
+        <f>STDEV(Sheet1!D87:G87)</f>
+        <v>1172.0310639085767</v>
+      </c>
+      <c r="Q87" s="9">
+        <f>PRODUCT(Sheet1!D87,Sheet1!F87:G87)</f>
+        <v>210043184049.16562</v>
+      </c>
+      <c r="R87" s="9" t="str">
+        <f>IF(O87&gt;N87,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>83</v>
       </c>
@@ -4222,8 +7013,40 @@
       <c r="J88" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K88" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A88," ",Sheet1!B88)</f>
+        <v>Shane Oconnor</v>
+      </c>
+      <c r="L88" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A88, " (",Sheet1!H88,")")</f>
+        <v>Shane (Security Analyst)</v>
+      </c>
+      <c r="M88" s="9">
+        <f>SUM(Sheet1!D88:G88)</f>
+        <v>19744.52</v>
+      </c>
+      <c r="N88" s="9">
+        <f>AVERAGE(Sheet1!D88:G88)</f>
+        <v>4936.13</v>
+      </c>
+      <c r="O88" s="9">
+        <f>MEDIAN(Sheet1!D88:F88,Sheet1!G88)</f>
+        <v>5317.0249999999996</v>
+      </c>
+      <c r="P88" s="10">
+        <f>STDEV(Sheet1!D88:G88)</f>
+        <v>1129.455243351116</v>
+      </c>
+      <c r="Q88" s="9">
+        <f>PRODUCT(Sheet1!D88,Sheet1!F88:G88)</f>
+        <v>92767991893.954193</v>
+      </c>
+      <c r="R88" s="9" t="str">
+        <f>IF(O88&gt;N88,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>28</v>
       </c>
@@ -4254,8 +7077,40 @@
       <c r="J89" s="8">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K89" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A89," ",Sheet1!B89)</f>
+        <v>Natalie White</v>
+      </c>
+      <c r="L89" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A89, " (",Sheet1!H89,")")</f>
+        <v>Natalie (Backend Developer)</v>
+      </c>
+      <c r="M89" s="9">
+        <f>SUM(Sheet1!D89:G89)</f>
+        <v>22902.440000000002</v>
+      </c>
+      <c r="N89" s="9">
+        <f>AVERAGE(Sheet1!D89:G89)</f>
+        <v>5725.6100000000006</v>
+      </c>
+      <c r="O89" s="9">
+        <f>MEDIAN(Sheet1!D89:F89,Sheet1!G89)</f>
+        <v>5865.335</v>
+      </c>
+      <c r="P89" s="10">
+        <f>STDEV(Sheet1!D89:G89)</f>
+        <v>714.31725551979014</v>
+      </c>
+      <c r="Q89" s="9">
+        <f>PRODUCT(Sheet1!D89,Sheet1!F89:G89)</f>
+        <v>163435881303.95099</v>
+      </c>
+      <c r="R89" s="9" t="str">
+        <f>IF(O89&gt;N89,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>84</v>
       </c>
@@ -4286,8 +7141,40 @@
       <c r="J90" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K90" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A90," ",Sheet1!B90)</f>
+        <v>Hannah Schmidt</v>
+      </c>
+      <c r="L90" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A90, " (",Sheet1!H90,")")</f>
+        <v>Hannah (System Administrator)</v>
+      </c>
+      <c r="M90" s="9">
+        <f>SUM(Sheet1!D90:G90)</f>
+        <v>18634.68</v>
+      </c>
+      <c r="N90" s="9">
+        <f>AVERAGE(Sheet1!D90:G90)</f>
+        <v>4658.67</v>
+      </c>
+      <c r="O90" s="9">
+        <f>MEDIAN(Sheet1!D90:F90,Sheet1!G90)</f>
+        <v>4720.0999999999995</v>
+      </c>
+      <c r="P90" s="10">
+        <f>STDEV(Sheet1!D90:G90)</f>
+        <v>1699.9921361190648</v>
+      </c>
+      <c r="Q90" s="9">
+        <f>PRODUCT(Sheet1!D90,Sheet1!F90:G90)</f>
+        <v>62897184451.772697</v>
+      </c>
+      <c r="R90" s="9" t="str">
+        <f>IF(O90&gt;N90,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>85</v>
       </c>
@@ -4318,8 +7205,40 @@
       <c r="J91" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K91" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A91," ",Sheet1!B91)</f>
+        <v>Alexandra Bates</v>
+      </c>
+      <c r="L91" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A91, " (",Sheet1!H91,")")</f>
+        <v>Alexandra (DevOps Engineer)</v>
+      </c>
+      <c r="M91" s="9">
+        <f>SUM(Sheet1!D91:G91)</f>
+        <v>21365.14</v>
+      </c>
+      <c r="N91" s="9">
+        <f>AVERAGE(Sheet1!D91:G91)</f>
+        <v>5341.2849999999999</v>
+      </c>
+      <c r="O91" s="9">
+        <f>MEDIAN(Sheet1!D91:F91,Sheet1!G91)</f>
+        <v>5315.42</v>
+      </c>
+      <c r="P91" s="10">
+        <f>STDEV(Sheet1!D91:G91)</f>
+        <v>1248.1519362241143</v>
+      </c>
+      <c r="Q91" s="9">
+        <f>PRODUCT(Sheet1!D91,Sheet1!F91:G91)</f>
+        <v>164025137713.203</v>
+      </c>
+      <c r="R91" s="9" t="str">
+        <f>IF(O91&gt;N91,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>86</v>
       </c>
@@ -4350,8 +7269,40 @@
       <c r="J92" s="8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K92" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A92," ",Sheet1!B92)</f>
+        <v>Justin Pham</v>
+      </c>
+      <c r="L92" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A92, " (",Sheet1!H92,")")</f>
+        <v>Justin (Business Analyst)</v>
+      </c>
+      <c r="M92" s="9">
+        <f>SUM(Sheet1!D92:G92)</f>
+        <v>19777.61</v>
+      </c>
+      <c r="N92" s="9">
+        <f>AVERAGE(Sheet1!D92:G92)</f>
+        <v>4944.4025000000001</v>
+      </c>
+      <c r="O92" s="9">
+        <f>MEDIAN(Sheet1!D92:F92,Sheet1!G92)</f>
+        <v>4975.5400000000009</v>
+      </c>
+      <c r="P92" s="10">
+        <f>STDEV(Sheet1!D92:G92)</f>
+        <v>881.11396158025946</v>
+      </c>
+      <c r="Q92" s="9">
+        <f>PRODUCT(Sheet1!D92,Sheet1!F92:G92)</f>
+        <v>95118190907.376648</v>
+      </c>
+      <c r="R92" s="9" t="str">
+        <f>IF(O92&gt;N92,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>87</v>
       </c>
@@ -4382,8 +7333,40 @@
       <c r="J93" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K93" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A93," ",Sheet1!B93)</f>
+        <v>Paul Peterson</v>
+      </c>
+      <c r="L93" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A93, " (",Sheet1!H93,")")</f>
+        <v>Paul (Product Manager)</v>
+      </c>
+      <c r="M93" s="9">
+        <f>SUM(Sheet1!D93:G93)</f>
+        <v>21287.41</v>
+      </c>
+      <c r="N93" s="9">
+        <f>AVERAGE(Sheet1!D93:G93)</f>
+        <v>5321.8525</v>
+      </c>
+      <c r="O93" s="9">
+        <f>MEDIAN(Sheet1!D93:F93,Sheet1!G93)</f>
+        <v>5488.3549999999996</v>
+      </c>
+      <c r="P93" s="10">
+        <f>STDEV(Sheet1!D93:G93)</f>
+        <v>726.11160516709708</v>
+      </c>
+      <c r="Q93" s="9">
+        <f>PRODUCT(Sheet1!D93,Sheet1!F93:G93)</f>
+        <v>130646291244.30035</v>
+      </c>
+      <c r="R93" s="9" t="str">
+        <f>IF(O93&gt;N93,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>88</v>
       </c>
@@ -4414,8 +7397,40 @@
       <c r="J94" s="8">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K94" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A94," ",Sheet1!B94)</f>
+        <v>Joel King</v>
+      </c>
+      <c r="L94" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A94, " (",Sheet1!H94,")")</f>
+        <v>Joel (Data Scientist)</v>
+      </c>
+      <c r="M94" s="9">
+        <f>SUM(Sheet1!D94:G94)</f>
+        <v>16943.949999999997</v>
+      </c>
+      <c r="N94" s="9">
+        <f>AVERAGE(Sheet1!D94:G94)</f>
+        <v>4235.9874999999993</v>
+      </c>
+      <c r="O94" s="9">
+        <f>MEDIAN(Sheet1!D94:F94,Sheet1!G94)</f>
+        <v>4050.6149999999998</v>
+      </c>
+      <c r="P94" s="10">
+        <f>STDEV(Sheet1!D94:G94)</f>
+        <v>951.94967967062269</v>
+      </c>
+      <c r="Q94" s="9">
+        <f>PRODUCT(Sheet1!D94,Sheet1!F94:G94)</f>
+        <v>53912058466.226677</v>
+      </c>
+      <c r="R94" s="9" t="str">
+        <f>IF(O94&gt;N94,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>89</v>
       </c>
@@ -4446,8 +7461,40 @@
       <c r="J95" s="8">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K95" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A95," ",Sheet1!B95)</f>
+        <v>Elaine Shaw</v>
+      </c>
+      <c r="L95" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A95, " (",Sheet1!H95,")")</f>
+        <v>Elaine (QA Engineer)</v>
+      </c>
+      <c r="M95" s="9">
+        <f>SUM(Sheet1!D95:G95)</f>
+        <v>23022.57</v>
+      </c>
+      <c r="N95" s="9">
+        <f>AVERAGE(Sheet1!D95:G95)</f>
+        <v>5755.6424999999999</v>
+      </c>
+      <c r="O95" s="9">
+        <f>MEDIAN(Sheet1!D95:F95,Sheet1!G95)</f>
+        <v>5897.5249999999996</v>
+      </c>
+      <c r="P95" s="10">
+        <f>STDEV(Sheet1!D95:G95)</f>
+        <v>948.32521785777556</v>
+      </c>
+      <c r="Q95" s="9">
+        <f>PRODUCT(Sheet1!D95,Sheet1!F95:G95)</f>
+        <v>227770836653.85419</v>
+      </c>
+      <c r="R95" s="9" t="str">
+        <f>IF(O95&gt;N95,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>90</v>
       </c>
@@ -4478,8 +7525,40 @@
       <c r="J96" s="8">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K96" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A96," ",Sheet1!B96)</f>
+        <v>Tanya Nielsen</v>
+      </c>
+      <c r="L96" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A96, " (",Sheet1!H96,")")</f>
+        <v>Tanya (System Administrator)</v>
+      </c>
+      <c r="M96" s="9">
+        <f>SUM(Sheet1!D96:G96)</f>
+        <v>19242.05</v>
+      </c>
+      <c r="N96" s="9">
+        <f>AVERAGE(Sheet1!D96:G96)</f>
+        <v>4810.5124999999998</v>
+      </c>
+      <c r="O96" s="9">
+        <f>MEDIAN(Sheet1!D96:F96,Sheet1!G96)</f>
+        <v>4876.165</v>
+      </c>
+      <c r="P96" s="10">
+        <f>STDEV(Sheet1!D96:G96)</f>
+        <v>1119.8616539964523</v>
+      </c>
+      <c r="Q96" s="9">
+        <f>PRODUCT(Sheet1!D96,Sheet1!F96:G96)</f>
+        <v>80290192745.185165</v>
+      </c>
+      <c r="R96" s="9" t="str">
+        <f>IF(O96&gt;N96,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>91</v>
       </c>
@@ -4510,8 +7589,40 @@
       <c r="J97" s="8">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K97" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A97," ",Sheet1!B97)</f>
+        <v>Alejandra Mueller</v>
+      </c>
+      <c r="L97" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A97, " (",Sheet1!H97,")")</f>
+        <v>Alejandra (UI/UX Designer)</v>
+      </c>
+      <c r="M97" s="9">
+        <f>SUM(Sheet1!D97:G97)</f>
+        <v>19409.71</v>
+      </c>
+      <c r="N97" s="9">
+        <f>AVERAGE(Sheet1!D97:G97)</f>
+        <v>4852.4274999999998</v>
+      </c>
+      <c r="O97" s="9">
+        <f>MEDIAN(Sheet1!D97:F97,Sheet1!G97)</f>
+        <v>4991.25</v>
+      </c>
+      <c r="P97" s="10">
+        <f>STDEV(Sheet1!D97:G97)</f>
+        <v>1222.984391352428</v>
+      </c>
+      <c r="Q97" s="9">
+        <f>PRODUCT(Sheet1!D97,Sheet1!F97:G97)</f>
+        <v>102463335803.36929</v>
+      </c>
+      <c r="R97" s="9" t="str">
+        <f>IF(O97&gt;N97,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>92</v>
       </c>
@@ -4542,8 +7653,40 @@
       <c r="J98" s="8">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K98" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A98," ",Sheet1!B98)</f>
+        <v>Eddie Perez</v>
+      </c>
+      <c r="L98" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A98, " (",Sheet1!H98,")")</f>
+        <v>Eddie (Technical Support)</v>
+      </c>
+      <c r="M98" s="9">
+        <f>SUM(Sheet1!D98:G98)</f>
+        <v>18746.150000000001</v>
+      </c>
+      <c r="N98" s="9">
+        <f>AVERAGE(Sheet1!D98:G98)</f>
+        <v>4686.5375000000004</v>
+      </c>
+      <c r="O98" s="9">
+        <f>MEDIAN(Sheet1!D98:F98,Sheet1!G98)</f>
+        <v>4762.4400000000005</v>
+      </c>
+      <c r="P98" s="10">
+        <f>STDEV(Sheet1!D98:G98)</f>
+        <v>1188.5130753277374</v>
+      </c>
+      <c r="Q98" s="9">
+        <f>PRODUCT(Sheet1!D98,Sheet1!F98:G98)</f>
+        <v>102903114044.19565</v>
+      </c>
+      <c r="R98" s="9" t="str">
+        <f>IF(O98&gt;N98,"Approved", "Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>93</v>
       </c>
@@ -4574,8 +7717,40 @@
       <c r="J99" s="8">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K99" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A99," ",Sheet1!B99)</f>
+        <v>Jessica Nunez</v>
+      </c>
+      <c r="L99" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A99, " (",Sheet1!H99,")")</f>
+        <v>Jessica (UI/UX Designer)</v>
+      </c>
+      <c r="M99" s="9">
+        <f>SUM(Sheet1!D99:G99)</f>
+        <v>17845.009999999998</v>
+      </c>
+      <c r="N99" s="9">
+        <f>AVERAGE(Sheet1!D99:G99)</f>
+        <v>4461.2524999999996</v>
+      </c>
+      <c r="O99" s="9">
+        <f>MEDIAN(Sheet1!D99:F99,Sheet1!G99)</f>
+        <v>3923.0349999999999</v>
+      </c>
+      <c r="P99" s="10">
+        <f>STDEV(Sheet1!D99:G99)</f>
+        <v>1631.3872216281663</v>
+      </c>
+      <c r="Q99" s="9">
+        <f>PRODUCT(Sheet1!D99,Sheet1!F99:G99)</f>
+        <v>78064189310.20372</v>
+      </c>
+      <c r="R99" s="9" t="str">
+        <f>IF(O99&gt;N99,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>94</v>
       </c>
@@ -4606,8 +7781,40 @@
       <c r="J100" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K100" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A100," ",Sheet1!B100)</f>
+        <v>Carrie Wright</v>
+      </c>
+      <c r="L100" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A100, " (",Sheet1!H100,")")</f>
+        <v>Carrie (Full Stack Developer)</v>
+      </c>
+      <c r="M100" s="9">
+        <f>SUM(Sheet1!D100:G100)</f>
+        <v>19593.02</v>
+      </c>
+      <c r="N100" s="9">
+        <f>AVERAGE(Sheet1!D100:G100)</f>
+        <v>4898.2550000000001</v>
+      </c>
+      <c r="O100" s="9">
+        <f>MEDIAN(Sheet1!D100:F100,Sheet1!G100)</f>
+        <v>4556.71</v>
+      </c>
+      <c r="P100" s="10">
+        <f>STDEV(Sheet1!D100:G100)</f>
+        <v>1497.5227319476637</v>
+      </c>
+      <c r="Q100" s="9">
+        <f>PRODUCT(Sheet1!D100,Sheet1!F100:G100)</f>
+        <v>121263863034.35628</v>
+      </c>
+      <c r="R100" s="9" t="str">
+        <f>IF(O100&gt;N100,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>95</v>
       </c>
@@ -4638,14 +7845,102 @@
       <c r="J101" s="8">
         <v>4.5</v>
       </c>
+      <c r="K101" s="8" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A101," ",Sheet1!B101)</f>
+        <v>Daniel Haynes</v>
+      </c>
+      <c r="L101" s="9" t="str">
+        <f>_xlfn.CONCAT(Sheet1!A101, " (",Sheet1!H101,")")</f>
+        <v>Daniel (Backend Developer)</v>
+      </c>
+      <c r="M101" s="9">
+        <f>SUM(Sheet1!D101:G101)</f>
+        <v>21449.11</v>
+      </c>
+      <c r="N101" s="9">
+        <f>AVERAGE(Sheet1!D101:G101)</f>
+        <v>5362.2775000000001</v>
+      </c>
+      <c r="O101" s="9">
+        <f>MEDIAN(Sheet1!D101:F101,Sheet1!G101)</f>
+        <v>5326.5550000000003</v>
+      </c>
+      <c r="P101" s="10">
+        <f>STDEV(Sheet1!D101:G101)</f>
+        <v>1143.3617554496905</v>
+      </c>
+      <c r="Q101" s="9">
+        <f>PRODUCT(Sheet1!D101,Sheet1!F101:G101)</f>
+        <v>146893185171.40561</v>
+      </c>
+      <c r="R101" s="9" t="str">
+        <f>IF(O101&gt;N101,"Approved", "Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E104" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="E105" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="E106" s="2">
+        <f>VLOOKUP(E105,K2:N101,4,FALSE)</f>
+        <v>4235.9874999999993</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N101">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{93E9A7EC-5A8B-4947-9623-3C97FE145FB8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P101">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q101">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BC57C642-6F85-4595-AC4D-C017562496B9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{82039766-BEA8-407F-836B-ED3A6E61961A}">
+          <x14:cfRule type="iconSet" priority="4" id="{82039766-BEA8-407F-836B-ED3A6E61961A}">
             <x14:iconSet iconSet="3Stars" showValue="0">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -4660,6 +7955,32 @@
           </x14:cfRule>
           <xm:sqref>J2:J101</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{93E9A7EC-5A8B-4947-9623-3C97FE145FB8}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N2:N101</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{BC57C642-6F85-4595-AC4D-C017562496B9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>Q2:Q101</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -4668,7 +7989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3A3C5C-E7A3-4ED0-A8D8-554506645B9D}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -4681,3473 +8002,12 @@
     <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A2," ",Sheet1!B2)</f>
-        <v>Maria Matthews</v>
-      </c>
-      <c r="B2" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A2, " (",Sheet1!H2,")")</f>
-        <v>Maria (System Administrator)</v>
-      </c>
-      <c r="C2" s="9">
-        <f>SUM(Sheet1!D2:G2)</f>
-        <v>19714.559999999998</v>
-      </c>
-      <c r="D2" s="9">
-        <f>AVERAGE(Sheet1!D2:G2)</f>
-        <v>4928.6399999999994</v>
-      </c>
-      <c r="E2" s="9">
-        <f>MEDIAN(Sheet1!D2:F2,Sheet1!G2)</f>
-        <v>5229.2250000000004</v>
-      </c>
-      <c r="F2" s="10">
-        <f>STDEV(Sheet1!D2:G2)</f>
-        <v>1275.5392790763742</v>
-      </c>
-      <c r="G2" s="9">
-        <f>PRODUCT(Sheet1!D2,Sheet1!F2:G2)</f>
-        <v>113158186357.21536</v>
-      </c>
-      <c r="H2" s="9" t="str">
-        <f>IF(E2&gt;D2,"Approved", "Not Approved")</f>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A3," ",Sheet1!B3)</f>
-        <v>Jenna Wilson</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A3, " (",Sheet1!H3,")")</f>
-        <v>Jenna (QA Engineer)</v>
-      </c>
-      <c r="C3" s="9">
-        <f>SUM(Sheet1!D3:G3)</f>
-        <v>19350.419999999998</v>
-      </c>
-      <c r="D3" s="9">
-        <f>AVERAGE(Sheet1!D3:G3)</f>
-        <v>4837.6049999999996</v>
-      </c>
-      <c r="E3" s="9">
-        <f>MEDIAN(Sheet1!D3:F3,Sheet1!G3)</f>
-        <v>4999.085</v>
-      </c>
-      <c r="F3" s="10">
-        <f>STDEV(Sheet1!D3:G3)</f>
-        <v>1126.3574497911416</v>
-      </c>
-      <c r="G3" s="9">
-        <f>PRODUCT(Sheet1!D3,Sheet1!F3:G3)</f>
-        <v>87962839949.162384</v>
-      </c>
-      <c r="H3" s="9" t="str">
-        <f t="shared" ref="H3:H66" si="0">IF(E3&gt;D3,"Approved", "Not Approved")</f>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A4," ",Sheet1!B4)</f>
-        <v>Charles Morgan</v>
-      </c>
-      <c r="B4" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A4, " (",Sheet1!H4,")")</f>
-        <v>Charles (Mobile App Developer)</v>
-      </c>
-      <c r="C4" s="9">
-        <f>SUM(Sheet1!D4:G4)</f>
-        <v>22629.119999999999</v>
-      </c>
-      <c r="D4" s="9">
-        <f>AVERAGE(Sheet1!D4:G4)</f>
-        <v>5657.28</v>
-      </c>
-      <c r="E4" s="9">
-        <f>MEDIAN(Sheet1!D4:F4,Sheet1!G4)</f>
-        <v>5960.4449999999997</v>
-      </c>
-      <c r="F4" s="10">
-        <f>STDEV(Sheet1!D4:G4)</f>
-        <v>1378.9222741692167</v>
-      </c>
-      <c r="G4" s="9">
-        <f>PRODUCT(Sheet1!D4,Sheet1!F4:G4)</f>
-        <v>157977029147.8287</v>
-      </c>
-      <c r="H4" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A5," ",Sheet1!B5)</f>
-        <v>Richard Padilla</v>
-      </c>
-      <c r="B5" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A5, " (",Sheet1!H5,")")</f>
-        <v>Richard (System Administrator)</v>
-      </c>
-      <c r="C5" s="9">
-        <f>SUM(Sheet1!D5:G5)</f>
-        <v>22833.69</v>
-      </c>
-      <c r="D5" s="9">
-        <f>AVERAGE(Sheet1!D5:G5)</f>
-        <v>5708.4224999999997</v>
-      </c>
-      <c r="E5" s="9">
-        <f>MEDIAN(Sheet1!D5:F5,Sheet1!G5)</f>
-        <v>6186.16</v>
-      </c>
-      <c r="F5" s="10">
-        <f>STDEV(Sheet1!D5:G5)</f>
-        <v>1256.5419138618797</v>
-      </c>
-      <c r="G5" s="9">
-        <f>PRODUCT(Sheet1!D5,Sheet1!F5:G5)</f>
-        <v>251538956263.08948</v>
-      </c>
-      <c r="H5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A6," ",Sheet1!B6)</f>
-        <v>Cindy Roberts</v>
-      </c>
-      <c r="B6" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A6, " (",Sheet1!H6,")")</f>
-        <v>Cindy (Full Stack Developer)</v>
-      </c>
-      <c r="C6" s="9">
-        <f>SUM(Sheet1!D6:G6)</f>
-        <v>19810.580000000002</v>
-      </c>
-      <c r="D6" s="9">
-        <f>AVERAGE(Sheet1!D6:G6)</f>
-        <v>4952.6450000000004</v>
-      </c>
-      <c r="E6" s="9">
-        <f>MEDIAN(Sheet1!D6:F6,Sheet1!G6)</f>
-        <v>5235.7950000000001</v>
-      </c>
-      <c r="F6" s="10">
-        <f>STDEV(Sheet1!D6:G6)</f>
-        <v>1472.3394251439872</v>
-      </c>
-      <c r="G6" s="9">
-        <f>PRODUCT(Sheet1!D6,Sheet1!F6:G6)</f>
-        <v>81951095956.771439</v>
-      </c>
-      <c r="H6" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A7," ",Sheet1!B7)</f>
-        <v>Lauren Bailey</v>
-      </c>
-      <c r="B7" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A7, " (",Sheet1!H7,")")</f>
-        <v>Lauren (UI/UX Designer)</v>
-      </c>
-      <c r="C7" s="9">
-        <f>SUM(Sheet1!D7:G7)</f>
-        <v>20536.919999999998</v>
-      </c>
-      <c r="D7" s="9">
-        <f>AVERAGE(Sheet1!D7:G7)</f>
-        <v>5134.2299999999996</v>
-      </c>
-      <c r="E7" s="9">
-        <f>MEDIAN(Sheet1!D7:F7,Sheet1!G7)</f>
-        <v>5292.0949999999993</v>
-      </c>
-      <c r="F7" s="10">
-        <f>STDEV(Sheet1!D7:G7)</f>
-        <v>1451.0492338304748</v>
-      </c>
-      <c r="G7" s="9">
-        <f>PRODUCT(Sheet1!D7,Sheet1!F7:G7)</f>
-        <v>107348911244.79958</v>
-      </c>
-      <c r="H7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A8," ",Sheet1!B8)</f>
-        <v>Jill Thomas</v>
-      </c>
-      <c r="B8" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A8, " (",Sheet1!H8,")")</f>
-        <v>Jill (Mobile App Developer)</v>
-      </c>
-      <c r="C8" s="9">
-        <f>SUM(Sheet1!D8:G8)</f>
-        <v>22228.089999999997</v>
-      </c>
-      <c r="D8" s="9">
-        <f>AVERAGE(Sheet1!D8:G8)</f>
-        <v>5557.0224999999991</v>
-      </c>
-      <c r="E8" s="9">
-        <f>MEDIAN(Sheet1!D8:F8,Sheet1!G8)</f>
-        <v>5647.27</v>
-      </c>
-      <c r="F8" s="10">
-        <f>STDEV(Sheet1!D8:G8)</f>
-        <v>1008.4312351824893</v>
-      </c>
-      <c r="G8" s="9">
-        <f>PRODUCT(Sheet1!D8,Sheet1!F8:G8)</f>
-        <v>206930333174.88055</v>
-      </c>
-      <c r="H8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A9," ",Sheet1!B9)</f>
-        <v>Kristin Ashley</v>
-      </c>
-      <c r="B9" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A9, " (",Sheet1!H9,")")</f>
-        <v>Kristin (QA Engineer)</v>
-      </c>
-      <c r="C9" s="9">
-        <f>SUM(Sheet1!D9:G9)</f>
-        <v>14240.029999999999</v>
-      </c>
-      <c r="D9" s="9">
-        <f>AVERAGE(Sheet1!D9:G9)</f>
-        <v>3560.0074999999997</v>
-      </c>
-      <c r="E9" s="9">
-        <f>MEDIAN(Sheet1!D9:F9,Sheet1!G9)</f>
-        <v>3395.2750000000001</v>
-      </c>
-      <c r="F9" s="10">
-        <f>STDEV(Sheet1!D9:G9)</f>
-        <v>523.70867533868477</v>
-      </c>
-      <c r="G9" s="9">
-        <f>PRODUCT(Sheet1!D9,Sheet1!F9:G9)</f>
-        <v>49796409013.680664</v>
-      </c>
-      <c r="H9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A10," ",Sheet1!B10)</f>
-        <v>Amanda Howard</v>
-      </c>
-      <c r="B10" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A10, " (",Sheet1!H10,")")</f>
-        <v>Amanda (Backend Developer)</v>
-      </c>
-      <c r="C10" s="9">
-        <f>SUM(Sheet1!D10:G10)</f>
-        <v>18016.830000000002</v>
-      </c>
-      <c r="D10" s="9">
-        <f>AVERAGE(Sheet1!D10:G10)</f>
-        <v>4504.2075000000004</v>
-      </c>
-      <c r="E10" s="9">
-        <f>MEDIAN(Sheet1!D10:F10,Sheet1!G10)</f>
-        <v>4344.7650000000003</v>
-      </c>
-      <c r="F10" s="10">
-        <f>STDEV(Sheet1!D10:G10)</f>
-        <v>730.13116800453304</v>
-      </c>
-      <c r="G10" s="9">
-        <f>PRODUCT(Sheet1!D10,Sheet1!F10:G10)</f>
-        <v>71890055469.734116</v>
-      </c>
-      <c r="H10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A11," ",Sheet1!B11)</f>
-        <v>Joanne Johnson</v>
-      </c>
-      <c r="B11" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A11, " (",Sheet1!H11,")")</f>
-        <v>Joanne (Product Manager)</v>
-      </c>
-      <c r="C11" s="9">
-        <f>SUM(Sheet1!D11:G11)</f>
-        <v>21615.72</v>
-      </c>
-      <c r="D11" s="9">
-        <f>AVERAGE(Sheet1!D11:G11)</f>
-        <v>5403.93</v>
-      </c>
-      <c r="E11" s="9">
-        <f>MEDIAN(Sheet1!D11:F11,Sheet1!G11)</f>
-        <v>5970.1849999999995</v>
-      </c>
-      <c r="F11" s="10">
-        <f>STDEV(Sheet1!D11:G11)</f>
-        <v>1594.0756624660767</v>
-      </c>
-      <c r="G11" s="9">
-        <f>PRODUCT(Sheet1!D11,Sheet1!F11:G11)</f>
-        <v>120367436686.89662</v>
-      </c>
-      <c r="H11" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A12," ",Sheet1!B12)</f>
-        <v>Jackie Velasquez</v>
-      </c>
-      <c r="B12" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A12, " (",Sheet1!H12,")")</f>
-        <v>Jackie (Technical Support)</v>
-      </c>
-      <c r="C12" s="9">
-        <f>SUM(Sheet1!D12:G12)</f>
-        <v>17223.73</v>
-      </c>
-      <c r="D12" s="9">
-        <f>AVERAGE(Sheet1!D12:G12)</f>
-        <v>4305.9324999999999</v>
-      </c>
-      <c r="E12" s="9">
-        <f>MEDIAN(Sheet1!D12:F12,Sheet1!G12)</f>
-        <v>3900.2999999999997</v>
-      </c>
-      <c r="F12" s="10">
-        <f>STDEV(Sheet1!D12:G12)</f>
-        <v>1451.4359064130263</v>
-      </c>
-      <c r="G12" s="9">
-        <f>PRODUCT(Sheet1!D12,Sheet1!F12:G12)</f>
-        <v>92045222022.270508</v>
-      </c>
-      <c r="H12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A13," ",Sheet1!B13)</f>
-        <v>Alan Barton</v>
-      </c>
-      <c r="B13" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A13, " (",Sheet1!H13,")")</f>
-        <v>Alan (Cloud Engineer)</v>
-      </c>
-      <c r="C13" s="9">
-        <f>SUM(Sheet1!D13:G13)</f>
-        <v>19073.71</v>
-      </c>
-      <c r="D13" s="9">
-        <f>AVERAGE(Sheet1!D13:G13)</f>
-        <v>4768.4274999999998</v>
-      </c>
-      <c r="E13" s="9">
-        <f>MEDIAN(Sheet1!D13:F13,Sheet1!G13)</f>
-        <v>4712.0300000000007</v>
-      </c>
-      <c r="F13" s="10">
-        <f>STDEV(Sheet1!D13:G13)</f>
-        <v>561.4052111368992</v>
-      </c>
-      <c r="G13" s="9">
-        <f>PRODUCT(Sheet1!D13,Sheet1!F13:G13)</f>
-        <v>103627345702.87041</v>
-      </c>
-      <c r="H13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A14," ",Sheet1!B14)</f>
-        <v>Leslie Leon</v>
-      </c>
-      <c r="B14" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A14, " (",Sheet1!H14,")")</f>
-        <v>Leslie (Data Scientist)</v>
-      </c>
-      <c r="C14" s="9">
-        <f>SUM(Sheet1!D14:G14)</f>
-        <v>20880.230000000003</v>
-      </c>
-      <c r="D14" s="9">
-        <f>AVERAGE(Sheet1!D14:G14)</f>
-        <v>5220.0575000000008</v>
-      </c>
-      <c r="E14" s="9">
-        <f>MEDIAN(Sheet1!D14:F14,Sheet1!G14)</f>
-        <v>5332.3250000000007</v>
-      </c>
-      <c r="F14" s="10">
-        <f>STDEV(Sheet1!D14:G14)</f>
-        <v>1131.6725805159615</v>
-      </c>
-      <c r="G14" s="9">
-        <f>PRODUCT(Sheet1!D14,Sheet1!F14:G14)</f>
-        <v>124110078261.20549</v>
-      </c>
-      <c r="H14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A15," ",Sheet1!B15)</f>
-        <v>Ruben Chang</v>
-      </c>
-      <c r="B15" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A15, " (",Sheet1!H15,")")</f>
-        <v>Ruben (Business Analyst)</v>
-      </c>
-      <c r="C15" s="9">
-        <f>SUM(Sheet1!D15:G15)</f>
-        <v>20198.150000000001</v>
-      </c>
-      <c r="D15" s="9">
-        <f>AVERAGE(Sheet1!D15:G15)</f>
-        <v>5049.5375000000004</v>
-      </c>
-      <c r="E15" s="9">
-        <f>MEDIAN(Sheet1!D15:F15,Sheet1!G15)</f>
-        <v>5096.8850000000002</v>
-      </c>
-      <c r="F15" s="10">
-        <f>STDEV(Sheet1!D15:G15)</f>
-        <v>1600.0705218078108</v>
-      </c>
-      <c r="G15" s="9">
-        <f>PRODUCT(Sheet1!D15,Sheet1!F15:G15)</f>
-        <v>80213777587.854767</v>
-      </c>
-      <c r="H15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A16," ",Sheet1!B16)</f>
-        <v>Kristine Myers</v>
-      </c>
-      <c r="B16" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A16, " (",Sheet1!H16,")")</f>
-        <v>Kristine (Product Manager)</v>
-      </c>
-      <c r="C16" s="9">
-        <f>SUM(Sheet1!D16:G16)</f>
-        <v>18639.140000000003</v>
-      </c>
-      <c r="D16" s="9">
-        <f>AVERAGE(Sheet1!D16:G16)</f>
-        <v>4659.7850000000008</v>
-      </c>
-      <c r="E16" s="9">
-        <f>MEDIAN(Sheet1!D16:F16,Sheet1!G16)</f>
-        <v>4450.8450000000003</v>
-      </c>
-      <c r="F16" s="10">
-        <f>STDEV(Sheet1!D16:G16)</f>
-        <v>1826.3813481764034</v>
-      </c>
-      <c r="G16" s="9">
-        <f>PRODUCT(Sheet1!D16,Sheet1!F16:G16)</f>
-        <v>64316747311.785149</v>
-      </c>
-      <c r="H16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A17," ",Sheet1!B17)</f>
-        <v>Stanley Cannon</v>
-      </c>
-      <c r="B17" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A17, " (",Sheet1!H17,")")</f>
-        <v>Stanley (Mobile App Developer)</v>
-      </c>
-      <c r="C17" s="9">
-        <f>SUM(Sheet1!D17:G17)</f>
-        <v>19397.739999999998</v>
-      </c>
-      <c r="D17" s="9">
-        <f>AVERAGE(Sheet1!D17:G17)</f>
-        <v>4849.4349999999995</v>
-      </c>
-      <c r="E17" s="9">
-        <f>MEDIAN(Sheet1!D17:F17,Sheet1!G17)</f>
-        <v>4447.9799999999996</v>
-      </c>
-      <c r="F17" s="10">
-        <f>STDEV(Sheet1!D17:G17)</f>
-        <v>1157.5710365099294</v>
-      </c>
-      <c r="G17" s="9">
-        <f>PRODUCT(Sheet1!D17,Sheet1!F17:G17)</f>
-        <v>129420325465.51807</v>
-      </c>
-      <c r="H17" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A18," ",Sheet1!B18)</f>
-        <v>Derek Stanley</v>
-      </c>
-      <c r="B18" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A18, " (",Sheet1!H18,")")</f>
-        <v>Derek (Backend Developer)</v>
-      </c>
-      <c r="C18" s="9">
-        <f>SUM(Sheet1!D18:G18)</f>
-        <v>21824.71</v>
-      </c>
-      <c r="D18" s="9">
-        <f>AVERAGE(Sheet1!D18:G18)</f>
-        <v>5456.1774999999998</v>
-      </c>
-      <c r="E18" s="9">
-        <f>MEDIAN(Sheet1!D18:F18,Sheet1!G18)</f>
-        <v>5436.165</v>
-      </c>
-      <c r="F18" s="10">
-        <f>STDEV(Sheet1!D18:G18)</f>
-        <v>968.5732299065819</v>
-      </c>
-      <c r="G18" s="9">
-        <f>PRODUCT(Sheet1!D18,Sheet1!F18:G18)</f>
-        <v>183358561081.89267</v>
-      </c>
-      <c r="H18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A19," ",Sheet1!B19)</f>
-        <v>Kevin Edwards</v>
-      </c>
-      <c r="B19" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A19, " (",Sheet1!H19,")")</f>
-        <v>Kevin (DevOps Engineer)</v>
-      </c>
-      <c r="C19" s="9">
-        <f>SUM(Sheet1!D19:G19)</f>
-        <v>18426.02</v>
-      </c>
-      <c r="D19" s="9">
-        <f>AVERAGE(Sheet1!D19:G19)</f>
-        <v>4606.5050000000001</v>
-      </c>
-      <c r="E19" s="9">
-        <f>MEDIAN(Sheet1!D19:F19,Sheet1!G19)</f>
-        <v>4403.5450000000001</v>
-      </c>
-      <c r="F19" s="10">
-        <f>STDEV(Sheet1!D19:G19)</f>
-        <v>713.64658940308993</v>
-      </c>
-      <c r="G19" s="9">
-        <f>PRODUCT(Sheet1!D19,Sheet1!F19:G19)</f>
-        <v>99125739732.658188</v>
-      </c>
-      <c r="H19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A20," ",Sheet1!B20)</f>
-        <v>George Sanchez</v>
-      </c>
-      <c r="B20" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A20, " (",Sheet1!H20,")")</f>
-        <v>George (Frontend Developer)</v>
-      </c>
-      <c r="C20" s="9">
-        <f>SUM(Sheet1!D20:G20)</f>
-        <v>22764.21</v>
-      </c>
-      <c r="D20" s="9">
-        <f>AVERAGE(Sheet1!D20:G20)</f>
-        <v>5691.0524999999998</v>
-      </c>
-      <c r="E20" s="9">
-        <f>MEDIAN(Sheet1!D20:F20,Sheet1!G20)</f>
-        <v>6265.1</v>
-      </c>
-      <c r="F20" s="10">
-        <f>STDEV(Sheet1!D20:G20)</f>
-        <v>1344.8458723679091</v>
-      </c>
-      <c r="G20" s="9">
-        <f>PRODUCT(Sheet1!D20,Sheet1!F20:G20)</f>
-        <v>155517713008.32782</v>
-      </c>
-      <c r="H20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A21," ",Sheet1!B21)</f>
-        <v>Amy Mason</v>
-      </c>
-      <c r="B21" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A21, " (",Sheet1!H21,")")</f>
-        <v>Amy (DevOps Engineer)</v>
-      </c>
-      <c r="C21" s="9">
-        <f>SUM(Sheet1!D21:G21)</f>
-        <v>24016.58</v>
-      </c>
-      <c r="D21" s="9">
-        <f>AVERAGE(Sheet1!D21:G21)</f>
-        <v>6004.1450000000004</v>
-      </c>
-      <c r="E21" s="9">
-        <f>MEDIAN(Sheet1!D21:F21,Sheet1!G21)</f>
-        <v>6666.5</v>
-      </c>
-      <c r="F21" s="10">
-        <f>STDEV(Sheet1!D21:G21)</f>
-        <v>1525.4829684507556</v>
-      </c>
-      <c r="G21" s="9">
-        <f>PRODUCT(Sheet1!D21,Sheet1!F21:G21)</f>
-        <v>165968888894.27213</v>
-      </c>
-      <c r="H21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A22," ",Sheet1!B22)</f>
-        <v>Natalie Bryant</v>
-      </c>
-      <c r="B22" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A22, " (",Sheet1!H22,")")</f>
-        <v>Natalie (UI/UX Designer)</v>
-      </c>
-      <c r="C22" s="9">
-        <f>SUM(Sheet1!D22:G22)</f>
-        <v>22008.39</v>
-      </c>
-      <c r="D22" s="9">
-        <f>AVERAGE(Sheet1!D22:G22)</f>
-        <v>5502.0974999999999</v>
-      </c>
-      <c r="E22" s="9">
-        <f>MEDIAN(Sheet1!D22:F22,Sheet1!G22)</f>
-        <v>5659.01</v>
-      </c>
-      <c r="F22" s="10">
-        <f>STDEV(Sheet1!D22:G22)</f>
-        <v>1137.8845285404286</v>
-      </c>
-      <c r="G22" s="9">
-        <f>PRODUCT(Sheet1!D22,Sheet1!F22:G22)</f>
-        <v>146461600787.33304</v>
-      </c>
-      <c r="H22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A23," ",Sheet1!B23)</f>
-        <v>Amy Mercer</v>
-      </c>
-      <c r="B23" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A23, " (",Sheet1!H23,")")</f>
-        <v>Amy (Scrum Master)</v>
-      </c>
-      <c r="C23" s="9">
-        <f>SUM(Sheet1!D23:G23)</f>
-        <v>20493.810000000001</v>
-      </c>
-      <c r="D23" s="9">
-        <f>AVERAGE(Sheet1!D23:G23)</f>
-        <v>5123.4525000000003</v>
-      </c>
-      <c r="E23" s="9">
-        <f>MEDIAN(Sheet1!D23:F23,Sheet1!G23)</f>
-        <v>5027.5650000000005</v>
-      </c>
-      <c r="F23" s="10">
-        <f>STDEV(Sheet1!D23:G23)</f>
-        <v>547.97091007795893</v>
-      </c>
-      <c r="G23" s="9">
-        <f>PRODUCT(Sheet1!D23,Sheet1!F23:G23)</f>
-        <v>147458259612.07111</v>
-      </c>
-      <c r="H23" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A24," ",Sheet1!B24)</f>
-        <v>Matthew Garza</v>
-      </c>
-      <c r="B24" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A24, " (",Sheet1!H24,")")</f>
-        <v>Matthew (Software Engineer)</v>
-      </c>
-      <c r="C24" s="9">
-        <f>SUM(Sheet1!D24:G24)</f>
-        <v>16724.97</v>
-      </c>
-      <c r="D24" s="9">
-        <f>AVERAGE(Sheet1!D24:G24)</f>
-        <v>4181.2425000000003</v>
-      </c>
-      <c r="E24" s="9">
-        <f>MEDIAN(Sheet1!D24:F24,Sheet1!G24)</f>
-        <v>4479.17</v>
-      </c>
-      <c r="F24" s="10">
-        <f>STDEV(Sheet1!D24:G24)</f>
-        <v>733.65308156625622</v>
-      </c>
-      <c r="G24" s="9">
-        <f>PRODUCT(Sheet1!D24,Sheet1!F24:G24)</f>
-        <v>93739035957.534073</v>
-      </c>
-      <c r="H24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A25," ",Sheet1!B25)</f>
-        <v>Theodore Wright</v>
-      </c>
-      <c r="B25" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A25, " (",Sheet1!H25,")")</f>
-        <v>Theodore (Frontend Developer)</v>
-      </c>
-      <c r="C25" s="9">
-        <f>SUM(Sheet1!D25:G25)</f>
-        <v>21774.05</v>
-      </c>
-      <c r="D25" s="9">
-        <f>AVERAGE(Sheet1!D25:G25)</f>
-        <v>5443.5124999999998</v>
-      </c>
-      <c r="E25" s="9">
-        <f>MEDIAN(Sheet1!D25:F25,Sheet1!G25)</f>
-        <v>5295.75</v>
-      </c>
-      <c r="F25" s="10">
-        <f>STDEV(Sheet1!D25:G25)</f>
-        <v>1384.0697617864726</v>
-      </c>
-      <c r="G25" s="9">
-        <f>PRODUCT(Sheet1!D25,Sheet1!F25:G25)</f>
-        <v>126773526660.61113</v>
-      </c>
-      <c r="H25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A26," ",Sheet1!B26)</f>
-        <v>Kayla West</v>
-      </c>
-      <c r="B26" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A26, " (",Sheet1!H26,")")</f>
-        <v>Kayla (Mobile App Developer)</v>
-      </c>
-      <c r="C26" s="9">
-        <f>SUM(Sheet1!D26:G26)</f>
-        <v>14105.11</v>
-      </c>
-      <c r="D26" s="9">
-        <f>AVERAGE(Sheet1!D26:G26)</f>
-        <v>3526.2775000000001</v>
-      </c>
-      <c r="E26" s="9">
-        <f>MEDIAN(Sheet1!D26:F26,Sheet1!G26)</f>
-        <v>3577.7</v>
-      </c>
-      <c r="F26" s="10">
-        <f>STDEV(Sheet1!D26:G26)</f>
-        <v>374.17851651985598</v>
-      </c>
-      <c r="G26" s="9">
-        <f>PRODUCT(Sheet1!D26,Sheet1!F26:G26)</f>
-        <v>49787488719.748901</v>
-      </c>
-      <c r="H26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A27," ",Sheet1!B27)</f>
-        <v>Jesse Carter</v>
-      </c>
-      <c r="B27" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A27, " (",Sheet1!H27,")")</f>
-        <v>Jesse (QA Engineer)</v>
-      </c>
-      <c r="C27" s="9">
-        <f>SUM(Sheet1!D27:G27)</f>
-        <v>20233.919999999998</v>
-      </c>
-      <c r="D27" s="9">
-        <f>AVERAGE(Sheet1!D27:G27)</f>
-        <v>5058.4799999999996</v>
-      </c>
-      <c r="E27" s="9">
-        <f>MEDIAN(Sheet1!D27:F27,Sheet1!G27)</f>
-        <v>5011.4549999999999</v>
-      </c>
-      <c r="F27" s="10">
-        <f>STDEV(Sheet1!D27:G27)</f>
-        <v>1304.2718354954509</v>
-      </c>
-      <c r="G27" s="9">
-        <f>PRODUCT(Sheet1!D27,Sheet1!F27:G27)</f>
-        <v>112902533972.24257</v>
-      </c>
-      <c r="H27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A28," ",Sheet1!B28)</f>
-        <v>Carlos Vega</v>
-      </c>
-      <c r="B28" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A28, " (",Sheet1!H28,")")</f>
-        <v>Carlos (Technical Support)</v>
-      </c>
-      <c r="C28" s="9">
-        <f>SUM(Sheet1!D28:G28)</f>
-        <v>17441.5</v>
-      </c>
-      <c r="D28" s="9">
-        <f>AVERAGE(Sheet1!D28:G28)</f>
-        <v>4360.375</v>
-      </c>
-      <c r="E28" s="9">
-        <f>MEDIAN(Sheet1!D28:F28,Sheet1!G28)</f>
-        <v>4136.25</v>
-      </c>
-      <c r="F28" s="10">
-        <f>STDEV(Sheet1!D28:G28)</f>
-        <v>855.06618958222452</v>
-      </c>
-      <c r="G28" s="9">
-        <f>PRODUCT(Sheet1!D28,Sheet1!F28:G28)</f>
-        <v>94430736121.629593</v>
-      </c>
-      <c r="H28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A29," ",Sheet1!B29)</f>
-        <v>Bridget Keith</v>
-      </c>
-      <c r="B29" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A29, " (",Sheet1!H29,")")</f>
-        <v>Bridget (UI/UX Designer)</v>
-      </c>
-      <c r="C29" s="9">
-        <f>SUM(Sheet1!D29:G29)</f>
-        <v>18843.07</v>
-      </c>
-      <c r="D29" s="9">
-        <f>AVERAGE(Sheet1!D29:G29)</f>
-        <v>4710.7674999999999</v>
-      </c>
-      <c r="E29" s="9">
-        <f>MEDIAN(Sheet1!D29:F29,Sheet1!G29)</f>
-        <v>4224.9949999999999</v>
-      </c>
-      <c r="F29" s="10">
-        <f>STDEV(Sheet1!D29:G29)</f>
-        <v>1519.7799713856623</v>
-      </c>
-      <c r="G29" s="9">
-        <f>PRODUCT(Sheet1!D29,Sheet1!F29:G29)</f>
-        <v>92860492703.391556</v>
-      </c>
-      <c r="H29" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A30," ",Sheet1!B30)</f>
-        <v>William Duncan</v>
-      </c>
-      <c r="B30" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A30, " (",Sheet1!H30,")")</f>
-        <v>William (Security Analyst)</v>
-      </c>
-      <c r="C30" s="9">
-        <f>SUM(Sheet1!D30:G30)</f>
-        <v>18384.02</v>
-      </c>
-      <c r="D30" s="9">
-        <f>AVERAGE(Sheet1!D30:G30)</f>
-        <v>4596.0050000000001</v>
-      </c>
-      <c r="E30" s="9">
-        <f>MEDIAN(Sheet1!D30:F30,Sheet1!G30)</f>
-        <v>4342.2350000000006</v>
-      </c>
-      <c r="F30" s="10">
-        <f>STDEV(Sheet1!D30:G30)</f>
-        <v>1538.4899608923899</v>
-      </c>
-      <c r="G30" s="9">
-        <f>PRODUCT(Sheet1!D30,Sheet1!F30:G30)</f>
-        <v>70240152244.86557</v>
-      </c>
-      <c r="H30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A31," ",Sheet1!B31)</f>
-        <v>John Hernandez</v>
-      </c>
-      <c r="B31" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A31, " (",Sheet1!H31,")")</f>
-        <v>John (UI/UX Designer)</v>
-      </c>
-      <c r="C31" s="9">
-        <f>SUM(Sheet1!D31:G31)</f>
-        <v>15916.75</v>
-      </c>
-      <c r="D31" s="9">
-        <f>AVERAGE(Sheet1!D31:G31)</f>
-        <v>3979.1875</v>
-      </c>
-      <c r="E31" s="9">
-        <f>MEDIAN(Sheet1!D31:F31,Sheet1!G31)</f>
-        <v>4064.09</v>
-      </c>
-      <c r="F31" s="10">
-        <f>STDEV(Sheet1!D31:G31)</f>
-        <v>706.83200726316159</v>
-      </c>
-      <c r="G31" s="9">
-        <f>PRODUCT(Sheet1!D31,Sheet1!F31:G31)</f>
-        <v>50275890927.047287</v>
-      </c>
-      <c r="H31" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A32," ",Sheet1!B32)</f>
-        <v>Jesse Murray</v>
-      </c>
-      <c r="B32" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A32, " (",Sheet1!H32,")")</f>
-        <v>Jesse (Security Analyst)</v>
-      </c>
-      <c r="C32" s="9">
-        <f>SUM(Sheet1!D32:G32)</f>
-        <v>18740.980000000003</v>
-      </c>
-      <c r="D32" s="9">
-        <f>AVERAGE(Sheet1!D32:G32)</f>
-        <v>4685.2450000000008</v>
-      </c>
-      <c r="E32" s="9">
-        <f>MEDIAN(Sheet1!D32:F32,Sheet1!G32)</f>
-        <v>4510.5300000000007</v>
-      </c>
-      <c r="F32" s="10">
-        <f>STDEV(Sheet1!D32:G32)</f>
-        <v>1679.5520275259892</v>
-      </c>
-      <c r="G32" s="9">
-        <f>PRODUCT(Sheet1!D32,Sheet1!F32:G32)</f>
-        <v>111367491422.6749</v>
-      </c>
-      <c r="H32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A33," ",Sheet1!B33)</f>
-        <v>Stephen Haynes</v>
-      </c>
-      <c r="B33" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A33, " (",Sheet1!H33,")")</f>
-        <v>Stephen (Technical Support)</v>
-      </c>
-      <c r="C33" s="9">
-        <f>SUM(Sheet1!D33:G33)</f>
-        <v>20347.879999999997</v>
-      </c>
-      <c r="D33" s="9">
-        <f>AVERAGE(Sheet1!D33:G33)</f>
-        <v>5086.9699999999993</v>
-      </c>
-      <c r="E33" s="9">
-        <f>MEDIAN(Sheet1!D33:F33,Sheet1!G33)</f>
-        <v>5137.9650000000001</v>
-      </c>
-      <c r="F33" s="10">
-        <f>STDEV(Sheet1!D33:G33)</f>
-        <v>2070.2973758536878</v>
-      </c>
-      <c r="G33" s="9">
-        <f>PRODUCT(Sheet1!D33,Sheet1!F33:G33)</f>
-        <v>76005189473.290848</v>
-      </c>
-      <c r="H33" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A34," ",Sheet1!B34)</f>
-        <v>Samuel Smith</v>
-      </c>
-      <c r="B34" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A34, " (",Sheet1!H34,")")</f>
-        <v>Samuel (System Administrator)</v>
-      </c>
-      <c r="C34" s="9">
-        <f>SUM(Sheet1!D34:G34)</f>
-        <v>18052.490000000002</v>
-      </c>
-      <c r="D34" s="9">
-        <f>AVERAGE(Sheet1!D34:G34)</f>
-        <v>4513.1225000000004</v>
-      </c>
-      <c r="E34" s="9">
-        <f>MEDIAN(Sheet1!D34:F34,Sheet1!G34)</f>
-        <v>4648.24</v>
-      </c>
-      <c r="F34" s="10">
-        <f>STDEV(Sheet1!D34:G34)</f>
-        <v>1069.434287785677</v>
-      </c>
-      <c r="G34" s="9">
-        <f>PRODUCT(Sheet1!D34,Sheet1!F34:G34)</f>
-        <v>68690336616.366364</v>
-      </c>
-      <c r="H34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A35," ",Sheet1!B35)</f>
-        <v>Russell Moore</v>
-      </c>
-      <c r="B35" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A35, " (",Sheet1!H35,")")</f>
-        <v>Russell (Full Stack Developer)</v>
-      </c>
-      <c r="C35" s="9">
-        <f>SUM(Sheet1!D35:G35)</f>
-        <v>18526.12</v>
-      </c>
-      <c r="D35" s="9">
-        <f>AVERAGE(Sheet1!D35:G35)</f>
-        <v>4631.53</v>
-      </c>
-      <c r="E35" s="9">
-        <f>MEDIAN(Sheet1!D35:F35,Sheet1!G35)</f>
-        <v>4393.3999999999996</v>
-      </c>
-      <c r="F35" s="10">
-        <f>STDEV(Sheet1!D35:G35)</f>
-        <v>1087.8079752725971</v>
-      </c>
-      <c r="G35" s="9">
-        <f>PRODUCT(Sheet1!D35,Sheet1!F35:G35)</f>
-        <v>85087773454.95694</v>
-      </c>
-      <c r="H35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A36," ",Sheet1!B36)</f>
-        <v>Brenda Delgado</v>
-      </c>
-      <c r="B36" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A36, " (",Sheet1!H36,")")</f>
-        <v>Brenda (Business Analyst)</v>
-      </c>
-      <c r="C36" s="9">
-        <f>SUM(Sheet1!D36:G36)</f>
-        <v>17212.75</v>
-      </c>
-      <c r="D36" s="9">
-        <f>AVERAGE(Sheet1!D36:G36)</f>
-        <v>4303.1875</v>
-      </c>
-      <c r="E36" s="9">
-        <f>MEDIAN(Sheet1!D36:F36,Sheet1!G36)</f>
-        <v>4527.6350000000002</v>
-      </c>
-      <c r="F36" s="10">
-        <f>STDEV(Sheet1!D36:G36)</f>
-        <v>861.28250074622201</v>
-      </c>
-      <c r="G36" s="9">
-        <f>PRODUCT(Sheet1!D36,Sheet1!F36:G36)</f>
-        <v>103003129353.65613</v>
-      </c>
-      <c r="H36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A37," ",Sheet1!B37)</f>
-        <v>Lindsey Kline</v>
-      </c>
-      <c r="B37" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A37, " (",Sheet1!H37,")")</f>
-        <v>Lindsey (Scrum Master)</v>
-      </c>
-      <c r="C37" s="9">
-        <f>SUM(Sheet1!D37:G37)</f>
-        <v>18057.39</v>
-      </c>
-      <c r="D37" s="9">
-        <f>AVERAGE(Sheet1!D37:G37)</f>
-        <v>4514.3474999999999</v>
-      </c>
-      <c r="E37" s="9">
-        <f>MEDIAN(Sheet1!D37:F37,Sheet1!G37)</f>
-        <v>4124.8950000000004</v>
-      </c>
-      <c r="F37" s="10">
-        <f>STDEV(Sheet1!D37:G37)</f>
-        <v>1695.1464024556487</v>
-      </c>
-      <c r="G37" s="9">
-        <f>PRODUCT(Sheet1!D37,Sheet1!F37:G37)</f>
-        <v>104296013508.78088</v>
-      </c>
-      <c r="H37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A38," ",Sheet1!B38)</f>
-        <v>Shelia Sanchez</v>
-      </c>
-      <c r="B38" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A38, " (",Sheet1!H38,")")</f>
-        <v>Shelia (Software Engineer)</v>
-      </c>
-      <c r="C38" s="9">
-        <f>SUM(Sheet1!D38:G38)</f>
-        <v>20384.18</v>
-      </c>
-      <c r="D38" s="9">
-        <f>AVERAGE(Sheet1!D38:G38)</f>
-        <v>5096.0450000000001</v>
-      </c>
-      <c r="E38" s="9">
-        <f>MEDIAN(Sheet1!D38:F38,Sheet1!G38)</f>
-        <v>4864.1549999999997</v>
-      </c>
-      <c r="F38" s="10">
-        <f>STDEV(Sheet1!D38:G38)</f>
-        <v>1540.3343826260568</v>
-      </c>
-      <c r="G38" s="9">
-        <f>PRODUCT(Sheet1!D38,Sheet1!F38:G38)</f>
-        <v>100175530665.01782</v>
-      </c>
-      <c r="H38" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A39," ",Sheet1!B39)</f>
-        <v>Holly Christensen</v>
-      </c>
-      <c r="B39" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A39, " (",Sheet1!H39,")")</f>
-        <v>Holly (Technical Support)</v>
-      </c>
-      <c r="C39" s="9">
-        <f>SUM(Sheet1!D39:G39)</f>
-        <v>21184.25</v>
-      </c>
-      <c r="D39" s="9">
-        <f>AVERAGE(Sheet1!D39:G39)</f>
-        <v>5296.0625</v>
-      </c>
-      <c r="E39" s="9">
-        <f>MEDIAN(Sheet1!D39:F39,Sheet1!G39)</f>
-        <v>5232</v>
-      </c>
-      <c r="F39" s="10">
-        <f>STDEV(Sheet1!D39:G39)</f>
-        <v>1067.8809072605738</v>
-      </c>
-      <c r="G39" s="9">
-        <f>PRODUCT(Sheet1!D39,Sheet1!F39:G39)</f>
-        <v>181642058416.75967</v>
-      </c>
-      <c r="H39" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A40," ",Sheet1!B40)</f>
-        <v>Jason Johnson</v>
-      </c>
-      <c r="B40" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A40, " (",Sheet1!H40,")")</f>
-        <v>Jason (Frontend Developer)</v>
-      </c>
-      <c r="C40" s="9">
-        <f>SUM(Sheet1!D40:G40)</f>
-        <v>19594.850000000002</v>
-      </c>
-      <c r="D40" s="9">
-        <f>AVERAGE(Sheet1!D40:G40)</f>
-        <v>4898.7125000000005</v>
-      </c>
-      <c r="E40" s="9">
-        <f>MEDIAN(Sheet1!D40:F40,Sheet1!G40)</f>
-        <v>4757.7700000000004</v>
-      </c>
-      <c r="F40" s="10">
-        <f>STDEV(Sheet1!D40:G40)</f>
-        <v>748.48175080736246</v>
-      </c>
-      <c r="G40" s="9">
-        <f>PRODUCT(Sheet1!D40,Sheet1!F40:G40)</f>
-        <v>95383513583.054611</v>
-      </c>
-      <c r="H40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A41," ",Sheet1!B41)</f>
-        <v>Melissa Garcia</v>
-      </c>
-      <c r="B41" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A41, " (",Sheet1!H41,")")</f>
-        <v>Melissa (Frontend Developer)</v>
-      </c>
-      <c r="C41" s="9">
-        <f>SUM(Sheet1!D41:G41)</f>
-        <v>18702.18</v>
-      </c>
-      <c r="D41" s="9">
-        <f>AVERAGE(Sheet1!D41:G41)</f>
-        <v>4675.5450000000001</v>
-      </c>
-      <c r="E41" s="9">
-        <f>MEDIAN(Sheet1!D41:F41,Sheet1!G41)</f>
-        <v>4616.6750000000002</v>
-      </c>
-      <c r="F41" s="10">
-        <f>STDEV(Sheet1!D41:G41)</f>
-        <v>1006.9539666571977</v>
-      </c>
-      <c r="G41" s="9">
-        <f>PRODUCT(Sheet1!D41,Sheet1!F41:G41)</f>
-        <v>115557249581.30246</v>
-      </c>
-      <c r="H41" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A42," ",Sheet1!B42)</f>
-        <v>Amanda Hayes</v>
-      </c>
-      <c r="B42" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A42, " (",Sheet1!H42,")")</f>
-        <v>Amanda (Software Engineer)</v>
-      </c>
-      <c r="C42" s="9">
-        <f>SUM(Sheet1!D42:G42)</f>
-        <v>18176.54</v>
-      </c>
-      <c r="D42" s="9">
-        <f>AVERAGE(Sheet1!D42:G42)</f>
-        <v>4544.1350000000002</v>
-      </c>
-      <c r="E42" s="9">
-        <f>MEDIAN(Sheet1!D42:F42,Sheet1!G42)</f>
-        <v>4316.99</v>
-      </c>
-      <c r="F42" s="10">
-        <f>STDEV(Sheet1!D42:G42)</f>
-        <v>1045.0258708280862</v>
-      </c>
-      <c r="G42" s="9">
-        <f>PRODUCT(Sheet1!D42,Sheet1!F42:G42)</f>
-        <v>66134319202.563507</v>
-      </c>
-      <c r="H42" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A43," ",Sheet1!B43)</f>
-        <v>Abigail Wright</v>
-      </c>
-      <c r="B43" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A43, " (",Sheet1!H43,")")</f>
-        <v>Abigail (Scrum Master)</v>
-      </c>
-      <c r="C43" s="9">
-        <f>SUM(Sheet1!D43:G43)</f>
-        <v>24252.629999999997</v>
-      </c>
-      <c r="D43" s="9">
-        <f>AVERAGE(Sheet1!D43:G43)</f>
-        <v>6063.1574999999993</v>
-      </c>
-      <c r="E43" s="9">
-        <f>MEDIAN(Sheet1!D43:F43,Sheet1!G43)</f>
-        <v>6148.6299999999992</v>
-      </c>
-      <c r="F43" s="10">
-        <f>STDEV(Sheet1!D43:G43)</f>
-        <v>538.28865009862488</v>
-      </c>
-      <c r="G43" s="9">
-        <f>PRODUCT(Sheet1!D43,Sheet1!F43:G43)</f>
-        <v>202739188049.12485</v>
-      </c>
-      <c r="H43" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A44," ",Sheet1!B44)</f>
-        <v>Deborah Warren</v>
-      </c>
-      <c r="B44" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A44, " (",Sheet1!H44,")")</f>
-        <v>Deborah (Frontend Developer)</v>
-      </c>
-      <c r="C44" s="9">
-        <f>SUM(Sheet1!D44:G44)</f>
-        <v>21204.370000000003</v>
-      </c>
-      <c r="D44" s="9">
-        <f>AVERAGE(Sheet1!D44:G44)</f>
-        <v>5301.0925000000007</v>
-      </c>
-      <c r="E44" s="9">
-        <f>MEDIAN(Sheet1!D44:F44,Sheet1!G44)</f>
-        <v>5176.9400000000005</v>
-      </c>
-      <c r="F44" s="10">
-        <f>STDEV(Sheet1!D44:G44)</f>
-        <v>1203.3860243046106</v>
-      </c>
-      <c r="G44" s="9">
-        <f>PRODUCT(Sheet1!D44,Sheet1!F44:G44)</f>
-        <v>174873133677.57263</v>
-      </c>
-      <c r="H44" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A45," ",Sheet1!B45)</f>
-        <v>Megan Mullins</v>
-      </c>
-      <c r="B45" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A45, " (",Sheet1!H45,")")</f>
-        <v>Megan (System Administrator)</v>
-      </c>
-      <c r="C45" s="9">
-        <f>SUM(Sheet1!D45:G45)</f>
-        <v>19659.090000000004</v>
-      </c>
-      <c r="D45" s="9">
-        <f>AVERAGE(Sheet1!D45:G45)</f>
-        <v>4914.7725000000009</v>
-      </c>
-      <c r="E45" s="9">
-        <f>MEDIAN(Sheet1!D45:F45,Sheet1!G45)</f>
-        <v>4765.6900000000005</v>
-      </c>
-      <c r="F45" s="10">
-        <f>STDEV(Sheet1!D45:G45)</f>
-        <v>1224.2083787867391</v>
-      </c>
-      <c r="G45" s="9">
-        <f>PRODUCT(Sheet1!D45,Sheet1!F45:G45)</f>
-        <v>106737019199.38828</v>
-      </c>
-      <c r="H45" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A46," ",Sheet1!B46)</f>
-        <v>Lynn Diaz</v>
-      </c>
-      <c r="B46" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A46, " (",Sheet1!H46,")")</f>
-        <v>Lynn (Mobile App Developer)</v>
-      </c>
-      <c r="C46" s="9">
-        <f>SUM(Sheet1!D46:G46)</f>
-        <v>18686.379999999997</v>
-      </c>
-      <c r="D46" s="9">
-        <f>AVERAGE(Sheet1!D46:G46)</f>
-        <v>4671.5949999999993</v>
-      </c>
-      <c r="E46" s="9">
-        <f>MEDIAN(Sheet1!D46:F46,Sheet1!G46)</f>
-        <v>4463.1149999999998</v>
-      </c>
-      <c r="F46" s="10">
-        <f>STDEV(Sheet1!D46:G46)</f>
-        <v>1472.7776651506738</v>
-      </c>
-      <c r="G46" s="9">
-        <f>PRODUCT(Sheet1!D46,Sheet1!F46:G46)</f>
-        <v>128946644828.8494</v>
-      </c>
-      <c r="H46" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A47," ",Sheet1!B47)</f>
-        <v>Suzanne Robbins</v>
-      </c>
-      <c r="B47" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A47, " (",Sheet1!H47,")")</f>
-        <v>Suzanne (Data Scientist)</v>
-      </c>
-      <c r="C47" s="9">
-        <f>SUM(Sheet1!D47:G47)</f>
-        <v>22555.739999999998</v>
-      </c>
-      <c r="D47" s="9">
-        <f>AVERAGE(Sheet1!D47:G47)</f>
-        <v>5638.9349999999995</v>
-      </c>
-      <c r="E47" s="9">
-        <f>MEDIAN(Sheet1!D47:F47,Sheet1!G47)</f>
-        <v>5605.87</v>
-      </c>
-      <c r="F47" s="10">
-        <f>STDEV(Sheet1!D47:G47)</f>
-        <v>466.24504962519467</v>
-      </c>
-      <c r="G47" s="9">
-        <f>PRODUCT(Sheet1!D47,Sheet1!F47:G47)</f>
-        <v>161034640803.93109</v>
-      </c>
-      <c r="H47" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A48," ",Sheet1!B48)</f>
-        <v>Michelle Goodman</v>
-      </c>
-      <c r="B48" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A48, " (",Sheet1!H48,")")</f>
-        <v>Michelle (System Administrator)</v>
-      </c>
-      <c r="C48" s="9">
-        <f>SUM(Sheet1!D48:G48)</f>
-        <v>23021.87</v>
-      </c>
-      <c r="D48" s="9">
-        <f>AVERAGE(Sheet1!D48:G48)</f>
-        <v>5755.4674999999997</v>
-      </c>
-      <c r="E48" s="9">
-        <f>MEDIAN(Sheet1!D48:F48,Sheet1!G48)</f>
-        <v>6104.77</v>
-      </c>
-      <c r="F48" s="10">
-        <f>STDEV(Sheet1!D48:G48)</f>
-        <v>1245.4776305598587</v>
-      </c>
-      <c r="G48" s="9">
-        <f>PRODUCT(Sheet1!D48,Sheet1!F48:G48)</f>
-        <v>249717821655.48135</v>
-      </c>
-      <c r="H48" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A49," ",Sheet1!B49)</f>
-        <v>Elizabeth Richards</v>
-      </c>
-      <c r="B49" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A49, " (",Sheet1!H49,")")</f>
-        <v>Elizabeth (Mobile App Developer)</v>
-      </c>
-      <c r="C49" s="9">
-        <f>SUM(Sheet1!D49:G49)</f>
-        <v>19871.43</v>
-      </c>
-      <c r="D49" s="9">
-        <f>AVERAGE(Sheet1!D49:G49)</f>
-        <v>4967.8575000000001</v>
-      </c>
-      <c r="E49" s="9">
-        <f>MEDIAN(Sheet1!D49:F49,Sheet1!G49)</f>
-        <v>4922.0349999999999</v>
-      </c>
-      <c r="F49" s="10">
-        <f>STDEV(Sheet1!D49:G49)</f>
-        <v>1805.9322798557537</v>
-      </c>
-      <c r="G49" s="9">
-        <f>PRODUCT(Sheet1!D49,Sheet1!F49:G49)</f>
-        <v>77273871180.187515</v>
-      </c>
-      <c r="H49" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A50," ",Sheet1!B50)</f>
-        <v>Jeffrey Miller</v>
-      </c>
-      <c r="B50" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A50, " (",Sheet1!H50,")")</f>
-        <v>Jeffrey (QA Engineer)</v>
-      </c>
-      <c r="C50" s="9">
-        <f>SUM(Sheet1!D50:G50)</f>
-        <v>16669.78</v>
-      </c>
-      <c r="D50" s="9">
-        <f>AVERAGE(Sheet1!D50:G50)</f>
-        <v>4167.4449999999997</v>
-      </c>
-      <c r="E50" s="9">
-        <f>MEDIAN(Sheet1!D50:F50,Sheet1!G50)</f>
-        <v>4459.125</v>
-      </c>
-      <c r="F50" s="10">
-        <f>STDEV(Sheet1!D50:G50)</f>
-        <v>662.541268676909</v>
-      </c>
-      <c r="G50" s="9">
-        <f>PRODUCT(Sheet1!D50,Sheet1!F50:G50)</f>
-        <v>90952122667.10614</v>
-      </c>
-      <c r="H50" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A51," ",Sheet1!B51)</f>
-        <v>Catherine Welch</v>
-      </c>
-      <c r="B51" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A51, " (",Sheet1!H51,")")</f>
-        <v>Catherine (Product Manager)</v>
-      </c>
-      <c r="C51" s="9">
-        <f>SUM(Sheet1!D51:G51)</f>
-        <v>21733.079999999998</v>
-      </c>
-      <c r="D51" s="9">
-        <f>AVERAGE(Sheet1!D51:G51)</f>
-        <v>5433.2699999999995</v>
-      </c>
-      <c r="E51" s="9">
-        <f>MEDIAN(Sheet1!D51:F51,Sheet1!G51)</f>
-        <v>5708.68</v>
-      </c>
-      <c r="F51" s="10">
-        <f>STDEV(Sheet1!D51:G51)</f>
-        <v>1404.8083472369722</v>
-      </c>
-      <c r="G51" s="9">
-        <f>PRODUCT(Sheet1!D51,Sheet1!F51:G51)</f>
-        <v>214977580537.83859</v>
-      </c>
-      <c r="H51" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A52," ",Sheet1!B52)</f>
-        <v>Nicholas Nelson</v>
-      </c>
-      <c r="B52" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A52, " (",Sheet1!H52,")")</f>
-        <v>Nicholas (DevOps Engineer)</v>
-      </c>
-      <c r="C52" s="9">
-        <f>SUM(Sheet1!D52:G52)</f>
-        <v>20662.669999999998</v>
-      </c>
-      <c r="D52" s="9">
-        <f>AVERAGE(Sheet1!D52:G52)</f>
-        <v>5165.6674999999996</v>
-      </c>
-      <c r="E52" s="9">
-        <f>MEDIAN(Sheet1!D52:F52,Sheet1!G52)</f>
-        <v>4970.2999999999993</v>
-      </c>
-      <c r="F52" s="10">
-        <f>STDEV(Sheet1!D52:G52)</f>
-        <v>1270.4741508947243</v>
-      </c>
-      <c r="G52" s="9">
-        <f>PRODUCT(Sheet1!D52,Sheet1!F52:G52)</f>
-        <v>120864070328.31143</v>
-      </c>
-      <c r="H52" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A53," ",Sheet1!B53)</f>
-        <v>James Diaz</v>
-      </c>
-      <c r="B53" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A53, " (",Sheet1!H53,")")</f>
-        <v>James (Data Scientist)</v>
-      </c>
-      <c r="C53" s="9">
-        <f>SUM(Sheet1!D53:G53)</f>
-        <v>22507.42</v>
-      </c>
-      <c r="D53" s="9">
-        <f>AVERAGE(Sheet1!D53:G53)</f>
-        <v>5626.8549999999996</v>
-      </c>
-      <c r="E53" s="9">
-        <f>MEDIAN(Sheet1!D53:F53,Sheet1!G53)</f>
-        <v>5606.3249999999998</v>
-      </c>
-      <c r="F53" s="10">
-        <f>STDEV(Sheet1!D53:G53)</f>
-        <v>1198.1333971501972</v>
-      </c>
-      <c r="G53" s="9">
-        <f>PRODUCT(Sheet1!D53,Sheet1!F53:G53)</f>
-        <v>214333731457.7637</v>
-      </c>
-      <c r="H53" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A54," ",Sheet1!B54)</f>
-        <v>Lori Evans</v>
-      </c>
-      <c r="B54" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A54, " (",Sheet1!H54,")")</f>
-        <v>Lori (Technical Support)</v>
-      </c>
-      <c r="C54" s="9">
-        <f>SUM(Sheet1!D54:G54)</f>
-        <v>19224.239999999998</v>
-      </c>
-      <c r="D54" s="9">
-        <f>AVERAGE(Sheet1!D54:G54)</f>
-        <v>4806.0599999999995</v>
-      </c>
-      <c r="E54" s="9">
-        <f>MEDIAN(Sheet1!D54:F54,Sheet1!G54)</f>
-        <v>4594.3999999999996</v>
-      </c>
-      <c r="F54" s="10">
-        <f>STDEV(Sheet1!D54:G54)</f>
-        <v>1043.4307881535187</v>
-      </c>
-      <c r="G54" s="9">
-        <f>PRODUCT(Sheet1!D54,Sheet1!F54:G54)</f>
-        <v>79763929709.800705</v>
-      </c>
-      <c r="H54" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A55," ",Sheet1!B55)</f>
-        <v>Zachary Lopez</v>
-      </c>
-      <c r="B55" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A55, " (",Sheet1!H55,")")</f>
-        <v>Zachary (System Administrator)</v>
-      </c>
-      <c r="C55" s="9">
-        <f>SUM(Sheet1!D55:G55)</f>
-        <v>23228.14</v>
-      </c>
-      <c r="D55" s="9">
-        <f>AVERAGE(Sheet1!D55:G55)</f>
-        <v>5807.0349999999999</v>
-      </c>
-      <c r="E55" s="9">
-        <f>MEDIAN(Sheet1!D55:F55,Sheet1!G55)</f>
-        <v>5764.0450000000001</v>
-      </c>
-      <c r="F55" s="10">
-        <f>STDEV(Sheet1!D55:G55)</f>
-        <v>561.05101458482966</v>
-      </c>
-      <c r="G55" s="9">
-        <f>PRODUCT(Sheet1!D55,Sheet1!F55:G55)</f>
-        <v>213121017852.15479</v>
-      </c>
-      <c r="H55" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A56," ",Sheet1!B56)</f>
-        <v>Michael Gray</v>
-      </c>
-      <c r="B56" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A56, " (",Sheet1!H56,")")</f>
-        <v>Michael (Full Stack Developer)</v>
-      </c>
-      <c r="C56" s="9">
-        <f>SUM(Sheet1!D56:G56)</f>
-        <v>21206.22</v>
-      </c>
-      <c r="D56" s="9">
-        <f>AVERAGE(Sheet1!D56:G56)</f>
-        <v>5301.5550000000003</v>
-      </c>
-      <c r="E56" s="9">
-        <f>MEDIAN(Sheet1!D56:F56,Sheet1!G56)</f>
-        <v>5829.6749999999993</v>
-      </c>
-      <c r="F56" s="10">
-        <f>STDEV(Sheet1!D56:G56)</f>
-        <v>1559.00287296079</v>
-      </c>
-      <c r="G56" s="9">
-        <f>PRODUCT(Sheet1!D56,Sheet1!F56:G56)</f>
-        <v>102897099516.02682</v>
-      </c>
-      <c r="H56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A57," ",Sheet1!B57)</f>
-        <v>Charles Bradford</v>
-      </c>
-      <c r="B57" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A57, " (",Sheet1!H57,")")</f>
-        <v>Charles (Scrum Master)</v>
-      </c>
-      <c r="C57" s="9">
-        <f>SUM(Sheet1!D57:G57)</f>
-        <v>17344.05</v>
-      </c>
-      <c r="D57" s="9">
-        <f>AVERAGE(Sheet1!D57:G57)</f>
-        <v>4336.0124999999998</v>
-      </c>
-      <c r="E57" s="9">
-        <f>MEDIAN(Sheet1!D57:F57,Sheet1!G57)</f>
-        <v>4358.2250000000004</v>
-      </c>
-      <c r="F57" s="10">
-        <f>STDEV(Sheet1!D57:G57)</f>
-        <v>1317.1260867604919</v>
-      </c>
-      <c r="G57" s="9">
-        <f>PRODUCT(Sheet1!D57,Sheet1!F57:G57)</f>
-        <v>101798928932.99014</v>
-      </c>
-      <c r="H57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A58," ",Sheet1!B58)</f>
-        <v>Joshua Peters</v>
-      </c>
-      <c r="B58" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A58, " (",Sheet1!H58,")")</f>
-        <v>Joshua (Backend Developer)</v>
-      </c>
-      <c r="C58" s="9">
-        <f>SUM(Sheet1!D58:G58)</f>
-        <v>15219.650000000001</v>
-      </c>
-      <c r="D58" s="9">
-        <f>AVERAGE(Sheet1!D58:G58)</f>
-        <v>3804.9125000000004</v>
-      </c>
-      <c r="E58" s="9">
-        <f>MEDIAN(Sheet1!D58:F58,Sheet1!G58)</f>
-        <v>3883.4250000000002</v>
-      </c>
-      <c r="F58" s="10">
-        <f>STDEV(Sheet1!D58:G58)</f>
-        <v>575.72555118881451</v>
-      </c>
-      <c r="G58" s="9">
-        <f>PRODUCT(Sheet1!D58,Sheet1!F58:G58)</f>
-        <v>47962553772.182457</v>
-      </c>
-      <c r="H58" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A59," ",Sheet1!B59)</f>
-        <v>Adam Mckinney</v>
-      </c>
-      <c r="B59" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A59, " (",Sheet1!H59,")")</f>
-        <v>Adam (Data Scientist)</v>
-      </c>
-      <c r="C59" s="9">
-        <f>SUM(Sheet1!D59:G59)</f>
-        <v>15557.39</v>
-      </c>
-      <c r="D59" s="9">
-        <f>AVERAGE(Sheet1!D59:G59)</f>
-        <v>3889.3474999999999</v>
-      </c>
-      <c r="E59" s="9">
-        <f>MEDIAN(Sheet1!D59:F59,Sheet1!G59)</f>
-        <v>3834.375</v>
-      </c>
-      <c r="F59" s="10">
-        <f>STDEV(Sheet1!D59:G59)</f>
-        <v>609.248544212458</v>
-      </c>
-      <c r="G59" s="9">
-        <f>PRODUCT(Sheet1!D59,Sheet1!F59:G59)</f>
-        <v>65492006729.333176</v>
-      </c>
-      <c r="H59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A60," ",Sheet1!B60)</f>
-        <v>Devin Roberts</v>
-      </c>
-      <c r="B60" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A60, " (",Sheet1!H60,")")</f>
-        <v>Devin (DevOps Engineer)</v>
-      </c>
-      <c r="C60" s="9">
-        <f>SUM(Sheet1!D60:G60)</f>
-        <v>18890.27</v>
-      </c>
-      <c r="D60" s="9">
-        <f>AVERAGE(Sheet1!D60:G60)</f>
-        <v>4722.5675000000001</v>
-      </c>
-      <c r="E60" s="9">
-        <f>MEDIAN(Sheet1!D60:F60,Sheet1!G60)</f>
-        <v>4516.88</v>
-      </c>
-      <c r="F60" s="10">
-        <f>STDEV(Sheet1!D60:G60)</f>
-        <v>1269.2449021202856</v>
-      </c>
-      <c r="G60" s="9">
-        <f>PRODUCT(Sheet1!D60,Sheet1!F60:G60)</f>
-        <v>88586808185.127838</v>
-      </c>
-      <c r="H60" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A61," ",Sheet1!B61)</f>
-        <v>Brett Barry</v>
-      </c>
-      <c r="B61" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A61, " (",Sheet1!H61,")")</f>
-        <v>Brett (Data Scientist)</v>
-      </c>
-      <c r="C61" s="9">
-        <f>SUM(Sheet1!D61:G61)</f>
-        <v>18130.46</v>
-      </c>
-      <c r="D61" s="9">
-        <f>AVERAGE(Sheet1!D61:G61)</f>
-        <v>4532.6149999999998</v>
-      </c>
-      <c r="E61" s="9">
-        <f>MEDIAN(Sheet1!D61:F61,Sheet1!G61)</f>
-        <v>4571.3450000000003</v>
-      </c>
-      <c r="F61" s="10">
-        <f>STDEV(Sheet1!D61:G61)</f>
-        <v>722.447985417175</v>
-      </c>
-      <c r="G61" s="9">
-        <f>PRODUCT(Sheet1!D61,Sheet1!F61:G61)</f>
-        <v>75487772950.730072</v>
-      </c>
-      <c r="H61" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A62," ",Sheet1!B62)</f>
-        <v>Wendy Jackson</v>
-      </c>
-      <c r="B62" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A62, " (",Sheet1!H62,")")</f>
-        <v>Wendy (UI/UX Designer)</v>
-      </c>
-      <c r="C62" s="9">
-        <f>SUM(Sheet1!D62:G62)</f>
-        <v>21912.55</v>
-      </c>
-      <c r="D62" s="9">
-        <f>AVERAGE(Sheet1!D62:G62)</f>
-        <v>5478.1374999999998</v>
-      </c>
-      <c r="E62" s="9">
-        <f>MEDIAN(Sheet1!D62:F62,Sheet1!G62)</f>
-        <v>5504.1949999999997</v>
-      </c>
-      <c r="F62" s="10">
-        <f>STDEV(Sheet1!D62:G62)</f>
-        <v>1322.4958020695838</v>
-      </c>
-      <c r="G62" s="9">
-        <f>PRODUCT(Sheet1!D62,Sheet1!F62:G62)</f>
-        <v>118613938050.51414</v>
-      </c>
-      <c r="H62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A63," ",Sheet1!B63)</f>
-        <v>Caitlin Farrell</v>
-      </c>
-      <c r="B63" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A63, " (",Sheet1!H63,")")</f>
-        <v>Caitlin (Data Scientist)</v>
-      </c>
-      <c r="C63" s="9">
-        <f>SUM(Sheet1!D63:G63)</f>
-        <v>20870.04</v>
-      </c>
-      <c r="D63" s="9">
-        <f>AVERAGE(Sheet1!D63:G63)</f>
-        <v>5217.51</v>
-      </c>
-      <c r="E63" s="9">
-        <f>MEDIAN(Sheet1!D63:F63,Sheet1!G63)</f>
-        <v>5380.96</v>
-      </c>
-      <c r="F63" s="10">
-        <f>STDEV(Sheet1!D63:G63)</f>
-        <v>1676.615032816617</v>
-      </c>
-      <c r="G63" s="9">
-        <f>PRODUCT(Sheet1!D63,Sheet1!F63:G63)</f>
-        <v>96595853101.523834</v>
-      </c>
-      <c r="H63" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A64," ",Sheet1!B64)</f>
-        <v>Eric Blevins</v>
-      </c>
-      <c r="B64" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A64, " (",Sheet1!H64,")")</f>
-        <v>Eric (Product Manager)</v>
-      </c>
-      <c r="C64" s="9">
-        <f>SUM(Sheet1!D64:G64)</f>
-        <v>19213.14</v>
-      </c>
-      <c r="D64" s="9">
-        <f>AVERAGE(Sheet1!D64:G64)</f>
-        <v>4803.2849999999999</v>
-      </c>
-      <c r="E64" s="9">
-        <f>MEDIAN(Sheet1!D64:F64,Sheet1!G64)</f>
-        <v>4701.26</v>
-      </c>
-      <c r="F64" s="10">
-        <f>STDEV(Sheet1!D64:G64)</f>
-        <v>842.96423160574705</v>
-      </c>
-      <c r="G64" s="9">
-        <f>PRODUCT(Sheet1!D64,Sheet1!F64:G64)</f>
-        <v>86043202363.647064</v>
-      </c>
-      <c r="H64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A65," ",Sheet1!B65)</f>
-        <v>Michael Walter</v>
-      </c>
-      <c r="B65" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A65, " (",Sheet1!H65,")")</f>
-        <v>Michael (QA Engineer)</v>
-      </c>
-      <c r="C65" s="9">
-        <f>SUM(Sheet1!D65:G65)</f>
-        <v>19428.939999999999</v>
-      </c>
-      <c r="D65" s="9">
-        <f>AVERAGE(Sheet1!D65:G65)</f>
-        <v>4857.2349999999997</v>
-      </c>
-      <c r="E65" s="9">
-        <f>MEDIAN(Sheet1!D65:F65,Sheet1!G65)</f>
-        <v>4995.5249999999996</v>
-      </c>
-      <c r="F65" s="10">
-        <f>STDEV(Sheet1!D65:G65)</f>
-        <v>1168.0978610972656</v>
-      </c>
-      <c r="G65" s="9">
-        <f>PRODUCT(Sheet1!D65,Sheet1!F65:G65)</f>
-        <v>153128674617.51056</v>
-      </c>
-      <c r="H65" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A66," ",Sheet1!B66)</f>
-        <v>Nancy Hughes</v>
-      </c>
-      <c r="B66" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A66, " (",Sheet1!H66,")")</f>
-        <v>Nancy (Full Stack Developer)</v>
-      </c>
-      <c r="C66" s="9">
-        <f>SUM(Sheet1!D66:G66)</f>
-        <v>20586.63</v>
-      </c>
-      <c r="D66" s="9">
-        <f>AVERAGE(Sheet1!D66:G66)</f>
-        <v>5146.6575000000003</v>
-      </c>
-      <c r="E66" s="9">
-        <f>MEDIAN(Sheet1!D66:F66,Sheet1!G66)</f>
-        <v>5252.2049999999999</v>
-      </c>
-      <c r="F66" s="10">
-        <f>STDEV(Sheet1!D66:G66)</f>
-        <v>466.03763284202722</v>
-      </c>
-      <c r="G66" s="9">
-        <f>PRODUCT(Sheet1!D66,Sheet1!F66:G66)</f>
-        <v>123987898742.00204</v>
-      </c>
-      <c r="H66" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A67," ",Sheet1!B67)</f>
-        <v>Glen Wilcox</v>
-      </c>
-      <c r="B67" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A67, " (",Sheet1!H67,")")</f>
-        <v>Glen (Full Stack Developer)</v>
-      </c>
-      <c r="C67" s="9">
-        <f>SUM(Sheet1!D67:G67)</f>
-        <v>19014.72</v>
-      </c>
-      <c r="D67" s="9">
-        <f>AVERAGE(Sheet1!D67:G67)</f>
-        <v>4753.68</v>
-      </c>
-      <c r="E67" s="9">
-        <f>MEDIAN(Sheet1!D67:F67,Sheet1!G67)</f>
-        <v>4596.7700000000004</v>
-      </c>
-      <c r="F67" s="10">
-        <f>STDEV(Sheet1!D67:G67)</f>
-        <v>1463.6993273210169</v>
-      </c>
-      <c r="G67" s="9">
-        <f>PRODUCT(Sheet1!D67,Sheet1!F67:G67)</f>
-        <v>136146181659.85097</v>
-      </c>
-      <c r="H67" s="9" t="str">
-        <f t="shared" ref="H67:H101" si="1">IF(E67&gt;D67,"Approved", "Not Approved")</f>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A68," ",Sheet1!B68)</f>
-        <v>Angela Hansen</v>
-      </c>
-      <c r="B68" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A68, " (",Sheet1!H68,")")</f>
-        <v>Angela (Backend Developer)</v>
-      </c>
-      <c r="C68" s="9">
-        <f>SUM(Sheet1!D68:G68)</f>
-        <v>23047.770000000004</v>
-      </c>
-      <c r="D68" s="9">
-        <f>AVERAGE(Sheet1!D68:G68)</f>
-        <v>5761.942500000001</v>
-      </c>
-      <c r="E68" s="9">
-        <f>MEDIAN(Sheet1!D68:F68,Sheet1!G68)</f>
-        <v>6097.3649999999998</v>
-      </c>
-      <c r="F68" s="10">
-        <f>STDEV(Sheet1!D68:G68)</f>
-        <v>1363.2090341390494</v>
-      </c>
-      <c r="G68" s="9">
-        <f>PRODUCT(Sheet1!D68,Sheet1!F68:G68)</f>
-        <v>153538562781.4957</v>
-      </c>
-      <c r="H68" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A69," ",Sheet1!B69)</f>
-        <v>Brian Bennett</v>
-      </c>
-      <c r="B69" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A69, " (",Sheet1!H69,")")</f>
-        <v>Brian (Product Manager)</v>
-      </c>
-      <c r="C69" s="9">
-        <f>SUM(Sheet1!D69:G69)</f>
-        <v>16931.150000000001</v>
-      </c>
-      <c r="D69" s="9">
-        <f>AVERAGE(Sheet1!D69:G69)</f>
-        <v>4232.7875000000004</v>
-      </c>
-      <c r="E69" s="9">
-        <f>MEDIAN(Sheet1!D69:F69,Sheet1!G69)</f>
-        <v>4227.47</v>
-      </c>
-      <c r="F69" s="10">
-        <f>STDEV(Sheet1!D69:G69)</f>
-        <v>505.10762373807734</v>
-      </c>
-      <c r="G69" s="9">
-        <f>PRODUCT(Sheet1!D69,Sheet1!F69:G69)</f>
-        <v>67704924764.87899</v>
-      </c>
-      <c r="H69" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A70," ",Sheet1!B70)</f>
-        <v>Steven Blair</v>
-      </c>
-      <c r="B70" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A70, " (",Sheet1!H70,")")</f>
-        <v>Steven (Full Stack Developer)</v>
-      </c>
-      <c r="C70" s="9">
-        <f>SUM(Sheet1!D70:G70)</f>
-        <v>17613.5</v>
-      </c>
-      <c r="D70" s="9">
-        <f>AVERAGE(Sheet1!D70:G70)</f>
-        <v>4403.375</v>
-      </c>
-      <c r="E70" s="9">
-        <f>MEDIAN(Sheet1!D70:F70,Sheet1!G70)</f>
-        <v>4440.7950000000001</v>
-      </c>
-      <c r="F70" s="10">
-        <f>STDEV(Sheet1!D70:G70)</f>
-        <v>1449.1172180906105</v>
-      </c>
-      <c r="G70" s="9">
-        <f>PRODUCT(Sheet1!D70,Sheet1!F70:G70)</f>
-        <v>104396260345.75856</v>
-      </c>
-      <c r="H70" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A71," ",Sheet1!B71)</f>
-        <v>Caitlyn Gutierrez</v>
-      </c>
-      <c r="B71" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A71, " (",Sheet1!H71,")")</f>
-        <v>Caitlyn (DevOps Engineer)</v>
-      </c>
-      <c r="C71" s="9">
-        <f>SUM(Sheet1!D71:G71)</f>
-        <v>18804.849999999999</v>
-      </c>
-      <c r="D71" s="9">
-        <f>AVERAGE(Sheet1!D71:G71)</f>
-        <v>4701.2124999999996</v>
-      </c>
-      <c r="E71" s="9">
-        <f>MEDIAN(Sheet1!D71:F71,Sheet1!G71)</f>
-        <v>4730.4650000000001</v>
-      </c>
-      <c r="F71" s="10">
-        <f>STDEV(Sheet1!D71:G71)</f>
-        <v>881.44978118911604</v>
-      </c>
-      <c r="G71" s="9">
-        <f>PRODUCT(Sheet1!D71,Sheet1!F71:G71)</f>
-        <v>94942775027.302032</v>
-      </c>
-      <c r="H71" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A72," ",Sheet1!B72)</f>
-        <v>Jennifer Marquez</v>
-      </c>
-      <c r="B72" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A72, " (",Sheet1!H72,")")</f>
-        <v>Jennifer (Full Stack Developer)</v>
-      </c>
-      <c r="C72" s="9">
-        <f>SUM(Sheet1!D72:G72)</f>
-        <v>18896.09</v>
-      </c>
-      <c r="D72" s="9">
-        <f>AVERAGE(Sheet1!D72:G72)</f>
-        <v>4724.0225</v>
-      </c>
-      <c r="E72" s="9">
-        <f>MEDIAN(Sheet1!D72:F72,Sheet1!G72)</f>
-        <v>4809.6550000000007</v>
-      </c>
-      <c r="F72" s="10">
-        <f>STDEV(Sheet1!D72:G72)</f>
-        <v>1155.7667690722335</v>
-      </c>
-      <c r="G72" s="9">
-        <f>PRODUCT(Sheet1!D72,Sheet1!F72:G72)</f>
-        <v>133585079922.14815</v>
-      </c>
-      <c r="H72" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A73," ",Sheet1!B73)</f>
-        <v>Joseph Black</v>
-      </c>
-      <c r="B73" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A73, " (",Sheet1!H73,")")</f>
-        <v>Joseph (Software Engineer)</v>
-      </c>
-      <c r="C73" s="9">
-        <f>SUM(Sheet1!D73:G73)</f>
-        <v>17337.689999999999</v>
-      </c>
-      <c r="D73" s="9">
-        <f>AVERAGE(Sheet1!D73:G73)</f>
-        <v>4334.4224999999997</v>
-      </c>
-      <c r="E73" s="9">
-        <f>MEDIAN(Sheet1!D73:F73,Sheet1!G73)</f>
-        <v>4139.4799999999996</v>
-      </c>
-      <c r="F73" s="10">
-        <f>STDEV(Sheet1!D73:G73)</f>
-        <v>1167.5812113760376</v>
-      </c>
-      <c r="G73" s="9">
-        <f>PRODUCT(Sheet1!D73,Sheet1!F73:G73)</f>
-        <v>78404179577.753082</v>
-      </c>
-      <c r="H73" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A74," ",Sheet1!B74)</f>
-        <v>Veronica Porter</v>
-      </c>
-      <c r="B74" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A74, " (",Sheet1!H74,")")</f>
-        <v>Veronica (Business Analyst)</v>
-      </c>
-      <c r="C74" s="9">
-        <f>SUM(Sheet1!D74:G74)</f>
-        <v>17077.93</v>
-      </c>
-      <c r="D74" s="9">
-        <f>AVERAGE(Sheet1!D74:G74)</f>
-        <v>4269.4825000000001</v>
-      </c>
-      <c r="E74" s="9">
-        <f>MEDIAN(Sheet1!D74:F74,Sheet1!G74)</f>
-        <v>3602.0600000000004</v>
-      </c>
-      <c r="F74" s="10">
-        <f>STDEV(Sheet1!D74:G74)</f>
-        <v>1793.7920908209135</v>
-      </c>
-      <c r="G74" s="9">
-        <f>PRODUCT(Sheet1!D74,Sheet1!F74:G74)</f>
-        <v>85440838451.515121</v>
-      </c>
-      <c r="H74" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A75," ",Sheet1!B75)</f>
-        <v>Amanda Todd</v>
-      </c>
-      <c r="B75" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A75, " (",Sheet1!H75,")")</f>
-        <v>Amanda (Cloud Engineer)</v>
-      </c>
-      <c r="C75" s="9">
-        <f>SUM(Sheet1!D75:G75)</f>
-        <v>15674.35</v>
-      </c>
-      <c r="D75" s="9">
-        <f>AVERAGE(Sheet1!D75:G75)</f>
-        <v>3918.5875000000001</v>
-      </c>
-      <c r="E75" s="9">
-        <f>MEDIAN(Sheet1!D75:F75,Sheet1!G75)</f>
-        <v>4074.8950000000004</v>
-      </c>
-      <c r="F75" s="10">
-        <f>STDEV(Sheet1!D75:G75)</f>
-        <v>555.69997722842197</v>
-      </c>
-      <c r="G75" s="9">
-        <f>PRODUCT(Sheet1!D75,Sheet1!F75:G75)</f>
-        <v>57929787896.080551</v>
-      </c>
-      <c r="H75" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A76," ",Sheet1!B76)</f>
-        <v>Ashley Brown</v>
-      </c>
-      <c r="B76" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A76, " (",Sheet1!H76,")")</f>
-        <v>Ashley (Software Engineer)</v>
-      </c>
-      <c r="C76" s="9">
-        <f>SUM(Sheet1!D76:G76)</f>
-        <v>21780.21</v>
-      </c>
-      <c r="D76" s="9">
-        <f>AVERAGE(Sheet1!D76:G76)</f>
-        <v>5445.0524999999998</v>
-      </c>
-      <c r="E76" s="9">
-        <f>MEDIAN(Sheet1!D76:F76,Sheet1!G76)</f>
-        <v>5217.3</v>
-      </c>
-      <c r="F76" s="10">
-        <f>STDEV(Sheet1!D76:G76)</f>
-        <v>1031.1545093203399</v>
-      </c>
-      <c r="G76" s="9">
-        <f>PRODUCT(Sheet1!D76,Sheet1!F76:G76)</f>
-        <v>122123246299.63921</v>
-      </c>
-      <c r="H76" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A77," ",Sheet1!B77)</f>
-        <v>Stephen Green</v>
-      </c>
-      <c r="B77" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A77, " (",Sheet1!H77,")")</f>
-        <v>Stephen (UI/UX Designer)</v>
-      </c>
-      <c r="C77" s="9">
-        <f>SUM(Sheet1!D77:G77)</f>
-        <v>22165.87</v>
-      </c>
-      <c r="D77" s="9">
-        <f>AVERAGE(Sheet1!D77:G77)</f>
-        <v>5541.4674999999997</v>
-      </c>
-      <c r="E77" s="9">
-        <f>MEDIAN(Sheet1!D77:F77,Sheet1!G77)</f>
-        <v>6060.66</v>
-      </c>
-      <c r="F77" s="10">
-        <f>STDEV(Sheet1!D77:G77)</f>
-        <v>1508.499346003063</v>
-      </c>
-      <c r="G77" s="9">
-        <f>PRODUCT(Sheet1!D77,Sheet1!F77:G77)</f>
-        <v>122340255426.26314</v>
-      </c>
-      <c r="H77" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A78," ",Sheet1!B78)</f>
-        <v>Angela Gibbs</v>
-      </c>
-      <c r="B78" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A78, " (",Sheet1!H78,")")</f>
-        <v>Angela (Business Analyst)</v>
-      </c>
-      <c r="C78" s="9">
-        <f>SUM(Sheet1!D78:G78)</f>
-        <v>16554.86</v>
-      </c>
-      <c r="D78" s="9">
-        <f>AVERAGE(Sheet1!D78:G78)</f>
-        <v>4138.7150000000001</v>
-      </c>
-      <c r="E78" s="9">
-        <f>MEDIAN(Sheet1!D78:F78,Sheet1!G78)</f>
-        <v>3876.5450000000001</v>
-      </c>
-      <c r="F78" s="10">
-        <f>STDEV(Sheet1!D78:G78)</f>
-        <v>1125.3640346276086</v>
-      </c>
-      <c r="G78" s="9">
-        <f>PRODUCT(Sheet1!D78,Sheet1!F78:G78)</f>
-        <v>78383505842.041</v>
-      </c>
-      <c r="H78" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A79," ",Sheet1!B79)</f>
-        <v>Timothy Hughes</v>
-      </c>
-      <c r="B79" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A79, " (",Sheet1!H79,")")</f>
-        <v>Timothy (Full Stack Developer)</v>
-      </c>
-      <c r="C79" s="9">
-        <f>SUM(Sheet1!D79:G79)</f>
-        <v>19838.38</v>
-      </c>
-      <c r="D79" s="9">
-        <f>AVERAGE(Sheet1!D79:G79)</f>
-        <v>4959.5950000000003</v>
-      </c>
-      <c r="E79" s="9">
-        <f>MEDIAN(Sheet1!D79:F79,Sheet1!G79)</f>
-        <v>4764.33</v>
-      </c>
-      <c r="F79" s="10">
-        <f>STDEV(Sheet1!D79:G79)</f>
-        <v>1127.7508440697354</v>
-      </c>
-      <c r="G79" s="9">
-        <f>PRODUCT(Sheet1!D79,Sheet1!F79:G79)</f>
-        <v>144810918400.89178</v>
-      </c>
-      <c r="H79" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A80," ",Sheet1!B80)</f>
-        <v>Vanessa Griffin</v>
-      </c>
-      <c r="B80" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A80, " (",Sheet1!H80,")")</f>
-        <v>Vanessa (Data Scientist)</v>
-      </c>
-      <c r="C80" s="9">
-        <f>SUM(Sheet1!D80:G80)</f>
-        <v>18426.330000000002</v>
-      </c>
-      <c r="D80" s="9">
-        <f>AVERAGE(Sheet1!D80:G80)</f>
-        <v>4606.5825000000004</v>
-      </c>
-      <c r="E80" s="9">
-        <f>MEDIAN(Sheet1!D80:F80,Sheet1!G80)</f>
-        <v>4597.24</v>
-      </c>
-      <c r="F80" s="10">
-        <f>STDEV(Sheet1!D80:G80)</f>
-        <v>1267.6660293987775</v>
-      </c>
-      <c r="G80" s="9">
-        <f>PRODUCT(Sheet1!D80,Sheet1!F80:G80)</f>
-        <v>93292651885.618942</v>
-      </c>
-      <c r="H80" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A81," ",Sheet1!B81)</f>
-        <v>Kaitlin Colon</v>
-      </c>
-      <c r="B81" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A81, " (",Sheet1!H81,")")</f>
-        <v>Kaitlin (Scrum Master)</v>
-      </c>
-      <c r="C81" s="9">
-        <f>SUM(Sheet1!D81:G81)</f>
-        <v>16668.38</v>
-      </c>
-      <c r="D81" s="9">
-        <f>AVERAGE(Sheet1!D81:G81)</f>
-        <v>4167.0950000000003</v>
-      </c>
-      <c r="E81" s="9">
-        <f>MEDIAN(Sheet1!D81:F81,Sheet1!G81)</f>
-        <v>3887.17</v>
-      </c>
-      <c r="F81" s="10">
-        <f>STDEV(Sheet1!D81:G81)</f>
-        <v>1247.4151424846491</v>
-      </c>
-      <c r="G81" s="9">
-        <f>PRODUCT(Sheet1!D81,Sheet1!F81:G81)</f>
-        <v>45405706108.971603</v>
-      </c>
-      <c r="H81" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A82," ",Sheet1!B82)</f>
-        <v>Joshua Benson</v>
-      </c>
-      <c r="B82" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A82, " (",Sheet1!H82,")")</f>
-        <v>Joshua (Data Scientist)</v>
-      </c>
-      <c r="C82" s="9">
-        <f>SUM(Sheet1!D82:G82)</f>
-        <v>19293.84</v>
-      </c>
-      <c r="D82" s="9">
-        <f>AVERAGE(Sheet1!D82:G82)</f>
-        <v>4823.46</v>
-      </c>
-      <c r="E82" s="9">
-        <f>MEDIAN(Sheet1!D82:F82,Sheet1!G82)</f>
-        <v>4401.7349999999997</v>
-      </c>
-      <c r="F82" s="10">
-        <f>STDEV(Sheet1!D82:G82)</f>
-        <v>1542.8769077062902</v>
-      </c>
-      <c r="G82" s="9">
-        <f>PRODUCT(Sheet1!D82,Sheet1!F82:G82)</f>
-        <v>128302228318.60582</v>
-      </c>
-      <c r="H82" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A83," ",Sheet1!B83)</f>
-        <v>Nicholas Chavez</v>
-      </c>
-      <c r="B83" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A83, " (",Sheet1!H83,")")</f>
-        <v>Nicholas (Security Analyst)</v>
-      </c>
-      <c r="C83" s="9">
-        <f>SUM(Sheet1!D83:G83)</f>
-        <v>18560.11</v>
-      </c>
-      <c r="D83" s="9">
-        <f>AVERAGE(Sheet1!D83:G83)</f>
-        <v>4640.0275000000001</v>
-      </c>
-      <c r="E83" s="9">
-        <f>MEDIAN(Sheet1!D83:F83,Sheet1!G83)</f>
-        <v>4793</v>
-      </c>
-      <c r="F83" s="10">
-        <f>STDEV(Sheet1!D83:G83)</f>
-        <v>1236.9130520877359</v>
-      </c>
-      <c r="G83" s="9">
-        <f>PRODUCT(Sheet1!D83,Sheet1!F83:G83)</f>
-        <v>90748270084.750259</v>
-      </c>
-      <c r="H83" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A84," ",Sheet1!B84)</f>
-        <v>Timothy Nelson</v>
-      </c>
-      <c r="B84" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A84, " (",Sheet1!H84,")")</f>
-        <v>Timothy (Frontend Developer)</v>
-      </c>
-      <c r="C84" s="9">
-        <f>SUM(Sheet1!D84:G84)</f>
-        <v>19074.2</v>
-      </c>
-      <c r="D84" s="9">
-        <f>AVERAGE(Sheet1!D84:G84)</f>
-        <v>4768.55</v>
-      </c>
-      <c r="E84" s="9">
-        <f>MEDIAN(Sheet1!D84:F84,Sheet1!G84)</f>
-        <v>4336.2150000000001</v>
-      </c>
-      <c r="F84" s="10">
-        <f>STDEV(Sheet1!D84:G84)</f>
-        <v>1382.2439053220667</v>
-      </c>
-      <c r="G84" s="9">
-        <f>PRODUCT(Sheet1!D84,Sheet1!F84:G84)</f>
-        <v>116582513141.04779</v>
-      </c>
-      <c r="H84" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A85," ",Sheet1!B85)</f>
-        <v>Scott Smith</v>
-      </c>
-      <c r="B85" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A85, " (",Sheet1!H85,")")</f>
-        <v>Scott (Frontend Developer)</v>
-      </c>
-      <c r="C85" s="9">
-        <f>SUM(Sheet1!D85:G85)</f>
-        <v>21241.65</v>
-      </c>
-      <c r="D85" s="9">
-        <f>AVERAGE(Sheet1!D85:G85)</f>
-        <v>5310.4125000000004</v>
-      </c>
-      <c r="E85" s="9">
-        <f>MEDIAN(Sheet1!D85:F85,Sheet1!G85)</f>
-        <v>5599.3600000000006</v>
-      </c>
-      <c r="F85" s="10">
-        <f>STDEV(Sheet1!D85:G85)</f>
-        <v>1031.2032643591645</v>
-      </c>
-      <c r="G85" s="9">
-        <f>PRODUCT(Sheet1!D85,Sheet1!F85:G85)</f>
-        <v>137870426873.35104</v>
-      </c>
-      <c r="H85" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A86," ",Sheet1!B86)</f>
-        <v>Cathy Carr</v>
-      </c>
-      <c r="B86" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A86, " (",Sheet1!H86,")")</f>
-        <v>Cathy (DevOps Engineer)</v>
-      </c>
-      <c r="C86" s="9">
-        <f>SUM(Sheet1!D86:G86)</f>
-        <v>22267.69</v>
-      </c>
-      <c r="D86" s="9">
-        <f>AVERAGE(Sheet1!D86:G86)</f>
-        <v>5566.9224999999997</v>
-      </c>
-      <c r="E86" s="9">
-        <f>MEDIAN(Sheet1!D86:F86,Sheet1!G86)</f>
-        <v>5608.3649999999998</v>
-      </c>
-      <c r="F86" s="10">
-        <f>STDEV(Sheet1!D86:G86)</f>
-        <v>910.44551937957146</v>
-      </c>
-      <c r="G86" s="9">
-        <f>PRODUCT(Sheet1!D86,Sheet1!F86:G86)</f>
-        <v>168926898807.40781</v>
-      </c>
-      <c r="H86" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A87," ",Sheet1!B87)</f>
-        <v>Katherine Williams</v>
-      </c>
-      <c r="B87" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A87, " (",Sheet1!H87,")")</f>
-        <v>Katherine (Mobile App Developer)</v>
-      </c>
-      <c r="C87" s="9">
-        <f>SUM(Sheet1!D87:G87)</f>
-        <v>21501.82</v>
-      </c>
-      <c r="D87" s="9">
-        <f>AVERAGE(Sheet1!D87:G87)</f>
-        <v>5375.4549999999999</v>
-      </c>
-      <c r="E87" s="9">
-        <f>MEDIAN(Sheet1!D87:F87,Sheet1!G87)</f>
-        <v>5780.26</v>
-      </c>
-      <c r="F87" s="10">
-        <f>STDEV(Sheet1!D87:G87)</f>
-        <v>1172.0310639085767</v>
-      </c>
-      <c r="G87" s="9">
-        <f>PRODUCT(Sheet1!D87,Sheet1!F87:G87)</f>
-        <v>210043184049.16562</v>
-      </c>
-      <c r="H87" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A88," ",Sheet1!B88)</f>
-        <v>Shane Oconnor</v>
-      </c>
-      <c r="B88" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A88, " (",Sheet1!H88,")")</f>
-        <v>Shane (Security Analyst)</v>
-      </c>
-      <c r="C88" s="9">
-        <f>SUM(Sheet1!D88:G88)</f>
-        <v>19744.52</v>
-      </c>
-      <c r="D88" s="9">
-        <f>AVERAGE(Sheet1!D88:G88)</f>
-        <v>4936.13</v>
-      </c>
-      <c r="E88" s="9">
-        <f>MEDIAN(Sheet1!D88:F88,Sheet1!G88)</f>
-        <v>5317.0249999999996</v>
-      </c>
-      <c r="F88" s="10">
-        <f>STDEV(Sheet1!D88:G88)</f>
-        <v>1129.455243351116</v>
-      </c>
-      <c r="G88" s="9">
-        <f>PRODUCT(Sheet1!D88,Sheet1!F88:G88)</f>
-        <v>92767991893.954193</v>
-      </c>
-      <c r="H88" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A89," ",Sheet1!B89)</f>
-        <v>Natalie White</v>
-      </c>
-      <c r="B89" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A89, " (",Sheet1!H89,")")</f>
-        <v>Natalie (Backend Developer)</v>
-      </c>
-      <c r="C89" s="9">
-        <f>SUM(Sheet1!D89:G89)</f>
-        <v>22902.440000000002</v>
-      </c>
-      <c r="D89" s="9">
-        <f>AVERAGE(Sheet1!D89:G89)</f>
-        <v>5725.6100000000006</v>
-      </c>
-      <c r="E89" s="9">
-        <f>MEDIAN(Sheet1!D89:F89,Sheet1!G89)</f>
-        <v>5865.335</v>
-      </c>
-      <c r="F89" s="10">
-        <f>STDEV(Sheet1!D89:G89)</f>
-        <v>714.31725551979014</v>
-      </c>
-      <c r="G89" s="9">
-        <f>PRODUCT(Sheet1!D89,Sheet1!F89:G89)</f>
-        <v>163435881303.95099</v>
-      </c>
-      <c r="H89" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A90," ",Sheet1!B90)</f>
-        <v>Hannah Schmidt</v>
-      </c>
-      <c r="B90" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A90, " (",Sheet1!H90,")")</f>
-        <v>Hannah (System Administrator)</v>
-      </c>
-      <c r="C90" s="9">
-        <f>SUM(Sheet1!D90:G90)</f>
-        <v>18634.68</v>
-      </c>
-      <c r="D90" s="9">
-        <f>AVERAGE(Sheet1!D90:G90)</f>
-        <v>4658.67</v>
-      </c>
-      <c r="E90" s="9">
-        <f>MEDIAN(Sheet1!D90:F90,Sheet1!G90)</f>
-        <v>4720.0999999999995</v>
-      </c>
-      <c r="F90" s="10">
-        <f>STDEV(Sheet1!D90:G90)</f>
-        <v>1699.9921361190648</v>
-      </c>
-      <c r="G90" s="9">
-        <f>PRODUCT(Sheet1!D90,Sheet1!F90:G90)</f>
-        <v>62897184451.772697</v>
-      </c>
-      <c r="H90" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A91," ",Sheet1!B91)</f>
-        <v>Alexandra Bates</v>
-      </c>
-      <c r="B91" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A91, " (",Sheet1!H91,")")</f>
-        <v>Alexandra (DevOps Engineer)</v>
-      </c>
-      <c r="C91" s="9">
-        <f>SUM(Sheet1!D91:G91)</f>
-        <v>21365.14</v>
-      </c>
-      <c r="D91" s="9">
-        <f>AVERAGE(Sheet1!D91:G91)</f>
-        <v>5341.2849999999999</v>
-      </c>
-      <c r="E91" s="9">
-        <f>MEDIAN(Sheet1!D91:F91,Sheet1!G91)</f>
-        <v>5315.42</v>
-      </c>
-      <c r="F91" s="10">
-        <f>STDEV(Sheet1!D91:G91)</f>
-        <v>1248.1519362241143</v>
-      </c>
-      <c r="G91" s="9">
-        <f>PRODUCT(Sheet1!D91,Sheet1!F91:G91)</f>
-        <v>164025137713.203</v>
-      </c>
-      <c r="H91" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A92," ",Sheet1!B92)</f>
-        <v>Justin Pham</v>
-      </c>
-      <c r="B92" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A92, " (",Sheet1!H92,")")</f>
-        <v>Justin (Business Analyst)</v>
-      </c>
-      <c r="C92" s="9">
-        <f>SUM(Sheet1!D92:G92)</f>
-        <v>19777.61</v>
-      </c>
-      <c r="D92" s="9">
-        <f>AVERAGE(Sheet1!D92:G92)</f>
-        <v>4944.4025000000001</v>
-      </c>
-      <c r="E92" s="9">
-        <f>MEDIAN(Sheet1!D92:F92,Sheet1!G92)</f>
-        <v>4975.5400000000009</v>
-      </c>
-      <c r="F92" s="10">
-        <f>STDEV(Sheet1!D92:G92)</f>
-        <v>881.11396158025946</v>
-      </c>
-      <c r="G92" s="9">
-        <f>PRODUCT(Sheet1!D92,Sheet1!F92:G92)</f>
-        <v>95118190907.376648</v>
-      </c>
-      <c r="H92" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A93," ",Sheet1!B93)</f>
-        <v>Paul Peterson</v>
-      </c>
-      <c r="B93" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A93, " (",Sheet1!H93,")")</f>
-        <v>Paul (Product Manager)</v>
-      </c>
-      <c r="C93" s="9">
-        <f>SUM(Sheet1!D93:G93)</f>
-        <v>21287.41</v>
-      </c>
-      <c r="D93" s="9">
-        <f>AVERAGE(Sheet1!D93:G93)</f>
-        <v>5321.8525</v>
-      </c>
-      <c r="E93" s="9">
-        <f>MEDIAN(Sheet1!D93:F93,Sheet1!G93)</f>
-        <v>5488.3549999999996</v>
-      </c>
-      <c r="F93" s="10">
-        <f>STDEV(Sheet1!D93:G93)</f>
-        <v>726.11160516709708</v>
-      </c>
-      <c r="G93" s="9">
-        <f>PRODUCT(Sheet1!D93,Sheet1!F93:G93)</f>
-        <v>130646291244.30035</v>
-      </c>
-      <c r="H93" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A94," ",Sheet1!B94)</f>
-        <v>Joel King</v>
-      </c>
-      <c r="B94" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A94, " (",Sheet1!H94,")")</f>
-        <v>Joel (Data Scientist)</v>
-      </c>
-      <c r="C94" s="9">
-        <f>SUM(Sheet1!D94:G94)</f>
-        <v>16943.949999999997</v>
-      </c>
-      <c r="D94" s="9">
-        <f>AVERAGE(Sheet1!D94:G94)</f>
-        <v>4235.9874999999993</v>
-      </c>
-      <c r="E94" s="9">
-        <f>MEDIAN(Sheet1!D94:F94,Sheet1!G94)</f>
-        <v>4050.6149999999998</v>
-      </c>
-      <c r="F94" s="10">
-        <f>STDEV(Sheet1!D94:G94)</f>
-        <v>951.94967967062269</v>
-      </c>
-      <c r="G94" s="9">
-        <f>PRODUCT(Sheet1!D94,Sheet1!F94:G94)</f>
-        <v>53912058466.226677</v>
-      </c>
-      <c r="H94" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A95," ",Sheet1!B95)</f>
-        <v>Elaine Shaw</v>
-      </c>
-      <c r="B95" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A95, " (",Sheet1!H95,")")</f>
-        <v>Elaine (QA Engineer)</v>
-      </c>
-      <c r="C95" s="9">
-        <f>SUM(Sheet1!D95:G95)</f>
-        <v>23022.57</v>
-      </c>
-      <c r="D95" s="9">
-        <f>AVERAGE(Sheet1!D95:G95)</f>
-        <v>5755.6424999999999</v>
-      </c>
-      <c r="E95" s="9">
-        <f>MEDIAN(Sheet1!D95:F95,Sheet1!G95)</f>
-        <v>5897.5249999999996</v>
-      </c>
-      <c r="F95" s="10">
-        <f>STDEV(Sheet1!D95:G95)</f>
-        <v>948.32521785777556</v>
-      </c>
-      <c r="G95" s="9">
-        <f>PRODUCT(Sheet1!D95,Sheet1!F95:G95)</f>
-        <v>227770836653.85419</v>
-      </c>
-      <c r="H95" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A96," ",Sheet1!B96)</f>
-        <v>Tanya Nielsen</v>
-      </c>
-      <c r="B96" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A96, " (",Sheet1!H96,")")</f>
-        <v>Tanya (System Administrator)</v>
-      </c>
-      <c r="C96" s="9">
-        <f>SUM(Sheet1!D96:G96)</f>
-        <v>19242.05</v>
-      </c>
-      <c r="D96" s="9">
-        <f>AVERAGE(Sheet1!D96:G96)</f>
-        <v>4810.5124999999998</v>
-      </c>
-      <c r="E96" s="9">
-        <f>MEDIAN(Sheet1!D96:F96,Sheet1!G96)</f>
-        <v>4876.165</v>
-      </c>
-      <c r="F96" s="10">
-        <f>STDEV(Sheet1!D96:G96)</f>
-        <v>1119.8616539964523</v>
-      </c>
-      <c r="G96" s="9">
-        <f>PRODUCT(Sheet1!D96,Sheet1!F96:G96)</f>
-        <v>80290192745.185165</v>
-      </c>
-      <c r="H96" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A97," ",Sheet1!B97)</f>
-        <v>Alejandra Mueller</v>
-      </c>
-      <c r="B97" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A97, " (",Sheet1!H97,")")</f>
-        <v>Alejandra (UI/UX Designer)</v>
-      </c>
-      <c r="C97" s="9">
-        <f>SUM(Sheet1!D97:G97)</f>
-        <v>19409.71</v>
-      </c>
-      <c r="D97" s="9">
-        <f>AVERAGE(Sheet1!D97:G97)</f>
-        <v>4852.4274999999998</v>
-      </c>
-      <c r="E97" s="9">
-        <f>MEDIAN(Sheet1!D97:F97,Sheet1!G97)</f>
-        <v>4991.25</v>
-      </c>
-      <c r="F97" s="10">
-        <f>STDEV(Sheet1!D97:G97)</f>
-        <v>1222.984391352428</v>
-      </c>
-      <c r="G97" s="9">
-        <f>PRODUCT(Sheet1!D97,Sheet1!F97:G97)</f>
-        <v>102463335803.36929</v>
-      </c>
-      <c r="H97" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A98," ",Sheet1!B98)</f>
-        <v>Eddie Perez</v>
-      </c>
-      <c r="B98" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A98, " (",Sheet1!H98,")")</f>
-        <v>Eddie (Technical Support)</v>
-      </c>
-      <c r="C98" s="9">
-        <f>SUM(Sheet1!D98:G98)</f>
-        <v>18746.150000000001</v>
-      </c>
-      <c r="D98" s="9">
-        <f>AVERAGE(Sheet1!D98:G98)</f>
-        <v>4686.5375000000004</v>
-      </c>
-      <c r="E98" s="9">
-        <f>MEDIAN(Sheet1!D98:F98,Sheet1!G98)</f>
-        <v>4762.4400000000005</v>
-      </c>
-      <c r="F98" s="10">
-        <f>STDEV(Sheet1!D98:G98)</f>
-        <v>1188.5130753277374</v>
-      </c>
-      <c r="G98" s="9">
-        <f>PRODUCT(Sheet1!D98,Sheet1!F98:G98)</f>
-        <v>102903114044.19565</v>
-      </c>
-      <c r="H98" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Approved</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A99," ",Sheet1!B99)</f>
-        <v>Jessica Nunez</v>
-      </c>
-      <c r="B99" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A99, " (",Sheet1!H99,")")</f>
-        <v>Jessica (UI/UX Designer)</v>
-      </c>
-      <c r="C99" s="9">
-        <f>SUM(Sheet1!D99:G99)</f>
-        <v>17845.009999999998</v>
-      </c>
-      <c r="D99" s="9">
-        <f>AVERAGE(Sheet1!D99:G99)</f>
-        <v>4461.2524999999996</v>
-      </c>
-      <c r="E99" s="9">
-        <f>MEDIAN(Sheet1!D99:F99,Sheet1!G99)</f>
-        <v>3923.0349999999999</v>
-      </c>
-      <c r="F99" s="10">
-        <f>STDEV(Sheet1!D99:G99)</f>
-        <v>1631.3872216281663</v>
-      </c>
-      <c r="G99" s="9">
-        <f>PRODUCT(Sheet1!D99,Sheet1!F99:G99)</f>
-        <v>78064189310.20372</v>
-      </c>
-      <c r="H99" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A100," ",Sheet1!B100)</f>
-        <v>Carrie Wright</v>
-      </c>
-      <c r="B100" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A100, " (",Sheet1!H100,")")</f>
-        <v>Carrie (Full Stack Developer)</v>
-      </c>
-      <c r="C100" s="9">
-        <f>SUM(Sheet1!D100:G100)</f>
-        <v>19593.02</v>
-      </c>
-      <c r="D100" s="9">
-        <f>AVERAGE(Sheet1!D100:G100)</f>
-        <v>4898.2550000000001</v>
-      </c>
-      <c r="E100" s="9">
-        <f>MEDIAN(Sheet1!D100:F100,Sheet1!G100)</f>
-        <v>4556.71</v>
-      </c>
-      <c r="F100" s="10">
-        <f>STDEV(Sheet1!D100:G100)</f>
-        <v>1497.5227319476637</v>
-      </c>
-      <c r="G100" s="9">
-        <f>PRODUCT(Sheet1!D100,Sheet1!F100:G100)</f>
-        <v>121263863034.35628</v>
-      </c>
-      <c r="H100" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A101," ",Sheet1!B101)</f>
-        <v>Daniel Haynes</v>
-      </c>
-      <c r="B101" s="9" t="str">
-        <f>_xlfn.CONCAT(Sheet1!A101, " (",Sheet1!H101,")")</f>
-        <v>Daniel (Backend Developer)</v>
-      </c>
-      <c r="C101" s="9">
-        <f>SUM(Sheet1!D101:G101)</f>
-        <v>21449.11</v>
-      </c>
-      <c r="D101" s="9">
-        <f>AVERAGE(Sheet1!D101:G101)</f>
-        <v>5362.2775000000001</v>
-      </c>
-      <c r="E101" s="9">
-        <f>MEDIAN(Sheet1!D101:F101,Sheet1!G101)</f>
-        <v>5326.5550000000003</v>
-      </c>
-      <c r="F101" s="10">
-        <f>STDEV(Sheet1!D101:G101)</f>
-        <v>1143.3617554496905</v>
-      </c>
-      <c r="G101" s="9">
-        <f>PRODUCT(Sheet1!D101,Sheet1!F101:G101)</f>
-        <v>146893185171.40561</v>
-      </c>
-      <c r="H101" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Approved</v>
+    <row r="2" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D101">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44831B24-8F21-4600-A16D-99B90A9E404E}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F101">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G101">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B228BA3C-846D-4582-BFD8-5C0712141BC8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -8169,32 +8029,6 @@
           </x14:cfRule>
           <xm:sqref>J5</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44831B24-8F21-4600-A16D-99B90A9E404E}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D2:D101</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B228BA3C-846D-4582-BFD8-5C0712141BC8}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF008AEF"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>G2:G101</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
